--- a/src/test/resources/Login_TC.xlsx
+++ b/src/test/resources/Login_TC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\automation-framework\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\advanced_selenium_framework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E963ED1-0004-4663-AD82-CC47B3F55968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57393A47-D85A-45E8-AD72-D1BA549B5F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="3" r:id="rId1"/>
@@ -1102,12 +1102,6 @@
     <t>password</t>
   </si>
   <si>
-    <t>chivq9@fpt.com</t>
-  </si>
-  <si>
-    <t>Blackpink20112003.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Đăng nhập bằng SSO thành công: </t>
     </r>
@@ -1877,12 +1871,18 @@
   <si>
     <t>//button[@type='button' and (.//span[normalize-space()='Gửi' or normalize-space()='Send'] or normalize-space()='Gửi' or normalize-space()='Send')]</t>
   </si>
+  <si>
+    <t>trangntt219@fpt.com</t>
+  </si>
+  <si>
+    <t>TuanKiet@1810</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1963,6 +1963,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2060,11 +2068,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2138,8 +2147,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{E8C153C8-3DCD-4C83-AB27-02EEFDB33FD9}"/>
   </cellStyles>
@@ -2453,26 +2464,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="74" style="24" customWidth="1"/>
-    <col min="3" max="3" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="65.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="80.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="65.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="80.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>175</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>11</v>
@@ -2484,15 +2496,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -2501,18 +2513,18 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -2521,18 +2533,18 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" t="s">
         <v>225</v>
-      </c>
-      <c r="C4" t="s">
-        <v>227</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -2541,38 +2553,38 @@
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -2581,18 +2593,18 @@
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D7" t="s">
         <v>30</v>
@@ -2601,18 +2613,18 @@
         <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>31</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -2624,32 +2636,32 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>39</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D10" s="24" t="s">
         <v>41</v>
@@ -2658,18 +2670,18 @@
         <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>43</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>45</v>
@@ -2678,18 +2690,18 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>46</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>48</v>
@@ -2698,18 +2710,18 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -2718,18 +2730,18 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>54</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>56</v>
@@ -2741,15 +2753,15 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>58</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>60</v>
@@ -2758,18 +2770,18 @@
         <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>62</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D16" t="s">
         <v>51</v>
@@ -2781,15 +2793,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>66</v>
@@ -2798,18 +2810,18 @@
         <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D18" t="s">
         <v>70</v>
@@ -2818,18 +2830,18 @@
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>71</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D19" t="s">
         <v>73</v>
@@ -2838,18 +2850,18 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>74</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -2861,15 +2873,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>77</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -2881,15 +2893,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>80</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D22" t="s">
         <v>82</v>
@@ -2898,38 +2910,38 @@
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>83</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>87</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C24" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s">
         <v>89</v>
@@ -2938,18 +2950,18 @@
         <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>91</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D25" t="s">
         <v>94</v>
@@ -2958,18 +2970,18 @@
         <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>95</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -2978,18 +2990,18 @@
         <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C27" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D27" t="s">
         <v>100</v>
@@ -2998,18 +3010,18 @@
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>101</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D28" t="s">
         <v>104</v>
@@ -3018,18 +3030,18 @@
         <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>105</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C29" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D29" t="s">
         <v>104</v>
@@ -3038,18 +3050,18 @@
         <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>107</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C30" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D30" t="s">
         <v>104</v>
@@ -3058,18 +3070,18 @@
         <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>109</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C31" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D31" t="s">
         <v>112</v>
@@ -3078,18 +3090,18 @@
         <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>113</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C32" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D32" t="s">
         <v>115</v>
@@ -3098,18 +3110,18 @@
         <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>116</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C33" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D33" t="s">
         <v>118</v>
@@ -3118,18 +3130,18 @@
         <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>119</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C34" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D34" t="s">
         <v>121</v>
@@ -3138,18 +3150,18 @@
         <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D35" t="s">
         <v>125</v>
@@ -3161,15 +3173,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>126</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D36" t="s">
         <v>128</v>
@@ -3178,18 +3190,18 @@
         <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>129</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D37" t="s">
         <v>131</v>
@@ -3198,18 +3210,18 @@
         <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>132</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D38" t="s">
         <v>135</v>
@@ -3218,18 +3230,18 @@
         <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>136</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D39" t="s">
         <v>138</v>
@@ -3238,18 +3250,18 @@
         <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>139</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D40" t="s">
         <v>141</v>
@@ -3258,18 +3270,18 @@
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>142</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C41" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D41" t="s">
         <v>145</v>
@@ -3278,18 +3290,18 @@
         <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>146</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D42" t="s">
         <v>148</v>
@@ -3298,38 +3310,38 @@
         <v>42</v>
       </c>
       <c r="F42" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>149</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D43" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>153</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D44" t="s">
         <v>76</v>
@@ -3341,15 +3353,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>155</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C45" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
         <v>157</v>
@@ -3358,18 +3370,18 @@
         <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>158</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C46" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D46" t="s">
         <v>161</v>
@@ -3378,18 +3390,18 @@
         <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>162</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D47" t="s">
         <v>161</v>
@@ -3401,15 +3413,15 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>165</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C48" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D48" t="s">
         <v>161</v>
@@ -3418,51 +3430,57 @@
         <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>167</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C49" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D49" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E49" t="s">
         <v>52</v>
       </c>
       <c r="F49" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>172</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C50" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D50" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="C1:C50" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Y"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3470,1754 +3488,1754 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F87"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="134.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="134.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>175</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>283</v>
-      </c>
       <c r="E1" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" t="s">
         <v>188</v>
       </c>
-      <c r="C2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" t="s">
         <v>190</v>
       </c>
-      <c r="E2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" t="s">
         <v>193</v>
       </c>
-      <c r="C3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" t="s">
         <v>196</v>
       </c>
-      <c r="C4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" t="s">
-        <v>197</v>
-      </c>
-      <c r="E4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" t="s">
         <v>188</v>
       </c>
-      <c r="C6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" t="s">
         <v>190</v>
       </c>
-      <c r="E6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" t="s">
         <v>193</v>
       </c>
-      <c r="C7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D7" t="s">
-        <v>194</v>
-      </c>
-      <c r="E7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>18</v>
       </c>
       <c r="B8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" t="s">
         <v>196</v>
       </c>
-      <c r="C8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" t="s">
         <v>188</v>
       </c>
-      <c r="C11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F11" t="s">
         <v>190</v>
       </c>
-      <c r="E11" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E12" t="s">
+        <v>189</v>
+      </c>
+      <c r="F12" t="s">
         <v>193</v>
       </c>
-      <c r="C12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" t="s">
-        <v>194</v>
-      </c>
-      <c r="E12" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" t="s">
         <v>196</v>
       </c>
-      <c r="C13" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" t="s">
-        <v>197</v>
-      </c>
-      <c r="E13" t="s">
-        <v>191</v>
-      </c>
-      <c r="F13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F14" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F15" t="s">
         <v>208</v>
       </c>
-      <c r="C15" t="s">
-        <v>189</v>
-      </c>
-      <c r="D15" t="s">
-        <v>209</v>
-      </c>
-      <c r="E15" t="s">
-        <v>191</v>
-      </c>
-      <c r="F15" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F16" t="s">
         <v>211</v>
       </c>
-      <c r="C16" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E16" t="s">
-        <v>191</v>
-      </c>
-      <c r="F16" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" t="s">
+        <v>189</v>
+      </c>
+      <c r="F17" t="s">
         <v>212</v>
       </c>
-      <c r="E17" t="s">
-        <v>191</v>
-      </c>
-      <c r="F17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" t="s">
         <v>188</v>
       </c>
-      <c r="C18" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" t="s">
         <v>190</v>
       </c>
-      <c r="E18" t="s">
-        <v>191</v>
-      </c>
-      <c r="F18" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" t="s">
+        <v>192</v>
+      </c>
+      <c r="E19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" t="s">
         <v>193</v>
       </c>
-      <c r="C19" t="s">
-        <v>189</v>
-      </c>
-      <c r="D19" t="s">
-        <v>194</v>
-      </c>
-      <c r="E19" t="s">
-        <v>191</v>
-      </c>
-      <c r="F19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" t="s">
         <v>196</v>
       </c>
-      <c r="C20" t="s">
-        <v>189</v>
-      </c>
-      <c r="D20" t="s">
-        <v>197</v>
-      </c>
-      <c r="E20" t="s">
-        <v>191</v>
-      </c>
-      <c r="F20" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E22" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F22" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F23" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F24" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>35</v>
       </c>
       <c r="B25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" t="s">
         <v>188</v>
       </c>
-      <c r="C25" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>189</v>
+      </c>
+      <c r="F25" t="s">
         <v>190</v>
       </c>
-      <c r="E25" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>35</v>
       </c>
       <c r="B26" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" t="s">
+        <v>192</v>
+      </c>
+      <c r="E26" t="s">
+        <v>189</v>
+      </c>
+      <c r="F26" t="s">
         <v>193</v>
       </c>
-      <c r="C26" t="s">
-        <v>189</v>
-      </c>
-      <c r="D26" t="s">
-        <v>194</v>
-      </c>
-      <c r="E26" t="s">
-        <v>191</v>
-      </c>
-      <c r="F26" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
       <c r="B27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" t="s">
+        <v>189</v>
+      </c>
+      <c r="F27" t="s">
         <v>196</v>
       </c>
-      <c r="C27" t="s">
-        <v>189</v>
-      </c>
-      <c r="D27" t="s">
-        <v>197</v>
-      </c>
-      <c r="E27" t="s">
-        <v>191</v>
-      </c>
-      <c r="F27" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E28" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D29" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F29" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>43</v>
       </c>
       <c r="B30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" t="s">
         <v>188</v>
       </c>
-      <c r="C30" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" t="s">
         <v>190</v>
       </c>
-      <c r="E30" t="s">
-        <v>191</v>
-      </c>
-      <c r="F30" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>43</v>
       </c>
       <c r="B31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" t="s">
+        <v>189</v>
+      </c>
+      <c r="F31" t="s">
         <v>193</v>
       </c>
-      <c r="C31" t="s">
-        <v>189</v>
-      </c>
-      <c r="D31" t="s">
-        <v>194</v>
-      </c>
-      <c r="E31" t="s">
-        <v>191</v>
-      </c>
-      <c r="F31" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>43</v>
       </c>
       <c r="B32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C32" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" t="s">
+        <v>195</v>
+      </c>
+      <c r="E32" t="s">
+        <v>189</v>
+      </c>
+      <c r="F32" t="s">
         <v>196</v>
       </c>
-      <c r="C32" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" t="s">
-        <v>197</v>
-      </c>
-      <c r="E32" t="s">
-        <v>191</v>
-      </c>
-      <c r="F32" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>43</v>
       </c>
       <c r="B33" t="s">
+        <v>334</v>
+      </c>
+      <c r="C33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D33" t="s">
+        <v>335</v>
+      </c>
+      <c r="E33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" t="s">
         <v>336</v>
       </c>
-      <c r="C33" t="s">
-        <v>317</v>
-      </c>
-      <c r="D33" t="s">
-        <v>337</v>
-      </c>
-      <c r="E33" t="s">
-        <v>191</v>
-      </c>
-      <c r="F33" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>43</v>
       </c>
       <c r="B34" t="s">
+        <v>337</v>
+      </c>
+      <c r="C34" t="s">
+        <v>317</v>
+      </c>
+      <c r="D34" t="s">
+        <v>338</v>
+      </c>
+      <c r="E34" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" t="s">
         <v>339</v>
       </c>
-      <c r="C34" t="s">
-        <v>319</v>
-      </c>
-      <c r="D34" t="s">
-        <v>340</v>
-      </c>
-      <c r="E34" t="s">
-        <v>191</v>
-      </c>
-      <c r="F34" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D35" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F35" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>46</v>
       </c>
       <c r="B36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" t="s">
         <v>188</v>
       </c>
-      <c r="C36" t="s">
-        <v>189</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>189</v>
+      </c>
+      <c r="F36" t="s">
         <v>190</v>
       </c>
-      <c r="E36" t="s">
-        <v>191</v>
-      </c>
-      <c r="F36" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>46</v>
       </c>
       <c r="B37" t="s">
+        <v>191</v>
+      </c>
+      <c r="C37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" t="s">
+        <v>192</v>
+      </c>
+      <c r="E37" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" t="s">
         <v>193</v>
       </c>
-      <c r="C37" t="s">
-        <v>189</v>
-      </c>
-      <c r="D37" t="s">
-        <v>194</v>
-      </c>
-      <c r="E37" t="s">
-        <v>191</v>
-      </c>
-      <c r="F37" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>46</v>
       </c>
       <c r="B38" t="s">
+        <v>194</v>
+      </c>
+      <c r="C38" t="s">
+        <v>187</v>
+      </c>
+      <c r="D38" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" t="s">
         <v>196</v>
       </c>
-      <c r="C38" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" t="s">
-        <v>197</v>
-      </c>
-      <c r="E38" t="s">
-        <v>191</v>
-      </c>
-      <c r="F38" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C39" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D39" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E39" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C40" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D40" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F40" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C41" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E41" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F41" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E42" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F42" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>49</v>
       </c>
       <c r="B43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" t="s">
         <v>188</v>
       </c>
-      <c r="C43" t="s">
-        <v>189</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" t="s">
         <v>190</v>
       </c>
-      <c r="E43" t="s">
-        <v>191</v>
-      </c>
-      <c r="F43" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" t="s">
+        <v>192</v>
+      </c>
+      <c r="E44" t="s">
+        <v>189</v>
+      </c>
+      <c r="F44" t="s">
         <v>193</v>
       </c>
-      <c r="C44" t="s">
-        <v>189</v>
-      </c>
-      <c r="D44" t="s">
-        <v>194</v>
-      </c>
-      <c r="E44" t="s">
-        <v>191</v>
-      </c>
-      <c r="F44" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
+        <v>194</v>
+      </c>
+      <c r="C45" t="s">
+        <v>187</v>
+      </c>
+      <c r="D45" t="s">
+        <v>195</v>
+      </c>
+      <c r="E45" t="s">
+        <v>189</v>
+      </c>
+      <c r="F45" t="s">
         <v>196</v>
       </c>
-      <c r="C45" t="s">
-        <v>189</v>
-      </c>
-      <c r="D45" t="s">
-        <v>197</v>
-      </c>
-      <c r="E45" t="s">
-        <v>191</v>
-      </c>
-      <c r="F45" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C46" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D46" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E46" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F46" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C47" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D47" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F47" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C48" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D48" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E48" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F48" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C49" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D49" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F49" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C50" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D50" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E50" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F50" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C51" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D51" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F51" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C52" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D52" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E52" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F52" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C53" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D53" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E53" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F53" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C54" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D54" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E54" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F54" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C55" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D55" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E55" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F55" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C56" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D56" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E56" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F56" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>54</v>
       </c>
       <c r="B57" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" t="s">
         <v>188</v>
       </c>
-      <c r="C57" t="s">
-        <v>189</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
+        <v>189</v>
+      </c>
+      <c r="F57" t="s">
         <v>190</v>
       </c>
-      <c r="E57" t="s">
-        <v>191</v>
-      </c>
-      <c r="F57" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>54</v>
       </c>
       <c r="B58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C58" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E58" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" t="s">
         <v>193</v>
       </c>
-      <c r="C58" t="s">
-        <v>189</v>
-      </c>
-      <c r="D58" t="s">
-        <v>194</v>
-      </c>
-      <c r="E58" t="s">
-        <v>191</v>
-      </c>
-      <c r="F58" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>54</v>
       </c>
       <c r="B59" t="s">
+        <v>194</v>
+      </c>
+      <c r="C59" t="s">
+        <v>187</v>
+      </c>
+      <c r="D59" t="s">
+        <v>195</v>
+      </c>
+      <c r="E59" t="s">
+        <v>189</v>
+      </c>
+      <c r="F59" t="s">
         <v>196</v>
       </c>
-      <c r="C59" t="s">
-        <v>189</v>
-      </c>
-      <c r="D59" t="s">
-        <v>197</v>
-      </c>
-      <c r="E59" t="s">
-        <v>191</v>
-      </c>
-      <c r="F59" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C60" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D60" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E60" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F60" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>54</v>
       </c>
       <c r="B61" t="s">
+        <v>358</v>
+      </c>
+      <c r="C61" t="s">
+        <v>320</v>
+      </c>
+      <c r="D61" t="s">
+        <v>359</v>
+      </c>
+      <c r="E61" t="s">
+        <v>189</v>
+      </c>
+      <c r="F61" t="s">
         <v>360</v>
       </c>
-      <c r="C61" t="s">
-        <v>322</v>
-      </c>
-      <c r="D61" t="s">
-        <v>361</v>
-      </c>
-      <c r="E61" t="s">
-        <v>191</v>
-      </c>
-      <c r="F61" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C62" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D62" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E62" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F62" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>58</v>
       </c>
       <c r="B63" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" t="s">
         <v>188</v>
       </c>
-      <c r="C63" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
+        <v>189</v>
+      </c>
+      <c r="F63" t="s">
         <v>190</v>
       </c>
-      <c r="E63" t="s">
-        <v>191</v>
-      </c>
-      <c r="F63" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>58</v>
       </c>
       <c r="B64" t="s">
+        <v>191</v>
+      </c>
+      <c r="C64" t="s">
+        <v>187</v>
+      </c>
+      <c r="D64" t="s">
+        <v>192</v>
+      </c>
+      <c r="E64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F64" t="s">
         <v>193</v>
       </c>
-      <c r="C64" t="s">
-        <v>189</v>
-      </c>
-      <c r="D64" t="s">
-        <v>194</v>
-      </c>
-      <c r="E64" t="s">
-        <v>191</v>
-      </c>
-      <c r="F64" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>58</v>
       </c>
       <c r="B65" t="s">
+        <v>194</v>
+      </c>
+      <c r="C65" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65" t="s">
+        <v>195</v>
+      </c>
+      <c r="E65" t="s">
+        <v>189</v>
+      </c>
+      <c r="F65" t="s">
         <v>196</v>
       </c>
-      <c r="C65" t="s">
-        <v>189</v>
-      </c>
-      <c r="D65" t="s">
-        <v>197</v>
-      </c>
-      <c r="E65" t="s">
-        <v>191</v>
-      </c>
-      <c r="F65" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>58</v>
       </c>
       <c r="B66" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C66" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D66" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E66" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F66" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>58</v>
       </c>
       <c r="B67" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C67" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D67" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E67" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F67" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>58</v>
       </c>
       <c r="B68" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C68" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D68" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E68" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F68" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>58</v>
       </c>
       <c r="B69" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C69" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D69" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E69" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F69" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>62</v>
       </c>
       <c r="B70" t="s">
+        <v>186</v>
+      </c>
+      <c r="C70" t="s">
+        <v>187</v>
+      </c>
+      <c r="D70" t="s">
         <v>188</v>
       </c>
-      <c r="C70" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
+        <v>189</v>
+      </c>
+      <c r="F70" t="s">
         <v>190</v>
       </c>
-      <c r="E70" t="s">
-        <v>191</v>
-      </c>
-      <c r="F70" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>62</v>
       </c>
       <c r="B71" t="s">
+        <v>191</v>
+      </c>
+      <c r="C71" t="s">
+        <v>187</v>
+      </c>
+      <c r="D71" t="s">
+        <v>192</v>
+      </c>
+      <c r="E71" t="s">
+        <v>189</v>
+      </c>
+      <c r="F71" t="s">
         <v>193</v>
       </c>
-      <c r="C71" t="s">
-        <v>189</v>
-      </c>
-      <c r="D71" t="s">
-        <v>194</v>
-      </c>
-      <c r="E71" t="s">
-        <v>191</v>
-      </c>
-      <c r="F71" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>62</v>
       </c>
       <c r="B72" t="s">
+        <v>194</v>
+      </c>
+      <c r="C72" t="s">
+        <v>187</v>
+      </c>
+      <c r="D72" t="s">
+        <v>195</v>
+      </c>
+      <c r="E72" t="s">
+        <v>189</v>
+      </c>
+      <c r="F72" t="s">
         <v>196</v>
       </c>
-      <c r="C72" t="s">
-        <v>189</v>
-      </c>
-      <c r="D72" t="s">
-        <v>197</v>
-      </c>
-      <c r="E72" t="s">
-        <v>191</v>
-      </c>
-      <c r="F72" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>62</v>
       </c>
       <c r="B73" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C73" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E73" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F73" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>62</v>
       </c>
       <c r="B74" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C74" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D74" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E74" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F74" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>62</v>
       </c>
       <c r="B75" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C75" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D75" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E75" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F75" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>62</v>
       </c>
       <c r="B76" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C76" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D76" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E76" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F76" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>62</v>
       </c>
       <c r="B77" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C77" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D77" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E77" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F77" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>62</v>
       </c>
       <c r="B78" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C78" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D78" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E78" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F78" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>62</v>
       </c>
       <c r="B79" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C79" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D79" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E79" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F79" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>65</v>
       </c>
       <c r="B80" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" t="s">
+        <v>187</v>
+      </c>
+      <c r="D80" t="s">
         <v>188</v>
       </c>
-      <c r="C80" t="s">
-        <v>189</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
+        <v>189</v>
+      </c>
+      <c r="F80" t="s">
         <v>190</v>
       </c>
-      <c r="E80" t="s">
-        <v>191</v>
-      </c>
-      <c r="F80" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>65</v>
       </c>
       <c r="B81" t="s">
+        <v>191</v>
+      </c>
+      <c r="C81" t="s">
+        <v>187</v>
+      </c>
+      <c r="D81" t="s">
+        <v>192</v>
+      </c>
+      <c r="E81" t="s">
+        <v>189</v>
+      </c>
+      <c r="F81" t="s">
         <v>193</v>
       </c>
-      <c r="C81" t="s">
-        <v>189</v>
-      </c>
-      <c r="D81" t="s">
-        <v>194</v>
-      </c>
-      <c r="E81" t="s">
-        <v>191</v>
-      </c>
-      <c r="F81" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>65</v>
       </c>
       <c r="B82" t="s">
+        <v>194</v>
+      </c>
+      <c r="C82" t="s">
+        <v>187</v>
+      </c>
+      <c r="D82" t="s">
+        <v>195</v>
+      </c>
+      <c r="E82" t="s">
+        <v>189</v>
+      </c>
+      <c r="F82" t="s">
         <v>196</v>
       </c>
-      <c r="C82" t="s">
-        <v>189</v>
-      </c>
-      <c r="D82" t="s">
-        <v>197</v>
-      </c>
-      <c r="E82" t="s">
-        <v>191</v>
-      </c>
-      <c r="F82" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C83" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E83" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F83" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C84" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D84" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E84" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F84" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>65</v>
       </c>
       <c r="B85" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C85" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D85" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E85" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F85" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>65</v>
       </c>
       <c r="B86" t="s">
+        <v>337</v>
+      </c>
+      <c r="C86" t="s">
+        <v>317</v>
+      </c>
+      <c r="D86" t="s">
+        <v>338</v>
+      </c>
+      <c r="E86" t="s">
+        <v>189</v>
+      </c>
+      <c r="F86" t="s">
         <v>339</v>
       </c>
-      <c r="C86" t="s">
-        <v>319</v>
-      </c>
-      <c r="D86" t="s">
-        <v>340</v>
-      </c>
-      <c r="E86" t="s">
-        <v>191</v>
-      </c>
-      <c r="F86" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C87" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D87" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E87" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F87" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -5228,412 +5246,416 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>175</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s">
         <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B3" t="s">
         <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" t="s">
         <v>305</v>
       </c>
-      <c r="B4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B5" t="s">
-        <v>307</v>
-      </c>
       <c r="C5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" t="s">
         <v>312</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B10" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>305</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>303</v>
+      </c>
+      <c r="B11" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>303</v>
+      </c>
+      <c r="B12" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>303</v>
+      </c>
+      <c r="B13" t="s">
+        <v>378</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" t="s">
+        <v>393</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" t="s">
+        <v>379</v>
+      </c>
+      <c r="C15" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>303</v>
+      </c>
+      <c r="B16" t="s">
+        <v>380</v>
+      </c>
+      <c r="C16" t="s">
         <v>314</v>
       </c>
-      <c r="C9" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>305</v>
-      </c>
-      <c r="B10" t="s">
-        <v>315</v>
-      </c>
-      <c r="C10" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B11" t="s">
-        <v>378</v>
-      </c>
-      <c r="C11" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>305</v>
-      </c>
-      <c r="B12" t="s">
-        <v>379</v>
-      </c>
-      <c r="C12" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>305</v>
-      </c>
-      <c r="B13" t="s">
-        <v>380</v>
-      </c>
-      <c r="C13" s="25" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>303</v>
+      </c>
+      <c r="B17" t="s">
+        <v>389</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>303</v>
+      </c>
+      <c r="B18" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>305</v>
-      </c>
-      <c r="B14" t="s">
-        <v>395</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>305</v>
-      </c>
-      <c r="B15" t="s">
-        <v>381</v>
-      </c>
-      <c r="C15" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>305</v>
-      </c>
-      <c r="B16" t="s">
-        <v>382</v>
-      </c>
-      <c r="C16" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>305</v>
-      </c>
-      <c r="B17" t="s">
-        <v>391</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>305</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" s="25" t="s">
         <v>392</v>
       </c>
-      <c r="C18" s="25" t="s">
-        <v>394</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C11" r:id="rId1" xr:uid="{ED2947B3-22B5-4017-9D41-D9E500DC9A78}"/>
+    <hyperlink ref="C12" r:id="rId2" xr:uid="{81425CE6-26E3-4568-A6B3-E280EB7017B0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="103.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="103.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B2" t="s">
         <v>286</v>
       </c>
-      <c r="C1" s="22" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>287</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>288</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>290</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
         <v>291</v>
       </c>
-      <c r="C3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>292</v>
       </c>
-      <c r="B4" t="s">
-        <v>288</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>294</v>
       </c>
-      <c r="B5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>296</v>
       </c>
-      <c r="B6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>298</v>
       </c>
-      <c r="B7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>300</v>
       </c>
-      <c r="B8" t="s">
-        <v>288</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>302</v>
-      </c>
-      <c r="B9" t="s">
-        <v>288</v>
-      </c>
-      <c r="C9" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>317</v>
       </c>
-      <c r="B10" t="s">
-        <v>291</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C11" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" t="s">
         <v>319</v>
       </c>
-      <c r="B11" t="s">
-        <v>291</v>
-      </c>
-      <c r="C11" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>320</v>
       </c>
-      <c r="B12" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>322</v>
       </c>
-      <c r="B13" t="s">
-        <v>291</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>324</v>
       </c>
-      <c r="B14" t="s">
-        <v>288</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C15" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>326</v>
       </c>
-      <c r="B15" t="s">
-        <v>291</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C16" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>328</v>
       </c>
-      <c r="B16" t="s">
-        <v>291</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>330</v>
-      </c>
-      <c r="B17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C17" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -5649,19 +5671,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I61"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="4"/>
-    <col min="2" max="2" width="25.44140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="47.44140625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="52.77734375" style="4" customWidth="1"/>
-    <col min="5" max="7" width="14.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="37.44140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="12.6640625" style="4"/>
+    <col min="1" max="1" width="12.6328125" style="4"/>
+    <col min="2" max="2" width="25.453125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="47.453125" style="20" customWidth="1"/>
+    <col min="4" max="4" width="52.81640625" style="4" customWidth="1"/>
+    <col min="5" max="7" width="14.36328125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="37.453125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="17.08984375" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="12.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -5749,7 +5771,7 @@
       </c>
       <c r="I3" s="17"/>
     </row>
-    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
@@ -5778,7 +5800,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="40.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
@@ -5786,7 +5808,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>16</v>
@@ -5803,13 +5825,13 @@
       <c r="H5" s="8"/>
       <c r="I5" s="18"/>
     </row>
-    <row r="6" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>19</v>
@@ -5826,13 +5848,13 @@
       <c r="H6" s="8"/>
       <c r="I6" s="18"/>
     </row>
-    <row r="7" spans="1:9" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="78.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>21</v>
@@ -5849,16 +5871,16 @@
       <c r="H7" s="8"/>
       <c r="I7" s="18"/>
     </row>
-    <row r="8" spans="1:9" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="94.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>23</v>
@@ -5874,7 +5896,7 @@
       </c>
       <c r="I8" s="18"/>
     </row>
-    <row r="9" spans="1:9" ht="117.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="117.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
@@ -5897,7 +5919,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="18"/>
     </row>
-    <row r="10" spans="1:9" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="98.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>28</v>
       </c>
@@ -5922,7 +5944,7 @@
       </c>
       <c r="I10" s="18"/>
     </row>
-    <row r="11" spans="1:9" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="58.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
         <v>31</v>
       </c>
@@ -5947,7 +5969,7 @@
       </c>
       <c r="I11" s="18"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
@@ -5958,7 +5980,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>17</v>
@@ -5974,7 +5996,7 @@
       </c>
       <c r="I12" s="18"/>
     </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
         <v>39</v>
       </c>
@@ -5997,7 +6019,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="18"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>43</v>
       </c>
@@ -6020,7 +6042,7 @@
       <c r="H14" s="8"/>
       <c r="I14" s="18"/>
     </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>46</v>
       </c>
@@ -6043,7 +6065,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="18"/>
     </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>49</v>
       </c>
@@ -6068,7 +6090,7 @@
       </c>
       <c r="I16" s="18"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>54</v>
       </c>
@@ -6093,7 +6115,7 @@
       </c>
       <c r="I17" s="18"/>
     </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>58</v>
       </c>
@@ -6118,7 +6140,7 @@
       </c>
       <c r="I18" s="18"/>
     </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>62</v>
       </c>
@@ -6143,13 +6165,13 @@
       </c>
       <c r="I19" s="18"/>
     </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>66</v>
@@ -6166,7 +6188,7 @@
       <c r="H20" s="8"/>
       <c r="I20" s="18"/>
     </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
         <v>67</v>
       </c>
@@ -6191,7 +6213,7 @@
       <c r="H21" s="8"/>
       <c r="I21" s="18"/>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
         <v>71</v>
       </c>
@@ -6214,7 +6236,7 @@
       <c r="H22" s="8"/>
       <c r="I22" s="18"/>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
         <v>74</v>
       </c>
@@ -6239,7 +6261,7 @@
       </c>
       <c r="I23" s="18"/>
     </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
         <v>77</v>
       </c>
@@ -6264,7 +6286,7 @@
       </c>
       <c r="I24" s="18"/>
     </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>80</v>
       </c>
@@ -6287,7 +6309,7 @@
       <c r="H25" s="8"/>
       <c r="I25" s="18"/>
     </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
         <v>83</v>
       </c>
@@ -6312,7 +6334,7 @@
       </c>
       <c r="I26" s="18"/>
     </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
         <v>87</v>
       </c>
@@ -6337,7 +6359,7 @@
       </c>
       <c r="I27" s="18"/>
     </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
         <v>91</v>
       </c>
@@ -6362,7 +6384,7 @@
       <c r="H28" s="8"/>
       <c r="I28" s="18"/>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>95</v>
       </c>
@@ -6385,7 +6407,7 @@
       <c r="H29" s="8"/>
       <c r="I29" s="18"/>
     </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
         <v>98</v>
       </c>
@@ -6408,7 +6430,7 @@
       <c r="H30" s="8"/>
       <c r="I30" s="18"/>
     </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8" t="s">
         <v>101</v>
       </c>
@@ -6433,7 +6455,7 @@
       <c r="H31" s="8"/>
       <c r="I31" s="18"/>
     </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>105</v>
       </c>
@@ -6456,7 +6478,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="18"/>
     </row>
-    <row r="33" spans="1:9" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>107</v>
       </c>
@@ -6479,7 +6501,7 @@
       <c r="H33" s="8"/>
       <c r="I33" s="18"/>
     </row>
-    <row r="34" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="56.5" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>109</v>
       </c>
@@ -6504,7 +6526,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="18"/>
     </row>
-    <row r="35" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>113</v>
       </c>
@@ -6527,7 +6549,7 @@
       <c r="H35" s="8"/>
       <c r="I35" s="18"/>
     </row>
-    <row r="36" spans="1:9" ht="97.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="98.5" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>116</v>
       </c>
@@ -6552,7 +6574,7 @@
       </c>
       <c r="I36" s="18"/>
     </row>
-    <row r="37" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>119</v>
       </c>
@@ -6577,7 +6599,7 @@
       </c>
       <c r="I37" s="18"/>
     </row>
-    <row r="38" spans="1:9" ht="152.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="154.5" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>122</v>
       </c>
@@ -6604,7 +6626,7 @@
       </c>
       <c r="I38" s="18"/>
     </row>
-    <row r="39" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="56.5" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>126</v>
       </c>
@@ -6627,7 +6649,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="18"/>
     </row>
-    <row r="40" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="56.5" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>129</v>
       </c>
@@ -6652,7 +6674,7 @@
       </c>
       <c r="I40" s="18"/>
     </row>
-    <row r="41" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>132</v>
       </c>
@@ -6677,7 +6699,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="18"/>
     </row>
-    <row r="42" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>136</v>
       </c>
@@ -6700,7 +6722,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="18"/>
     </row>
-    <row r="43" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>139</v>
       </c>
@@ -6723,7 +6745,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="18"/>
     </row>
-    <row r="44" spans="1:9" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="70.5" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>142</v>
       </c>
@@ -6748,7 +6770,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="18"/>
     </row>
-    <row r="45" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A45" s="8" t="s">
         <v>146</v>
       </c>
@@ -6771,7 +6793,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="18"/>
     </row>
-    <row r="46" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>149</v>
       </c>
@@ -6796,7 +6818,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="18"/>
     </row>
-    <row r="47" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A47" s="8" t="s">
         <v>153</v>
       </c>
@@ -6821,7 +6843,7 @@
       </c>
       <c r="I47" s="18"/>
     </row>
-    <row r="48" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="56.5" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
         <v>155</v>
       </c>
@@ -6844,7 +6866,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="18"/>
     </row>
-    <row r="49" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
         <v>158</v>
       </c>
@@ -6869,7 +6891,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="18"/>
     </row>
-    <row r="50" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
         <v>162</v>
       </c>
@@ -6894,7 +6916,7 @@
       </c>
       <c r="I50" s="18"/>
     </row>
-    <row r="51" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="28.5" x14ac:dyDescent="0.35">
       <c r="A51" s="8" t="s">
         <v>165</v>
       </c>
@@ -6917,7 +6939,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="18"/>
     </row>
-    <row r="52" spans="1:9" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="56.5" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
         <v>167</v>
       </c>
@@ -6944,7 +6966,7 @@
       </c>
       <c r="I52" s="19"/>
     </row>
-    <row r="53" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A53" s="8" t="s">
         <v>172</v>
       </c>
@@ -6967,7 +6989,7 @@
       <c r="H53" s="13"/>
       <c r="I53" s="19"/>
     </row>
-    <row r="54" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="6"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -6978,7 +7000,7 @@
       <c r="H54" s="13"/>
       <c r="I54" s="15"/>
     </row>
-    <row r="55" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="6"/>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -6989,7 +7011,7 @@
       <c r="H55" s="13"/>
       <c r="I55" s="15"/>
     </row>
-    <row r="56" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="6"/>
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
@@ -7000,7 +7022,7 @@
       <c r="H56" s="13"/>
       <c r="I56" s="15"/>
     </row>
-    <row r="57" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="6"/>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
@@ -7011,7 +7033,7 @@
       <c r="H57" s="13"/>
       <c r="I57" s="15"/>
     </row>
-    <row r="58" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="6"/>
       <c r="B58" s="13"/>
       <c r="C58" s="13"/>
@@ -7022,7 +7044,7 @@
       <c r="H58" s="13"/>
       <c r="I58" s="15"/>
     </row>
-    <row r="59" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
@@ -7033,7 +7055,7 @@
       <c r="H59" s="13"/>
       <c r="I59" s="15"/>
     </row>
-    <row r="60" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="6"/>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -7044,7 +7066,7 @@
       <c r="H60" s="13"/>
       <c r="I60" s="15"/>
     </row>
-    <row r="61" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="16"/>
       <c r="B61" s="13"/>
       <c r="C61" s="13"/>

--- a/src/test/resources/Login_TC.xlsx
+++ b/src/test/resources/Login_TC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\automation-framework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E963ED1-0004-4663-AD82-CC47B3F55968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F2ACCE-9713-477C-AEA0-B2256484BF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="422">
   <si>
     <t>Created Date: 20/05/2025</t>
   </si>
@@ -1096,12 +1096,6 @@
     <t>Value</t>
   </si>
   <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
     <t>chivq9@fpt.com</t>
   </si>
   <si>
@@ -1255,9 +1249,6 @@
     <t>loginwithmicrosoft</t>
   </si>
   <si>
-    <t>${email}|${password}</t>
-  </si>
-  <si>
     <t>SSO login</t>
   </si>
   <si>
@@ -1379,9 +1370,6 @@
   </si>
   <si>
     <t>Đăng nhập tài khoản đã có Mã Bảo mật - Kiểm tra Giới hạn nhập mã PIN</t>
-  </si>
-  <si>
-    <t>BE: Lỗi cộng dồn 5 lần nhập fail</t>
   </si>
   <si>
     <t>Đăng nhập tài khoản đã có Mã Bảo mật - Đăng nhập bằng SSO - Upload mã QR Pin thành công</t>
@@ -1592,12 +1580,6 @@
     <t>GLOBAL</t>
   </si>
   <si>
-    <t>passphrase</t>
-  </si>
-  <si>
-    <t>microsoftOtp</t>
-  </si>
-  <si>
     <t>Autotest send message PK-005</t>
   </si>
   <si>
@@ -1704,9 +1686,6 @@
     <t>Hội thoại|Tin nhắn|Chat|Chats|Conversation|Search|Message</t>
   </si>
   <si>
-    <t>${wrongPassphrase}</t>
-  </si>
-  <si>
     <t>Enter invalid passphrase</t>
   </si>
   <si>
@@ -1746,12 +1725,6 @@
     <t>Submit invalid PIN attempt 5</t>
   </si>
   <si>
-    <t>temporarily locked|tạm khóa|tạm khoá|vui lòng thử lại|5 attempts|attempts remaining</t>
-  </si>
-  <si>
-    <t>Account lock/attempt limit message should be displayed</t>
-  </si>
-  <si>
     <t>Switch to QR login screen</t>
   </si>
   <si>
@@ -1794,12 +1767,6 @@
     <t>Invalid QR upload attempt 5</t>
   </si>
   <si>
-    <t>temporarily locked|tạm khóa|tạm khoá|vui lòng thử lại|5 attempts|attempts remaining|QR Code  is incorrect, please try again!|QR Code is incorrect|please try again</t>
-  </si>
-  <si>
-    <t>QR upload limit/lock message should be displayed</t>
-  </si>
-  <si>
     <t>Open forgot code flow</t>
   </si>
   <si>
@@ -1824,65 +1791,161 @@
     <t>secure.qrInvalidPath</t>
   </si>
   <si>
-    <t>${secure.email}</t>
-  </si>
-  <si>
-    <t>${secure.password}</t>
+    <t>${secure.qrValidPath}</t>
+  </si>
+  <si>
+    <t>${secure.qrInvalidPath}</t>
+  </si>
+  <si>
+    <t>src\test\resources\QR login\Chivq9_UAT_QR.png</t>
+  </si>
+  <si>
+    <t>Fptchat@1234</t>
+  </si>
+  <si>
+    <t>nonSecure.email</t>
+  </si>
+  <si>
+    <t>nonSecure.password</t>
+  </si>
+  <si>
+    <t>fptchat01@fpt.com</t>
+  </si>
+  <si>
+    <t>Devteam@1234562</t>
+  </si>
+  <si>
+    <t>secure.InvalidPassphrase</t>
+  </si>
+  <si>
+    <t>Invalid@1234</t>
+  </si>
+  <si>
+    <t>${secure.InvalidPassphrase}</t>
+  </si>
+  <si>
+    <t>Skipped: message text assertion is more stable than SVG icon assertion</t>
+  </si>
+  <si>
+    <t>PIN code is incorrect|Pin code is incorrect|attempts remaining|incorrect|khÃ´ng Ä‘Ãºng|khÃ´ng há»£p lá»‡|MÃ£ báº£o máº­t</t>
+  </si>
+  <si>
+    <t>//button[@type='button' and (.//span[normalize-space()='Gửi' or normalize-space()='Send'] or normalize-space()='Gửi' or normalize-space()='Send')]</t>
+  </si>
+  <si>
+    <t>${nonSecure.email}|${nonSecure.password}</t>
+  </si>
+  <si>
+    <t>nonSecure.account</t>
+  </si>
+  <si>
+    <t>fptchat01</t>
+  </si>
+  <si>
+    <t>chivq9</t>
+  </si>
+  <si>
+    <t>${secure.email}|${secure.password}</t>
   </si>
   <si>
     <t>${secure.passphrase}</t>
   </si>
   <si>
-    <t>${secure.qrValidPath}</t>
-  </si>
-  <si>
-    <t>${secure.qrInvalidPath}</t>
-  </si>
-  <si>
-    <t>${nonSecure.account}</t>
-  </si>
-  <si>
-    <t>src\test\resources\QR login\Chivq9_UAT_QR.png</t>
-  </si>
-  <si>
-    <t>Fptchat@1234</t>
-  </si>
-  <si>
-    <t>nonSecure.email</t>
-  </si>
-  <si>
-    <t>nonSecure.password</t>
-  </si>
-  <si>
-    <t>fptchat01@fpt.com</t>
-  </si>
-  <si>
-    <t>Devteam@1234562</t>
-  </si>
-  <si>
-    <t>secure.InvalidPassphrase</t>
-  </si>
-  <si>
-    <t>Invalid@1234</t>
-  </si>
-  <si>
-    <t>${secure.InvalidPassphrase}</t>
-  </si>
-  <si>
-    <t>Skipped: message text assertion is more stable than SVG icon assertion</t>
-  </si>
-  <si>
-    <t>PIN code is incorrect|Pin code is incorrect|attempts remaining|incorrect|khÃ´ng Ä‘Ãºng|khÃ´ng há»£p lá»‡|MÃ£ báº£o máº­t</t>
-  </si>
-  <si>
-    <t>//button[@type='button' and (.//span[normalize-space()='Gửi' or normalize-space()='Send'] or normalize-space()='Gửi' or normalize-space()='Send')]</t>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>You have entered the wrong PIN too many times. Please try again in 60 minutes.</t>
+  </si>
+  <si>
+    <t>After exactly 5 invalid PIN submissions, lock message must be displayed</t>
+  </si>
+  <si>
+    <t>1 attempts remaining|1 attempt remaining</t>
+  </si>
+  <si>
+    <t>After invalid PIN attempt 4</t>
+  </si>
+  <si>
+    <t>2 attempts remaining</t>
+  </si>
+  <si>
+    <t>After invalid PIN attempt 3</t>
+  </si>
+  <si>
+    <t>3 attempts remaining</t>
+  </si>
+  <si>
+    <t>After invalid PIN attempt 2</t>
+  </si>
+  <si>
+    <t>4 attempts remaining</t>
+  </si>
+  <si>
+    <t>After invalid PIN attempt 1</t>
+  </si>
+  <si>
+    <t>Nhập sai mã PIN 5 lần, mỗi lần hiển thị số attempts remaining giảm dần 4 &gt; 3 &gt; 2 &gt; 1, sau lần thứ 5 hiển thị message khóa 60 phút.</t>
+  </si>
+  <si>
+    <t>Verify đúng sequence lỗi nhập sai PIN và message lock sau 5 lần</t>
+  </si>
+  <si>
+    <t>security.qrDeleteButton</t>
+  </si>
+  <si>
+    <t>(//*[local-name()='svg' and @viewBox='0 0 24 24' and .//*[local-name()='path' and contains(@d,'M16 8') and contains(@d,'L16 16')]]/ancestor::*[self::button or @role='button' or contains(@class,'cursor-pointer')][1] | //*[local-name()='svg' and @viewBox='0 0 24 24' and .//*[local-name()='path' and contains(@d,'M16 8') and contains(@d,'L16 16')]])[1]</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 1</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 1</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 2</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 2</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 3</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 3</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 4</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 4</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 5</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 5</t>
+  </si>
+  <si>
+    <t>Invalid QR upload attempt 6</t>
+  </si>
+  <si>
+    <t>Bạn đã nhập sai mã PIN quá số lần cho phép. Vui lòng thử lại sau</t>
+  </si>
+  <si>
+    <t>After attempt 6, QR PIN limit message should be displayed</t>
+  </si>
+  <si>
+    <t>Upload QR sai 5 lần: mỗi lần hiển thị lỗi QR và cho phép xóa ảnh để upload lại. Lần upload sai thứ 6 hiển thị message: Bạn đã nhập sai mã PIN quá số lần cho phép. Vui lòng thử lại sau</t>
+  </si>
+  <si>
+    <t>Verify giới hạn upload QR sai: xóa QR giữa các lần upload, lock ở lần thứ 6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1963,6 +2026,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2064,7 +2134,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2129,6 +2199,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2469,10 +2543,10 @@
         <v>175</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>11</v>
@@ -2489,10 +2563,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -2501,7 +2575,7 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2509,10 +2583,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -2521,7 +2595,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2529,10 +2603,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -2541,27 +2615,27 @@
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B5" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
-        <v>228</v>
+      <c r="F5" s="26" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2569,10 +2643,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C6" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -2581,46 +2655,46 @@
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="26" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="C8" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="F8" s="26" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2629,36 +2703,36 @@
         <v>35</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:6" s="26" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="C10" t="s">
-        <v>227</v>
-      </c>
-      <c r="D10" s="24" t="s">
+      <c r="B10" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F10" t="s">
-        <v>189</v>
+      <c r="F10" s="26" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2666,10 +2740,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>45</v>
@@ -2678,7 +2752,7 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2686,10 +2760,10 @@
         <v>46</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>48</v>
@@ -2698,27 +2772,27 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="C13" t="s">
-        <v>227</v>
-      </c>
-      <c r="D13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" t="s">
-        <v>236</v>
+      <c r="B13" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2726,10 +2800,10 @@
         <v>54</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>56</v>
@@ -2746,10 +2820,10 @@
         <v>58</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>60</v>
@@ -2758,38 +2832,38 @@
         <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="C16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B16" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>66</v>
@@ -2798,27 +2872,27 @@
         <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
-        <v>227</v>
-      </c>
-      <c r="D18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2826,10 +2900,10 @@
         <v>71</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D19" t="s">
         <v>73</v>
@@ -2838,7 +2912,7 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2846,10 +2920,10 @@
         <v>74</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -2866,10 +2940,10 @@
         <v>77</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -2886,10 +2960,10 @@
         <v>80</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C22" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D22" t="s">
         <v>82</v>
@@ -2898,7 +2972,7 @@
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2906,19 +2980,19 @@
         <v>83</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C23" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D23" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2926,10 +3000,10 @@
         <v>87</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C24" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D24" t="s">
         <v>89</v>
@@ -2938,7 +3012,7 @@
         <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2946,10 +3020,10 @@
         <v>91</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C25" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D25" t="s">
         <v>94</v>
@@ -2958,7 +3032,7 @@
         <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2966,10 +3040,10 @@
         <v>95</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C26" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -2978,7 +3052,7 @@
         <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2986,10 +3060,10 @@
         <v>98</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D27" t="s">
         <v>100</v>
@@ -2998,7 +3072,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -3006,10 +3080,10 @@
         <v>101</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C28" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D28" t="s">
         <v>104</v>
@@ -3018,7 +3092,7 @@
         <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -3026,10 +3100,10 @@
         <v>105</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C29" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D29" t="s">
         <v>104</v>
@@ -3038,7 +3112,7 @@
         <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3046,10 +3120,10 @@
         <v>107</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C30" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D30" t="s">
         <v>104</v>
@@ -3058,7 +3132,7 @@
         <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3066,10 +3140,10 @@
         <v>109</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C31" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D31" t="s">
         <v>112</v>
@@ -3078,7 +3152,7 @@
         <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3086,10 +3160,10 @@
         <v>113</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C32" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D32" t="s">
         <v>115</v>
@@ -3098,7 +3172,7 @@
         <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3106,10 +3180,10 @@
         <v>116</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C33" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D33" t="s">
         <v>118</v>
@@ -3118,7 +3192,7 @@
         <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3126,10 +3200,10 @@
         <v>119</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C34" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D34" t="s">
         <v>121</v>
@@ -3138,7 +3212,7 @@
         <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3146,10 +3220,10 @@
         <v>122</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C35" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D35" t="s">
         <v>125</v>
@@ -3166,10 +3240,10 @@
         <v>126</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C36" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D36" t="s">
         <v>128</v>
@@ -3178,7 +3252,7 @@
         <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3186,10 +3260,10 @@
         <v>129</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D37" t="s">
         <v>131</v>
@@ -3198,7 +3272,7 @@
         <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3206,10 +3280,10 @@
         <v>132</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C38" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D38" t="s">
         <v>135</v>
@@ -3218,7 +3292,7 @@
         <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -3226,10 +3300,10 @@
         <v>136</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C39" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D39" t="s">
         <v>138</v>
@@ -3238,7 +3312,7 @@
         <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3246,10 +3320,10 @@
         <v>139</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D40" t="s">
         <v>141</v>
@@ -3258,7 +3332,7 @@
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -3266,10 +3340,10 @@
         <v>142</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C41" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D41" t="s">
         <v>145</v>
@@ -3278,7 +3352,7 @@
         <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -3286,10 +3360,10 @@
         <v>146</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D42" t="s">
         <v>148</v>
@@ -3298,7 +3372,7 @@
         <v>42</v>
       </c>
       <c r="F42" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -3306,19 +3380,19 @@
         <v>149</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D43" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3326,10 +3400,10 @@
         <v>153</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D44" t="s">
         <v>76</v>
@@ -3346,10 +3420,10 @@
         <v>155</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C45" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D45" t="s">
         <v>157</v>
@@ -3358,7 +3432,7 @@
         <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3366,10 +3440,10 @@
         <v>158</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C46" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D46" t="s">
         <v>161</v>
@@ -3378,7 +3452,7 @@
         <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3386,10 +3460,10 @@
         <v>162</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D47" t="s">
         <v>161</v>
@@ -3406,10 +3480,10 @@
         <v>165</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C48" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D48" t="s">
         <v>161</v>
@@ -3418,7 +3492,7 @@
         <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3426,19 +3500,19 @@
         <v>167</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C49" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D49" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E49" t="s">
         <v>52</v>
       </c>
       <c r="F49" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3446,30 +3520,31 @@
         <v>172</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C50" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D50" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="C1:C50" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -3485,19 +3560,19 @@
         <v>175</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -3505,19 +3580,19 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" t="s">
         <v>188</v>
       </c>
-      <c r="C2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" t="s">
         <v>190</v>
-      </c>
-      <c r="E2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -3525,19 +3600,19 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
-        <v>194</v>
+        <v>386</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -3545,19 +3620,19 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -3565,19 +3640,19 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -3585,19 +3660,19 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" t="s">
         <v>188</v>
       </c>
-      <c r="C6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F6" t="s">
         <v>190</v>
-      </c>
-      <c r="E6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F6" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -3605,19 +3680,19 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>194</v>
+        <v>386</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -3625,19 +3700,19 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -3645,19 +3720,19 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -3665,19 +3740,19 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" t="s">
         <v>199</v>
       </c>
-      <c r="C10" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" t="s">
-        <v>202</v>
-      </c>
       <c r="E10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -3685,19 +3760,19 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" t="s">
         <v>188</v>
       </c>
-      <c r="C11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F11" t="s">
         <v>190</v>
-      </c>
-      <c r="E11" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -3705,19 +3780,19 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
-        <v>194</v>
+        <v>386</v>
       </c>
       <c r="E12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F12" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -3725,19 +3800,19 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D13" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3745,19 +3820,19 @@
         <v>25</v>
       </c>
       <c r="B14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" t="s">
+        <v>189</v>
+      </c>
+      <c r="F14" t="s">
         <v>204</v>
-      </c>
-      <c r="C14" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" t="s">
-        <v>191</v>
-      </c>
-      <c r="F14" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3765,19 +3840,19 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3785,19 +3860,19 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -3805,19 +3880,19 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D17" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F17" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -3825,19 +3900,19 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" t="s">
         <v>188</v>
       </c>
-      <c r="C18" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" t="s">
         <v>190</v>
-      </c>
-      <c r="E18" t="s">
-        <v>191</v>
-      </c>
-      <c r="F18" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -3845,19 +3920,19 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
-        <v>194</v>
+        <v>386</v>
       </c>
       <c r="E19" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F19" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -3865,19 +3940,19 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F20" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -3885,19 +3960,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D21" t="s">
+        <v>187</v>
+      </c>
+      <c r="E21" t="s">
+        <v>189</v>
+      </c>
+      <c r="F21" t="s">
         <v>204</v>
-      </c>
-      <c r="C21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" t="s">
-        <v>189</v>
-      </c>
-      <c r="E21" t="s">
-        <v>191</v>
-      </c>
-      <c r="F21" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -3905,19 +3980,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D22" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E22" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F22" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -3925,19 +4000,19 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F23" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -3945,19 +4020,19 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F24" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -3965,19 +4040,19 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" t="s">
         <v>188</v>
       </c>
-      <c r="C25" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>189</v>
+      </c>
+      <c r="F25" t="s">
         <v>190</v>
-      </c>
-      <c r="E25" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -3985,19 +4060,19 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D26" t="s">
-        <v>194</v>
+        <v>390</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F26" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -4005,19 +4080,19 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D27" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F27" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -4025,19 +4100,19 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C28" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E28" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F28" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -4045,19 +4120,19 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D29" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="E29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F29" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -4065,19 +4140,19 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" t="s">
         <v>188</v>
       </c>
-      <c r="C30" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" t="s">
         <v>190</v>
-      </c>
-      <c r="E30" t="s">
-        <v>191</v>
-      </c>
-      <c r="F30" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -4085,19 +4160,19 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C31" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D31" t="s">
-        <v>194</v>
+        <v>390</v>
       </c>
       <c r="E31" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F31" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -4105,19 +4180,19 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D32" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E32" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F32" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -4125,19 +4200,19 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C33" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D33" t="s">
-        <v>337</v>
+        <v>391</v>
       </c>
       <c r="E33" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F33" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -4145,19 +4220,19 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C34" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D34" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E34" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F34" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -4165,19 +4240,19 @@
         <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C35" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D35" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F35" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -4185,19 +4260,19 @@
         <v>46</v>
       </c>
       <c r="B36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" t="s">
         <v>188</v>
       </c>
-      <c r="C36" t="s">
-        <v>189</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>189</v>
+      </c>
+      <c r="F36" t="s">
         <v>190</v>
-      </c>
-      <c r="E36" t="s">
-        <v>191</v>
-      </c>
-      <c r="F36" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -4205,19 +4280,19 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
-        <v>194</v>
+        <v>390</v>
       </c>
       <c r="E37" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F37" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -4225,19 +4300,19 @@
         <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D38" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E38" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -4245,19 +4320,19 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C39" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D39" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="E39" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -4265,19 +4340,19 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C40" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D40" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F40" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -4285,19 +4360,19 @@
         <v>46</v>
       </c>
       <c r="B41" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C41" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E41" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F41" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -4305,19 +4380,19 @@
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="E42" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F42" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -4325,19 +4400,19 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" t="s">
         <v>188</v>
       </c>
-      <c r="C43" t="s">
-        <v>189</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" t="s">
         <v>190</v>
-      </c>
-      <c r="E43" t="s">
-        <v>191</v>
-      </c>
-      <c r="F43" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -4345,19 +4420,19 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D44" t="s">
-        <v>194</v>
+        <v>390</v>
       </c>
       <c r="E44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F44" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -4365,19 +4440,19 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E45" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F45" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -4385,19 +4460,19 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C46" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D46" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="E46" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F46" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -4405,19 +4480,19 @@
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C47" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D47" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F47" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -4425,19 +4500,16 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>336</v>
-      </c>
-      <c r="C48" t="s">
-        <v>317</v>
+        <v>196</v>
       </c>
       <c r="D48" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="E48" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F48" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -4445,19 +4517,19 @@
         <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C49" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D49" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="E49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F49" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -4465,19 +4537,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C50" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D50" t="s">
+        <v>334</v>
+      </c>
+      <c r="E50" t="s">
+        <v>189</v>
+      </c>
+      <c r="F50" t="s">
         <v>343</v>
-      </c>
-      <c r="E50" t="s">
-        <v>191</v>
-      </c>
-      <c r="F50" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -4485,19 +4557,16 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>339</v>
-      </c>
-      <c r="C51" t="s">
-        <v>319</v>
+        <v>196</v>
       </c>
       <c r="D51" t="s">
-        <v>340</v>
+        <v>399</v>
       </c>
       <c r="E51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F51" t="s">
-        <v>352</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -4505,19 +4574,19 @@
         <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C52" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D52" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="E52" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F52" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -4525,19 +4594,19 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C53" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D53" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E53" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F53" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -4545,19 +4614,16 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>336</v>
-      </c>
-      <c r="C54" t="s">
-        <v>317</v>
+        <v>196</v>
       </c>
       <c r="D54" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="E54" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F54" t="s">
-        <v>355</v>
+        <v>398</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -4565,19 +4631,19 @@
         <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C55" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D55" t="s">
-        <v>340</v>
+        <v>382</v>
       </c>
       <c r="E55" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F55" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -4585,99 +4651,96 @@
         <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>333</v>
       </c>
       <c r="C56" t="s">
-        <v>189</v>
+        <v>313</v>
       </c>
       <c r="D56" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="E56" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F56" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
-      </c>
-      <c r="C57" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D57" t="s">
-        <v>190</v>
+        <v>395</v>
       </c>
       <c r="E57" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F57" t="s">
-        <v>192</v>
+        <v>396</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>193</v>
+        <v>330</v>
       </c>
       <c r="C58" t="s">
-        <v>189</v>
+        <v>311</v>
       </c>
       <c r="D58" t="s">
-        <v>194</v>
+        <v>382</v>
       </c>
       <c r="E58" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F58" t="s">
-        <v>195</v>
+        <v>348</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B59" t="s">
-        <v>196</v>
+        <v>333</v>
       </c>
       <c r="C59" t="s">
-        <v>189</v>
+        <v>313</v>
       </c>
       <c r="D59" t="s">
-        <v>197</v>
+        <v>334</v>
       </c>
       <c r="E59" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F59" t="s">
-        <v>198</v>
+        <v>349</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B60" t="s">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="C60" t="s">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="D60" t="s">
-        <v>340</v>
+        <v>393</v>
       </c>
       <c r="E60" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F60" t="s">
-        <v>359</v>
+        <v>394</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -4685,19 +4748,19 @@
         <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>360</v>
+        <v>186</v>
       </c>
       <c r="C61" t="s">
-        <v>322</v>
+        <v>187</v>
       </c>
       <c r="D61" t="s">
-        <v>361</v>
+        <v>188</v>
       </c>
       <c r="E61" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F61" t="s">
-        <v>362</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -4705,99 +4768,99 @@
         <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C62" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D62" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="E62" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F62" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B63" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D63" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E63" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F63" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
-        <v>193</v>
+        <v>333</v>
       </c>
       <c r="C64" t="s">
-        <v>189</v>
+        <v>314</v>
       </c>
       <c r="D64" t="s">
-        <v>194</v>
+        <v>334</v>
       </c>
       <c r="E64" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F64" t="s">
-        <v>195</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B65" t="s">
-        <v>196</v>
+        <v>351</v>
       </c>
       <c r="C65" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="D65" t="s">
-        <v>197</v>
+        <v>352</v>
       </c>
       <c r="E65" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F65" t="s">
-        <v>198</v>
+        <v>353</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="C66" t="s">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="D66" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E66" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F66" t="s">
-        <v>359</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -4805,19 +4868,19 @@
         <v>58</v>
       </c>
       <c r="B67" t="s">
-        <v>360</v>
+        <v>186</v>
       </c>
       <c r="C67" t="s">
-        <v>322</v>
+        <v>187</v>
       </c>
       <c r="D67" t="s">
-        <v>363</v>
+        <v>188</v>
       </c>
       <c r="E67" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F67" t="s">
-        <v>364</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -4825,19 +4888,19 @@
         <v>58</v>
       </c>
       <c r="B68" t="s">
-        <v>332</v>
+        <v>191</v>
       </c>
       <c r="C68" t="s">
-        <v>326</v>
+        <v>187</v>
       </c>
       <c r="D68" t="s">
-        <v>189</v>
+        <v>390</v>
       </c>
       <c r="E68" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F68" t="s">
-        <v>365</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -4845,99 +4908,99 @@
         <v>58</v>
       </c>
       <c r="B69" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C69" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D69" t="s">
-        <v>366</v>
+        <v>194</v>
       </c>
       <c r="E69" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F69" t="s">
-        <v>367</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>188</v>
+        <v>333</v>
       </c>
       <c r="C70" t="s">
-        <v>189</v>
+        <v>314</v>
       </c>
       <c r="D70" t="s">
-        <v>190</v>
+        <v>334</v>
       </c>
       <c r="E70" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F70" t="s">
-        <v>192</v>
+        <v>350</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B71" t="s">
-        <v>193</v>
+        <v>351</v>
       </c>
       <c r="C71" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="D71" t="s">
-        <v>194</v>
+        <v>354</v>
       </c>
       <c r="E71" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F71" t="s">
-        <v>195</v>
+        <v>355</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B72" t="s">
-        <v>196</v>
+        <v>326</v>
       </c>
       <c r="C72" t="s">
-        <v>189</v>
+        <v>320</v>
       </c>
       <c r="D72" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E72" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F72" t="s">
-        <v>198</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B73" t="s">
-        <v>339</v>
+        <v>196</v>
       </c>
       <c r="C73" t="s">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="E73" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F73" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -4945,19 +5008,16 @@
         <v>62</v>
       </c>
       <c r="B74" t="s">
-        <v>360</v>
-      </c>
-      <c r="C74" t="s">
-        <v>322</v>
+        <v>186</v>
       </c>
       <c r="D74" t="s">
-        <v>363</v>
+        <v>188</v>
       </c>
       <c r="E74" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F74" t="s">
-        <v>368</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -4965,19 +5025,16 @@
         <v>62</v>
       </c>
       <c r="B75" t="s">
-        <v>360</v>
-      </c>
-      <c r="C75" t="s">
-        <v>322</v>
+        <v>191</v>
       </c>
       <c r="D75" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="E75" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F75" t="s">
-        <v>369</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -4985,19 +5042,16 @@
         <v>62</v>
       </c>
       <c r="B76" t="s">
-        <v>360</v>
-      </c>
-      <c r="C76" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="D76" t="s">
-        <v>363</v>
+        <v>194</v>
       </c>
       <c r="E76" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F76" t="s">
-        <v>370</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -5005,19 +5059,19 @@
         <v>62</v>
       </c>
       <c r="B77" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="C77" t="s">
-        <v>322</v>
-      </c>
-      <c r="D77" t="s">
-        <v>363</v>
+        <v>314</v>
+      </c>
+      <c r="D77">
+        <v>10</v>
       </c>
       <c r="E77" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F77" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -5025,19 +5079,19 @@
         <v>62</v>
       </c>
       <c r="B78" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C78" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D78" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="E78" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F78" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -5045,179 +5099,461 @@
         <v>62</v>
       </c>
       <c r="B79" t="s">
-        <v>199</v>
-      </c>
-      <c r="C79" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D79" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="E79" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F79" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>188</v>
+        <v>333</v>
       </c>
       <c r="C80" t="s">
-        <v>189</v>
-      </c>
-      <c r="D80" t="s">
-        <v>190</v>
+        <v>405</v>
+      </c>
+      <c r="D80">
+        <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F80" t="s">
-        <v>192</v>
+        <v>408</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B81" t="s">
-        <v>193</v>
+        <v>351</v>
       </c>
       <c r="C81" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="D81" t="s">
-        <v>194</v>
+        <v>354</v>
       </c>
       <c r="E81" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F81" t="s">
-        <v>195</v>
+        <v>360</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
         <v>196</v>
       </c>
-      <c r="C82" t="s">
-        <v>189</v>
-      </c>
       <c r="D82" t="s">
-        <v>197</v>
+        <v>357</v>
       </c>
       <c r="E82" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F82" t="s">
-        <v>198</v>
+        <v>409</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C83" t="s">
-        <v>328</v>
-      </c>
-      <c r="D83" t="s">
-        <v>340</v>
+        <v>405</v>
+      </c>
+      <c r="D83">
+        <v>10</v>
       </c>
       <c r="E83" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F83" t="s">
-        <v>375</v>
+        <v>410</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C84" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="D84" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="E84" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F84" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B85" t="s">
-        <v>336</v>
-      </c>
-      <c r="C85" t="s">
-        <v>317</v>
+        <v>196</v>
       </c>
       <c r="D85" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="E85" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F85" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B86" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C86" t="s">
-        <v>319</v>
-      </c>
-      <c r="D86" t="s">
-        <v>340</v>
+        <v>405</v>
+      </c>
+      <c r="D86">
+        <v>10</v>
       </c>
       <c r="E86" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F86" t="s">
-        <v>341</v>
+        <v>412</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" t="s">
+        <v>351</v>
+      </c>
+      <c r="C87" t="s">
+        <v>316</v>
+      </c>
+      <c r="D87" t="s">
+        <v>354</v>
+      </c>
+      <c r="E87" t="s">
+        <v>189</v>
+      </c>
+      <c r="F87" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" t="s">
+        <v>196</v>
+      </c>
+      <c r="D88" t="s">
+        <v>357</v>
+      </c>
+      <c r="E88" t="s">
+        <v>189</v>
+      </c>
+      <c r="F88" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>62</v>
+      </c>
+      <c r="B89" t="s">
+        <v>333</v>
+      </c>
+      <c r="C89" t="s">
+        <v>405</v>
+      </c>
+      <c r="D89">
+        <v>10</v>
+      </c>
+      <c r="E89" t="s">
+        <v>189</v>
+      </c>
+      <c r="F89" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>62</v>
+      </c>
+      <c r="B90" t="s">
+        <v>351</v>
+      </c>
+      <c r="C90" t="s">
+        <v>316</v>
+      </c>
+      <c r="D90" t="s">
+        <v>354</v>
+      </c>
+      <c r="E90" t="s">
+        <v>189</v>
+      </c>
+      <c r="F90" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>62</v>
+      </c>
+      <c r="B91" t="s">
+        <v>196</v>
+      </c>
+      <c r="D91" t="s">
+        <v>357</v>
+      </c>
+      <c r="E91" t="s">
+        <v>189</v>
+      </c>
+      <c r="F91" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>62</v>
+      </c>
+      <c r="B92" t="s">
+        <v>333</v>
+      </c>
+      <c r="C92" t="s">
+        <v>405</v>
+      </c>
+      <c r="D92">
+        <v>10</v>
+      </c>
+      <c r="E92" t="s">
+        <v>189</v>
+      </c>
+      <c r="F92" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>62</v>
+      </c>
+      <c r="B93" t="s">
+        <v>351</v>
+      </c>
+      <c r="C93" t="s">
+        <v>316</v>
+      </c>
+      <c r="D93" t="s">
+        <v>354</v>
+      </c>
+      <c r="E93" t="s">
+        <v>189</v>
+      </c>
+      <c r="F93" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>62</v>
+      </c>
+      <c r="B94" t="s">
+        <v>196</v>
+      </c>
+      <c r="D94" t="s">
+        <v>418</v>
+      </c>
+      <c r="E94" t="s">
+        <v>189</v>
+      </c>
+      <c r="F94" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
         <v>65</v>
       </c>
-      <c r="B87" t="s">
-        <v>199</v>
-      </c>
-      <c r="C87" t="s">
-        <v>189</v>
-      </c>
-      <c r="D87" t="s">
-        <v>342</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="B95" t="s">
+        <v>186</v>
+      </c>
+      <c r="C95" t="s">
+        <v>187</v>
+      </c>
+      <c r="D95" t="s">
+        <v>188</v>
+      </c>
+      <c r="E95" t="s">
+        <v>189</v>
+      </c>
+      <c r="F95" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>65</v>
+      </c>
+      <c r="B96" t="s">
         <v>191</v>
       </c>
-      <c r="F87" t="s">
-        <v>203</v>
+      <c r="C96" t="s">
+        <v>187</v>
+      </c>
+      <c r="D96" t="s">
+        <v>390</v>
+      </c>
+      <c r="E96" t="s">
+        <v>189</v>
+      </c>
+      <c r="F96" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>65</v>
+      </c>
+      <c r="B97" t="s">
+        <v>193</v>
+      </c>
+      <c r="C97" t="s">
+        <v>187</v>
+      </c>
+      <c r="D97" t="s">
+        <v>194</v>
+      </c>
+      <c r="E97" t="s">
+        <v>189</v>
+      </c>
+      <c r="F97" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98" t="s">
+        <v>333</v>
+      </c>
+      <c r="C98" t="s">
+        <v>322</v>
+      </c>
+      <c r="D98" t="s">
+        <v>334</v>
+      </c>
+      <c r="E98" t="s">
+        <v>189</v>
+      </c>
+      <c r="F98" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>65</v>
+      </c>
+      <c r="B99" t="s">
+        <v>333</v>
+      </c>
+      <c r="C99" t="s">
+        <v>324</v>
+      </c>
+      <c r="D99" t="s">
+        <v>334</v>
+      </c>
+      <c r="E99" t="s">
+        <v>189</v>
+      </c>
+      <c r="F99" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>65</v>
+      </c>
+      <c r="B100" t="s">
+        <v>330</v>
+      </c>
+      <c r="C100" t="s">
+        <v>311</v>
+      </c>
+      <c r="D100" t="s">
+        <v>331</v>
+      </c>
+      <c r="E100" t="s">
+        <v>189</v>
+      </c>
+      <c r="F100" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>65</v>
+      </c>
+      <c r="B101" t="s">
+        <v>333</v>
+      </c>
+      <c r="C101" t="s">
+        <v>313</v>
+      </c>
+      <c r="D101" t="s">
+        <v>334</v>
+      </c>
+      <c r="E101" t="s">
+        <v>189</v>
+      </c>
+      <c r="F101" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>65</v>
+      </c>
+      <c r="B102" t="s">
+        <v>196</v>
+      </c>
+      <c r="C102" t="s">
+        <v>187</v>
+      </c>
+      <c r="D102" t="s">
+        <v>336</v>
+      </c>
+      <c r="E102" t="s">
+        <v>189</v>
+      </c>
+      <c r="F102" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -5227,7 +5563,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -5240,7 +5576,7 @@
         <v>175</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>176</v>
@@ -5248,189 +5584,156 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>384</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B4" t="s">
         <v>306</v>
       </c>
       <c r="C4" t="s">
-        <v>385</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>301</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>309</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>301</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>367</v>
       </c>
       <c r="C7" t="s">
-        <v>308</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>368</v>
       </c>
       <c r="C8" t="s">
-        <v>313</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B9" t="s">
-        <v>314</v>
-      </c>
-      <c r="C9" t="s">
-        <v>386</v>
+        <v>369</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>315</v>
-      </c>
-      <c r="C10" t="s">
-        <v>387</v>
+        <v>380</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B12" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B13" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B14" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B15" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C15" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>305</v>
-      </c>
-      <c r="B16" t="s">
-        <v>382</v>
-      </c>
-      <c r="C16" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>305</v>
-      </c>
-      <c r="B17" t="s">
-        <v>391</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>305</v>
-      </c>
-      <c r="B18" t="s">
-        <v>392</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -5441,7 +5744,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
@@ -5451,189 +5754,200 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" t="s">
         <v>291</v>
-      </c>
-      <c r="C5" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C7" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C9" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B10" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C10" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C11" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B12" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C12" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B13" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C13" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C14" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B15" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C15" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B16" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C16" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B17" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C17" t="s">
-        <v>331</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>405</v>
+      </c>
+      <c r="B18" t="s">
+        <v>287</v>
+      </c>
+      <c r="C18" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -5662,10 +5976,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="29"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -5694,10 +6008,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="27"/>
+      <c r="B2" s="29"/>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
@@ -5723,11 +6037,11 @@
       <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="27"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
@@ -5786,7 +6100,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>16</v>
@@ -5809,7 +6123,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>19</v>
@@ -5832,7 +6146,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>21</v>
@@ -5855,10 +6169,10 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>23</v>
@@ -5958,7 +6272,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>17</v>
@@ -6149,7 +6463,7 @@
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>66</v>

--- a/src/test/resources/Login_TC.xlsx
+++ b/src/test/resources/Login_TC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\automation-framework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F2ACCE-9713-477C-AEA0-B2256484BF60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B2A31B-95CE-4230-BA58-4068D4BD7C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,10 @@
     <sheet name="M2.Login - Encrypt update" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ObjectRepository!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestCases!$C$1:$C$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestData!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TestSteps!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="421">
   <si>
     <t>Created Date: 20/05/2025</t>
   </si>
@@ -1093,9 +1096,6 @@
     <t>TestCaseID</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>chivq9@fpt.com</t>
   </si>
   <si>
@@ -1228,12 +1228,6 @@
     <t>Run</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>navigate</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -1246,24 +1240,15 @@
     <t>Open Beatchat login page</t>
   </si>
   <si>
-    <t>loginwithmicrosoft</t>
-  </si>
-  <si>
     <t>SSO login</t>
   </si>
   <si>
-    <t>entermicrosoftotp</t>
-  </si>
-  <si>
     <t>${microsoftOtp}</t>
   </si>
   <si>
     <t>Optional Microsoft MFA OTP</t>
   </si>
   <si>
-    <t>assertanytext</t>
-  </si>
-  <si>
     <t>User without security key should see setup suggestion</t>
   </si>
   <si>
@@ -1276,30 +1261,15 @@
     <t>Chat list should be displayed</t>
   </si>
   <si>
-    <t>skipsecuritykeysetup</t>
-  </si>
-  <si>
-    <t>recipient</t>
-  </si>
-  <si>
-    <t>message</t>
-  </si>
-  <si>
     <t>Skip security key setup if displayed</t>
   </si>
   <si>
-    <t>searchandopenaccount</t>
-  </si>
-  <si>
     <t>${recipient}</t>
   </si>
   <si>
     <t>Search account and open chat</t>
   </si>
   <si>
-    <t>sendchatmessage</t>
-  </si>
-  <si>
     <t>${message}</t>
   </si>
   <si>
@@ -1309,19 +1279,10 @@
     <t>Verify sent message is visible</t>
   </si>
   <si>
-    <t>opencreategroupchat</t>
-  </si>
-  <si>
     <t>Click create group chat icon</t>
   </si>
   <si>
-    <t>clicksecuritylock</t>
-  </si>
-  <si>
     <t>Click security lock toggle</t>
-  </si>
-  <si>
-    <t>assertmessagevisible</t>
   </si>
   <si>
     <t>Verify a warning/message is displayed after clicking security lock</t>
@@ -1505,24 +1466,6 @@
     <t>Hiển thị toàn bộ lịch sử tin nhắn bình thường</t>
   </si>
   <si>
-    <t>keyword</t>
-  </si>
-  <si>
-    <t>object</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>LocatorValue</t>
-  </si>
-  <si>
-    <t>ObjectName</t>
-  </si>
-  <si>
-    <t>LocatorType</t>
-  </si>
-  <si>
     <t>microsoft.ssoButton</t>
   </si>
   <si>
@@ -1575,9 +1518,6 @@
   </si>
   <si>
     <t>//button[.//span[normalize-space(.)='Bỏ qua'] or normalize-space(.)='Bỏ qua']</t>
-  </si>
-  <si>
-    <t>GLOBAL</t>
   </si>
   <si>
     <t>Autotest send message PK-005</t>
@@ -1653,9 +1593,6 @@
     <t>//button[contains(@class, "_button--neutral-flat_ff1v2_48")]</t>
   </si>
   <si>
-    <t>assertvisible</t>
-  </si>
-  <si>
     <t>PIN/passphrase screen is displayed</t>
   </si>
   <si>
@@ -1665,21 +1602,9 @@
     <t>PIN screen text is displayed</t>
   </si>
   <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>${passphrase}</t>
-  </si>
-  <si>
     <t>Enter valid passphrase</t>
   </si>
   <si>
-    <t>clickdeep</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>Submit passphrase</t>
   </si>
   <si>
@@ -1728,9 +1653,6 @@
     <t>Switch to QR login screen</t>
   </si>
   <si>
-    <t>uploadfile</t>
-  </si>
-  <si>
     <t>${qrValidPath}</t>
   </si>
   <si>
@@ -1785,18 +1707,6 @@
     <t>secure.passphrase</t>
   </si>
   <si>
-    <t>secure.qrValidPath</t>
-  </si>
-  <si>
-    <t>secure.qrInvalidPath</t>
-  </si>
-  <si>
-    <t>${secure.qrValidPath}</t>
-  </si>
-  <si>
-    <t>${secure.qrInvalidPath}</t>
-  </si>
-  <si>
     <t>src\test\resources\QR login\Chivq9_UAT_QR.png</t>
   </si>
   <si>
@@ -1815,18 +1725,9 @@
     <t>Devteam@1234562</t>
   </si>
   <si>
-    <t>secure.InvalidPassphrase</t>
-  </si>
-  <si>
     <t>Invalid@1234</t>
   </si>
   <si>
-    <t>${secure.InvalidPassphrase}</t>
-  </si>
-  <si>
-    <t>Skipped: message text assertion is more stable than SVG icon assertion</t>
-  </si>
-  <si>
     <t>PIN code is incorrect|Pin code is incorrect|attempts remaining|incorrect|khÃ´ng Ä‘Ãºng|khÃ´ng há»£p lá»‡|MÃ£ báº£o máº­t</t>
   </si>
   <si>
@@ -1939,13 +1840,112 @@
   </si>
   <si>
     <t>Verify giới hạn upload QR sai: xóa QR giữa các lần upload, lock ở lần thứ 6</t>
+  </si>
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Assertion</t>
+  </si>
+  <si>
+    <t>OPEN_URL</t>
+  </si>
+  <si>
+    <t>LOGIN_WITH_MICROSOFT</t>
+  </si>
+  <si>
+    <t>ENTER_MICROSOFT_OTP</t>
+  </si>
+  <si>
+    <t>VERIFY_TEXT</t>
+  </si>
+  <si>
+    <t>CONTAINS</t>
+  </si>
+  <si>
+    <t>SKIP_SECURITY_KEY_SETUP</t>
+  </si>
+  <si>
+    <t>SEARCH_AND_OPEN_ACCOUNT</t>
+  </si>
+  <si>
+    <t>SEND_CHAT_MESSAGE</t>
+  </si>
+  <si>
+    <t>OPEN_CREATE_GROUP_CHAT</t>
+  </si>
+  <si>
+    <t>CLICK_SECURITY_LOCK</t>
+  </si>
+  <si>
+    <t>ASSERT_MESSAGE_VISIBLE</t>
+  </si>
+  <si>
+    <t>VISIBLE</t>
+  </si>
+  <si>
+    <t>VERIFY_VISIBLE</t>
+  </si>
+  <si>
+    <t>INPUT</t>
+  </si>
+  <si>
+    <t>CLICK_DEEP</t>
+  </si>
+  <si>
+    <t>${secure.invalidPassphrase}</t>
+  </si>
+  <si>
+    <t>UPLOAD_FILE</t>
+  </si>
+  <si>
+    <t>KEY</t>
+  </si>
+  <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>base.url</t>
+  </si>
+  <si>
+    <t>https://beatchat.ai/</t>
+  </si>
+  <si>
+    <t>microsoftOtp</t>
+  </si>
+  <si>
+    <t>secure.invalidPassphrase</t>
+  </si>
+  <si>
+    <t>PK-005.recipient</t>
+  </si>
+  <si>
+    <t>PK-005.message</t>
+  </si>
+  <si>
+    <t>OBJECT</t>
+  </si>
+  <si>
+    <t>TYPE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2034,8 +2034,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2059,8 +2072,14 @@
         <fgColor indexed="31"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2129,12 +2148,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2198,10 +2232,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2212,6 +2251,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2543,10 +2589,10 @@
         <v>175</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>11</v>
@@ -2563,10 +2609,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -2575,7 +2621,7 @@
         <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2583,10 +2629,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -2595,7 +2641,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2603,10 +2649,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -2615,27 +2661,27 @@
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="25" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="26" t="s">
+      <c r="B5" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>225</v>
+      <c r="F5" s="25" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2643,10 +2689,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -2655,46 +2701,46 @@
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="26" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="25" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="26" t="s">
+      <c r="B7" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="26" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="26" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
+      <c r="F7" s="25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="25" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="B8" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="25" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2703,36 +2749,36 @@
         <v>35</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="26" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
+    <row r="10" spans="1:6" s="25" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="D10" s="27" t="s">
+      <c r="B10" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="26" t="s">
-        <v>187</v>
+      <c r="F10" s="25" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2740,10 +2786,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>45</v>
@@ -2752,7 +2798,7 @@
         <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2760,10 +2806,10 @@
         <v>46</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>48</v>
@@ -2772,27 +2818,27 @@
         <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="26" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="27" t="s">
-        <v>232</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>403</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>404</v>
+      <c r="B13" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2800,10 +2846,10 @@
         <v>54</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="C14" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>56</v>
@@ -2820,10 +2866,10 @@
         <v>58</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>60</v>
@@ -2832,27 +2878,27 @@
         <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="26" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>421</v>
+      <c r="B16" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -2860,10 +2906,10 @@
         <v>65</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>66</v>
@@ -2872,7 +2918,7 @@
         <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -2880,10 +2926,10 @@
         <v>67</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D18" s="24" t="s">
         <v>70</v>
@@ -2892,7 +2938,7 @@
         <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2900,10 +2946,10 @@
         <v>71</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="C19" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D19" t="s">
         <v>73</v>
@@ -2912,7 +2958,7 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2920,10 +2966,10 @@
         <v>74</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C20" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -2940,10 +2986,10 @@
         <v>77</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -2960,10 +3006,10 @@
         <v>80</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D22" t="s">
         <v>82</v>
@@ -2972,7 +3018,7 @@
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2980,19 +3026,19 @@
         <v>83</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C23" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D23" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3000,10 +3046,10 @@
         <v>87</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C24" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D24" t="s">
         <v>89</v>
@@ -3012,7 +3058,7 @@
         <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3020,10 +3066,10 @@
         <v>91</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C25" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D25" t="s">
         <v>94</v>
@@ -3032,7 +3078,7 @@
         <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3040,10 +3086,10 @@
         <v>95</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -3052,7 +3098,7 @@
         <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3060,10 +3106,10 @@
         <v>98</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D27" t="s">
         <v>100</v>
@@ -3072,7 +3118,7 @@
         <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -3080,10 +3126,10 @@
         <v>101</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D28" t="s">
         <v>104</v>
@@ -3092,7 +3138,7 @@
         <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -3100,10 +3146,10 @@
         <v>105</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C29" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D29" t="s">
         <v>104</v>
@@ -3112,7 +3158,7 @@
         <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3120,10 +3166,10 @@
         <v>107</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C30" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D30" t="s">
         <v>104</v>
@@ -3132,7 +3178,7 @@
         <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3140,10 +3186,10 @@
         <v>109</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="C31" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D31" t="s">
         <v>112</v>
@@ -3152,7 +3198,7 @@
         <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3160,10 +3206,10 @@
         <v>113</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C32" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D32" t="s">
         <v>115</v>
@@ -3172,7 +3218,7 @@
         <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3180,10 +3226,10 @@
         <v>116</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="C33" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D33" t="s">
         <v>118</v>
@@ -3192,7 +3238,7 @@
         <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3200,10 +3246,10 @@
         <v>119</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D34" t="s">
         <v>121</v>
@@ -3212,7 +3258,7 @@
         <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3220,10 +3266,10 @@
         <v>122</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D35" t="s">
         <v>125</v>
@@ -3240,10 +3286,10 @@
         <v>126</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D36" t="s">
         <v>128</v>
@@ -3252,7 +3298,7 @@
         <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3260,10 +3306,10 @@
         <v>129</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D37" t="s">
         <v>131</v>
@@ -3272,7 +3318,7 @@
         <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3280,10 +3326,10 @@
         <v>132</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="C38" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D38" t="s">
         <v>135</v>
@@ -3292,7 +3338,7 @@
         <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -3300,10 +3346,10 @@
         <v>136</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C39" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D39" t="s">
         <v>138</v>
@@ -3312,7 +3358,7 @@
         <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3320,10 +3366,10 @@
         <v>139</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D40" t="s">
         <v>141</v>
@@ -3332,7 +3378,7 @@
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -3340,10 +3386,10 @@
         <v>142</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="C41" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D41" t="s">
         <v>145</v>
@@ -3352,7 +3398,7 @@
         <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -3360,10 +3406,10 @@
         <v>146</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="C42" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D42" t="s">
         <v>148</v>
@@ -3372,7 +3418,7 @@
         <v>42</v>
       </c>
       <c r="F42" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -3380,19 +3426,19 @@
         <v>149</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D43" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -3400,10 +3446,10 @@
         <v>153</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="C44" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D44" t="s">
         <v>76</v>
@@ -3420,10 +3466,10 @@
         <v>155</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D45" t="s">
         <v>157</v>
@@ -3432,7 +3478,7 @@
         <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3440,10 +3486,10 @@
         <v>158</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="C46" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D46" t="s">
         <v>161</v>
@@ -3452,7 +3498,7 @@
         <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3460,10 +3506,10 @@
         <v>162</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="C47" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D47" t="s">
         <v>161</v>
@@ -3480,10 +3526,10 @@
         <v>165</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D48" t="s">
         <v>161</v>
@@ -3492,7 +3538,7 @@
         <v>17</v>
       </c>
       <c r="F48" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3500,19 +3546,19 @@
         <v>167</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="C49" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D49" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E49" t="s">
         <v>52</v>
       </c>
       <c r="F49" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3520,19 +3566,19 @@
         <v>172</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D50" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3544,2199 +3590,2284 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="134.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="37.109375" customWidth="1"/>
+    <col min="6" max="6" width="61.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="F1" s="22" t="s">
+    <row r="1" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>393</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="33">
+        <v>1</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" s="33">
+        <v>2</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="33">
+        <v>3</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="33">
+        <v>4</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="33">
+        <v>1</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="33">
+        <v>2</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="33">
+        <v>3</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="33">
+        <v>4</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="33">
+        <v>5</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="33">
+        <v>1</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="33">
+        <v>2</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="33">
+        <v>3</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="33">
+        <v>4</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="33">
+        <v>5</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>400</v>
+      </c>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="33">
+        <v>6</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>401</v>
+      </c>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="33">
+        <v>7</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="33">
+        <v>1</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="33">
+        <v>2</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="33">
+        <v>3</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="33">
+        <v>4</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="33">
+        <v>5</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>402</v>
+      </c>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="33">
+        <v>6</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>403</v>
+      </c>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="33">
+        <v>7</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>404</v>
+      </c>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="H24" s="33" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="33">
+        <v>1</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="33">
+        <v>2</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="33">
+        <v>3</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="33">
+        <v>4</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="33">
+        <v>5</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="33">
+        <v>1</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="33">
+        <v>2</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="33">
+        <v>3</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="33">
+        <v>4</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="33">
+        <v>5</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E34" s="33">
+        <v>10</v>
+      </c>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="33">
+        <v>6</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H35" s="33" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="33">
+        <v>1</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="33">
+        <v>2</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="33">
+        <v>3</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="33">
+        <v>4</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="33">
+        <v>5</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E40" s="33">
+        <v>10</v>
+      </c>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="33">
+        <v>6</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33" t="s">
+        <v>350</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="33">
+        <v>1</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="33">
+        <v>2</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="33">
+        <v>3</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="33">
+        <v>4</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="33">
+        <v>5</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E46" s="33">
+        <v>10</v>
+      </c>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="33">
+        <v>6</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="G47" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H47" s="33" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="33">
+        <v>7</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33"/>
+      <c r="H48" s="33" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="33">
+        <v>8</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E49" s="33">
+        <v>10</v>
+      </c>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
+      <c r="H49" s="33" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="33">
+        <v>9</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H50" s="33" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="33">
+        <v>10</v>
+      </c>
+      <c r="C51" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="33">
+        <v>11</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="33">
+        <v>10</v>
+      </c>
+      <c r="F52" s="33"/>
+      <c r="G52" s="33"/>
+      <c r="H52" s="33" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B53" s="33">
+        <v>12</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="G53" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H53" s="33" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" s="33">
+        <v>13</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B55" s="33">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C55" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E55" s="33">
+        <v>10</v>
+      </c>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="33" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B56" s="33">
+        <v>15</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="G56" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H56" s="33" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="33">
+        <v>16</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E57" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="F57" s="33"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B58" s="33">
+        <v>17</v>
+      </c>
+      <c r="C58" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D58" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" s="33">
+        <v>10</v>
+      </c>
+      <c r="F58" s="33"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="33" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B59" s="33">
+        <v>18</v>
+      </c>
+      <c r="C59" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33" t="s">
+        <v>359</v>
+      </c>
+      <c r="G59" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H59" s="33" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B60" s="33">
+        <v>1</v>
+      </c>
+      <c r="C60" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D3" t="s">
-        <v>386</v>
-      </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B61" s="33">
+        <v>2</v>
+      </c>
+      <c r="C61" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D61" s="33"/>
+      <c r="E61" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="F61" s="33"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" s="33">
+        <v>3</v>
+      </c>
+      <c r="C62" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D62" s="33"/>
+      <c r="E62" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="F3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="F62" s="33"/>
+      <c r="G62" s="33"/>
+      <c r="H62" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B63" s="33">
+        <v>4</v>
+      </c>
+      <c r="C63" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="E63" s="33">
+        <v>10</v>
+      </c>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B64" s="33">
+        <v>5</v>
+      </c>
+      <c r="C64" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D64" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E64" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="33" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B65" s="33">
+        <v>6</v>
+      </c>
+      <c r="C65" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="G65" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H65" s="33" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B66" s="33">
+        <v>1</v>
+      </c>
+      <c r="C66" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D66" s="33"/>
+      <c r="E66" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F66" s="33"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B67" s="33">
+        <v>2</v>
+      </c>
+      <c r="C67" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D67" s="33"/>
+      <c r="E67" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="F67" s="33"/>
+      <c r="G67" s="33"/>
+      <c r="H67" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" s="33">
+        <v>3</v>
+      </c>
+      <c r="C68" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D68" s="33"/>
+      <c r="E68" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F68" s="33"/>
+      <c r="G68" s="33"/>
+      <c r="H68" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" s="33">
+        <v>4</v>
+      </c>
+      <c r="C69" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D69" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="E69" s="33">
+        <v>10</v>
+      </c>
+      <c r="F69" s="33"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="33" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" s="33">
+        <v>5</v>
+      </c>
+      <c r="C70" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D70" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E70" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="F70" s="33"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="33" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" s="33">
+        <v>6</v>
+      </c>
+      <c r="C71" s="33" t="s">
+        <v>406</v>
+      </c>
+      <c r="D71" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="H71" s="33" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B72" s="33">
+        <v>7</v>
+      </c>
+      <c r="C72" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D72" s="33"/>
+      <c r="E72" s="33"/>
+      <c r="F72" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G72" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H72" s="33" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="33">
+        <v>1</v>
+      </c>
+      <c r="C73" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D73" s="33"/>
+      <c r="E73" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F73" s="33"/>
+      <c r="G73" s="33"/>
+      <c r="H73" s="33" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="33">
+        <v>2</v>
+      </c>
+      <c r="C74" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D74" s="33"/>
+      <c r="E74" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="F74" s="33"/>
+      <c r="G74" s="33"/>
+      <c r="H74" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="33">
+        <v>3</v>
+      </c>
+      <c r="C75" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D75" s="33"/>
+      <c r="E75" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F75" s="33"/>
+      <c r="G75" s="33"/>
+      <c r="H75" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="33">
+        <v>4</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="E76" s="33">
+        <v>10</v>
+      </c>
+      <c r="F76" s="33"/>
+      <c r="G76" s="33"/>
+      <c r="H76" s="33" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="33">
+        <v>5</v>
+      </c>
+      <c r="C77" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D77" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E77" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="F77" s="33"/>
+      <c r="G77" s="33"/>
+      <c r="H77" s="33" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="33">
+        <v>6</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G78" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H78" s="33" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="33">
+        <v>7</v>
+      </c>
+      <c r="C79" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="E79" s="33">
+        <v>10</v>
+      </c>
+      <c r="F79" s="33"/>
+      <c r="G79" s="33"/>
+      <c r="H79" s="33" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80" s="33">
+        <v>8</v>
+      </c>
+      <c r="C80" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="F80" s="33"/>
+      <c r="G80" s="33"/>
+      <c r="H80" s="33" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" s="33">
+        <v>9</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D81" s="33"/>
+      <c r="E81" s="33"/>
+      <c r="F81" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G81" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H81" s="33" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B82" s="33">
+        <v>10</v>
+      </c>
+      <c r="C82" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D82" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="E82" s="33">
+        <v>10</v>
+      </c>
+      <c r="F82" s="33"/>
+      <c r="G82" s="33"/>
+      <c r="H82" s="33" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" s="33">
+        <v>11</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D83" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E83" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="F83" s="33"/>
+      <c r="G83" s="33"/>
+      <c r="H83" s="33" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B84" s="33">
+        <v>12</v>
+      </c>
+      <c r="C84" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D84" s="33"/>
+      <c r="E84" s="33"/>
+      <c r="F84" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G84" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H84" s="33" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B85" s="33">
+        <v>13</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="E85" s="33">
+        <v>10</v>
+      </c>
+      <c r="F85" s="33"/>
+      <c r="G85" s="33"/>
+      <c r="H85" s="33" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B86" s="33">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C86" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D86" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E86" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="F86" s="33"/>
+      <c r="G86" s="33"/>
+      <c r="H86" s="33" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" s="33">
+        <v>15</v>
+      </c>
+      <c r="C87" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D87" s="33"/>
+      <c r="E87" s="33"/>
+      <c r="F87" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G87" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H87" s="33" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" s="33">
+        <v>16</v>
+      </c>
+      <c r="C88" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D88" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="E88" s="33">
+        <v>10</v>
+      </c>
+      <c r="F88" s="33"/>
+      <c r="G88" s="33"/>
+      <c r="H88" s="33" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B89" s="33">
+        <v>17</v>
+      </c>
+      <c r="C89" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D89" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E89" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="F89" s="33"/>
+      <c r="G89" s="33"/>
+      <c r="H89" s="33" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B90" s="33">
+        <v>18</v>
+      </c>
+      <c r="C90" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D90" s="33"/>
+      <c r="E90" s="33"/>
+      <c r="F90" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G90" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H90" s="33" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B91" s="33">
+        <v>19</v>
+      </c>
+      <c r="C91" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D91" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="E91" s="33">
+        <v>10</v>
+      </c>
+      <c r="F91" s="33"/>
+      <c r="G91" s="33"/>
+      <c r="H91" s="33" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B92" s="33">
+        <v>20</v>
+      </c>
+      <c r="C92" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="D92" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="E92" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="F92" s="33"/>
+      <c r="G92" s="33"/>
+      <c r="H92" s="33" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B93" s="33">
+        <v>21</v>
+      </c>
+      <c r="C93" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D93" s="33"/>
+      <c r="E93" s="33"/>
+      <c r="F93" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="G93" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H93" s="33" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B94" s="33">
+        <v>1</v>
+      </c>
+      <c r="C94" s="33" t="s">
+        <v>394</v>
+      </c>
+      <c r="D94" s="33"/>
+      <c r="E94" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="F94" s="33"/>
+      <c r="G94" s="33"/>
+      <c r="H94" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B95" s="33">
+        <v>2</v>
+      </c>
+      <c r="C95" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D95" s="33"/>
+      <c r="E95" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="F95" s="33"/>
+      <c r="G95" s="33"/>
+      <c r="H95" s="33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B96" s="33">
+        <v>3</v>
+      </c>
+      <c r="C96" s="33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D96" s="33"/>
+      <c r="E96" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="F96" s="33"/>
+      <c r="G96" s="33"/>
+      <c r="H96" s="33" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B97" s="33">
+        <v>4</v>
+      </c>
+      <c r="C97" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D97" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="E97" s="33">
+        <v>10</v>
+      </c>
+      <c r="F97" s="33"/>
+      <c r="G97" s="33"/>
+      <c r="H97" s="33" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B98" s="33">
+        <v>5</v>
+      </c>
+      <c r="C98" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D98" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="E98" s="33">
+        <v>10</v>
+      </c>
+      <c r="F98" s="33"/>
+      <c r="G98" s="33"/>
+      <c r="H98" s="33" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B99" s="33">
+        <v>6</v>
+      </c>
+      <c r="C99" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D99" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="E99" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="F99" s="33"/>
+      <c r="G99" s="33"/>
+      <c r="H99" s="33" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B100" s="33">
+        <v>7</v>
+      </c>
+      <c r="C100" s="33" t="s">
+        <v>408</v>
+      </c>
+      <c r="D100" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E100" s="33">
+        <v>10</v>
+      </c>
+      <c r="F100" s="33"/>
+      <c r="G100" s="33"/>
+      <c r="H100" s="33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B101" s="33">
+        <v>8</v>
+      </c>
+      <c r="C101" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D101" s="33"/>
+      <c r="E101" s="33"/>
+      <c r="F101" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="G101" s="33" t="s">
+        <v>398</v>
+      </c>
+      <c r="H101" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="E4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D7" t="s">
-        <v>386</v>
-      </c>
-      <c r="E7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" t="s">
-        <v>187</v>
-      </c>
-      <c r="D8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E8" t="s">
-        <v>189</v>
-      </c>
-      <c r="F8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>201</v>
-      </c>
-      <c r="C9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" t="s">
-        <v>187</v>
-      </c>
-      <c r="E9" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" t="s">
-        <v>199</v>
-      </c>
-      <c r="E10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F10" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" t="s">
-        <v>189</v>
-      </c>
-      <c r="F11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" t="s">
-        <v>386</v>
-      </c>
-      <c r="E12" t="s">
-        <v>189</v>
-      </c>
-      <c r="F12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>193</v>
-      </c>
-      <c r="C13" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" t="s">
-        <v>194</v>
-      </c>
-      <c r="E13" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" t="s">
-        <v>187</v>
-      </c>
-      <c r="E14" t="s">
-        <v>189</v>
-      </c>
-      <c r="F14" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" t="s">
-        <v>189</v>
-      </c>
-      <c r="F15" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" t="s">
-        <v>208</v>
-      </c>
-      <c r="C16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16" t="s">
-        <v>209</v>
-      </c>
-      <c r="E16" t="s">
-        <v>189</v>
-      </c>
-      <c r="F16" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>196</v>
-      </c>
-      <c r="C17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D17" t="s">
-        <v>209</v>
-      </c>
-      <c r="E17" t="s">
-        <v>189</v>
-      </c>
-      <c r="F17" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" t="s">
-        <v>188</v>
-      </c>
-      <c r="E18" t="s">
-        <v>189</v>
-      </c>
-      <c r="F18" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>191</v>
-      </c>
-      <c r="C19" t="s">
-        <v>187</v>
-      </c>
-      <c r="D19" t="s">
-        <v>386</v>
-      </c>
-      <c r="E19" t="s">
-        <v>189</v>
-      </c>
-      <c r="F19" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D20" t="s">
-        <v>194</v>
-      </c>
-      <c r="E20" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" t="s">
-        <v>187</v>
-      </c>
-      <c r="D21" t="s">
-        <v>187</v>
-      </c>
-      <c r="E21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F21" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>212</v>
-      </c>
-      <c r="C22" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" t="s">
-        <v>187</v>
-      </c>
-      <c r="E22" t="s">
-        <v>189</v>
-      </c>
-      <c r="F22" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" t="s">
-        <v>214</v>
-      </c>
-      <c r="C23" t="s">
-        <v>187</v>
-      </c>
-      <c r="D23" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" t="s">
-        <v>189</v>
-      </c>
-      <c r="F23" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>216</v>
-      </c>
-      <c r="C24" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" t="s">
-        <v>189</v>
-      </c>
-      <c r="F24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
-        <v>186</v>
-      </c>
-      <c r="C25" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" t="s">
-        <v>188</v>
-      </c>
-      <c r="E25" t="s">
-        <v>189</v>
-      </c>
-      <c r="F25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s">
-        <v>191</v>
-      </c>
-      <c r="C26" t="s">
-        <v>187</v>
-      </c>
-      <c r="D26" t="s">
-        <v>390</v>
-      </c>
-      <c r="E26" t="s">
-        <v>189</v>
-      </c>
-      <c r="F26" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>193</v>
-      </c>
-      <c r="C27" t="s">
-        <v>187</v>
-      </c>
-      <c r="D27" t="s">
-        <v>194</v>
-      </c>
-      <c r="E27" t="s">
-        <v>189</v>
-      </c>
-      <c r="F27" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
-        <v>326</v>
-      </c>
-      <c r="C28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D28" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" t="s">
-        <v>189</v>
-      </c>
-      <c r="F28" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" t="s">
-        <v>187</v>
-      </c>
-      <c r="D29" t="s">
-        <v>328</v>
-      </c>
-      <c r="E29" t="s">
-        <v>189</v>
-      </c>
-      <c r="F29" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" t="s">
-        <v>186</v>
-      </c>
-      <c r="C30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" t="s">
-        <v>188</v>
-      </c>
-      <c r="E30" t="s">
-        <v>189</v>
-      </c>
-      <c r="F30" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C31" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" t="s">
-        <v>390</v>
-      </c>
-      <c r="E31" t="s">
-        <v>189</v>
-      </c>
-      <c r="F31" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" t="s">
-        <v>193</v>
-      </c>
-      <c r="C32" t="s">
-        <v>187</v>
-      </c>
-      <c r="D32" t="s">
-        <v>194</v>
-      </c>
-      <c r="E32" t="s">
-        <v>189</v>
-      </c>
-      <c r="F32" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" t="s">
-        <v>330</v>
-      </c>
-      <c r="C33" t="s">
-        <v>311</v>
-      </c>
-      <c r="D33" t="s">
-        <v>391</v>
-      </c>
-      <c r="E33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F33" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" t="s">
-        <v>333</v>
-      </c>
-      <c r="C34" t="s">
-        <v>313</v>
-      </c>
-      <c r="D34" t="s">
-        <v>334</v>
-      </c>
-      <c r="E34" t="s">
-        <v>189</v>
-      </c>
-      <c r="F34" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" t="s">
-        <v>196</v>
-      </c>
-      <c r="C35" t="s">
-        <v>187</v>
-      </c>
-      <c r="D35" t="s">
-        <v>336</v>
-      </c>
-      <c r="E35" t="s">
-        <v>189</v>
-      </c>
-      <c r="F35" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" t="s">
-        <v>186</v>
-      </c>
-      <c r="C36" t="s">
-        <v>187</v>
-      </c>
-      <c r="D36" t="s">
-        <v>188</v>
-      </c>
-      <c r="E36" t="s">
-        <v>189</v>
-      </c>
-      <c r="F36" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" t="s">
-        <v>191</v>
-      </c>
-      <c r="C37" t="s">
-        <v>187</v>
-      </c>
-      <c r="D37" t="s">
-        <v>390</v>
-      </c>
-      <c r="E37" t="s">
-        <v>189</v>
-      </c>
-      <c r="F37" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" t="s">
-        <v>193</v>
-      </c>
-      <c r="C38" t="s">
-        <v>187</v>
-      </c>
-      <c r="D38" t="s">
-        <v>194</v>
-      </c>
-      <c r="E38" t="s">
-        <v>189</v>
-      </c>
-      <c r="F38" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" t="s">
-        <v>330</v>
-      </c>
-      <c r="C39" t="s">
-        <v>311</v>
-      </c>
-      <c r="D39" t="s">
-        <v>382</v>
-      </c>
-      <c r="E39" t="s">
-        <v>189</v>
-      </c>
-      <c r="F39" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" t="s">
-        <v>333</v>
-      </c>
-      <c r="C40" t="s">
-        <v>313</v>
-      </c>
-      <c r="D40" t="s">
-        <v>334</v>
-      </c>
-      <c r="E40" t="s">
-        <v>189</v>
-      </c>
-      <c r="F40" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" t="s">
-        <v>326</v>
-      </c>
-      <c r="C41" t="s">
-        <v>318</v>
-      </c>
-      <c r="D41" t="s">
-        <v>187</v>
-      </c>
-      <c r="E41" t="s">
-        <v>224</v>
-      </c>
-      <c r="F41" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" t="s">
-        <v>196</v>
-      </c>
-      <c r="C42" t="s">
-        <v>187</v>
-      </c>
-      <c r="D42" t="s">
-        <v>384</v>
-      </c>
-      <c r="E42" t="s">
-        <v>189</v>
-      </c>
-      <c r="F42" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" t="s">
-        <v>186</v>
-      </c>
-      <c r="C43" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" t="s">
-        <v>188</v>
-      </c>
-      <c r="E43" t="s">
-        <v>189</v>
-      </c>
-      <c r="F43" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" t="s">
-        <v>191</v>
-      </c>
-      <c r="C44" t="s">
-        <v>187</v>
-      </c>
-      <c r="D44" t="s">
-        <v>390</v>
-      </c>
-      <c r="E44" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" t="s">
-        <v>193</v>
-      </c>
-      <c r="C45" t="s">
-        <v>187</v>
-      </c>
-      <c r="D45" t="s">
-        <v>194</v>
-      </c>
-      <c r="E45" t="s">
-        <v>189</v>
-      </c>
-      <c r="F45" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" t="s">
-        <v>330</v>
-      </c>
-      <c r="C46" t="s">
-        <v>311</v>
-      </c>
-      <c r="D46" t="s">
-        <v>382</v>
-      </c>
-      <c r="E46" t="s">
-        <v>189</v>
-      </c>
-      <c r="F46" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" t="s">
-        <v>333</v>
-      </c>
-      <c r="C47" t="s">
-        <v>313</v>
-      </c>
-      <c r="D47" t="s">
-        <v>334</v>
-      </c>
-      <c r="E47" t="s">
-        <v>189</v>
-      </c>
-      <c r="F47" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" t="s">
-        <v>196</v>
-      </c>
-      <c r="D48" t="s">
-        <v>401</v>
-      </c>
-      <c r="E48" t="s">
-        <v>189</v>
-      </c>
-      <c r="F48" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" t="s">
-        <v>330</v>
-      </c>
-      <c r="C49" t="s">
-        <v>311</v>
-      </c>
-      <c r="D49" t="s">
-        <v>382</v>
-      </c>
-      <c r="E49" t="s">
-        <v>189</v>
-      </c>
-      <c r="F49" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>333</v>
-      </c>
-      <c r="C50" t="s">
-        <v>313</v>
-      </c>
-      <c r="D50" t="s">
-        <v>334</v>
-      </c>
-      <c r="E50" t="s">
-        <v>189</v>
-      </c>
-      <c r="F50" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" t="s">
-        <v>196</v>
-      </c>
-      <c r="D51" t="s">
-        <v>399</v>
-      </c>
-      <c r="E51" t="s">
-        <v>189</v>
-      </c>
-      <c r="F51" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" t="s">
-        <v>330</v>
-      </c>
-      <c r="C52" t="s">
-        <v>311</v>
-      </c>
-      <c r="D52" t="s">
-        <v>382</v>
-      </c>
-      <c r="E52" t="s">
-        <v>189</v>
-      </c>
-      <c r="F52" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" t="s">
-        <v>333</v>
-      </c>
-      <c r="C53" t="s">
-        <v>313</v>
-      </c>
-      <c r="D53" t="s">
-        <v>334</v>
-      </c>
-      <c r="E53" t="s">
-        <v>189</v>
-      </c>
-      <c r="F53" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" t="s">
-        <v>196</v>
-      </c>
-      <c r="D54" t="s">
-        <v>397</v>
-      </c>
-      <c r="E54" t="s">
-        <v>189</v>
-      </c>
-      <c r="F54" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" t="s">
-        <v>330</v>
-      </c>
-      <c r="C55" t="s">
-        <v>311</v>
-      </c>
-      <c r="D55" t="s">
-        <v>382</v>
-      </c>
-      <c r="E55" t="s">
-        <v>189</v>
-      </c>
-      <c r="F55" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" t="s">
-        <v>333</v>
-      </c>
-      <c r="C56" t="s">
-        <v>313</v>
-      </c>
-      <c r="D56" t="s">
-        <v>334</v>
-      </c>
-      <c r="E56" t="s">
-        <v>189</v>
-      </c>
-      <c r="F56" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57" t="s">
-        <v>196</v>
-      </c>
-      <c r="D57" t="s">
-        <v>395</v>
-      </c>
-      <c r="E57" t="s">
-        <v>189</v>
-      </c>
-      <c r="F57" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" t="s">
-        <v>330</v>
-      </c>
-      <c r="C58" t="s">
-        <v>311</v>
-      </c>
-      <c r="D58" t="s">
-        <v>382</v>
-      </c>
-      <c r="E58" t="s">
-        <v>189</v>
-      </c>
-      <c r="F58" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>49</v>
-      </c>
-      <c r="B59" t="s">
-        <v>333</v>
-      </c>
-      <c r="C59" t="s">
-        <v>313</v>
-      </c>
-      <c r="D59" t="s">
-        <v>334</v>
-      </c>
-      <c r="E59" t="s">
-        <v>189</v>
-      </c>
-      <c r="F59" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>49</v>
-      </c>
-      <c r="B60" t="s">
-        <v>196</v>
-      </c>
-      <c r="C60" t="s">
-        <v>187</v>
-      </c>
-      <c r="D60" t="s">
-        <v>393</v>
-      </c>
-      <c r="E60" t="s">
-        <v>189</v>
-      </c>
-      <c r="F60" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>54</v>
-      </c>
-      <c r="B61" t="s">
-        <v>186</v>
-      </c>
-      <c r="C61" t="s">
-        <v>187</v>
-      </c>
-      <c r="D61" t="s">
-        <v>188</v>
-      </c>
-      <c r="E61" t="s">
-        <v>189</v>
-      </c>
-      <c r="F61" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62" t="s">
-        <v>191</v>
-      </c>
-      <c r="C62" t="s">
-        <v>187</v>
-      </c>
-      <c r="D62" t="s">
-        <v>390</v>
-      </c>
-      <c r="E62" t="s">
-        <v>189</v>
-      </c>
-      <c r="F62" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" t="s">
-        <v>193</v>
-      </c>
-      <c r="C63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D63" t="s">
-        <v>194</v>
-      </c>
-      <c r="E63" t="s">
-        <v>189</v>
-      </c>
-      <c r="F63" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" t="s">
-        <v>333</v>
-      </c>
-      <c r="C64" t="s">
-        <v>314</v>
-      </c>
-      <c r="D64" t="s">
-        <v>334</v>
-      </c>
-      <c r="E64" t="s">
-        <v>189</v>
-      </c>
-      <c r="F64" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>54</v>
-      </c>
-      <c r="B65" t="s">
-        <v>351</v>
-      </c>
-      <c r="C65" t="s">
-        <v>316</v>
-      </c>
-      <c r="D65" t="s">
-        <v>352</v>
-      </c>
-      <c r="E65" t="s">
-        <v>189</v>
-      </c>
-      <c r="F65" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>54</v>
-      </c>
-      <c r="B66" t="s">
-        <v>196</v>
-      </c>
-      <c r="C66" t="s">
-        <v>187</v>
-      </c>
-      <c r="D66" t="s">
-        <v>336</v>
-      </c>
-      <c r="E66" t="s">
-        <v>189</v>
-      </c>
-      <c r="F66" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" t="s">
-        <v>186</v>
-      </c>
-      <c r="C67" t="s">
-        <v>187</v>
-      </c>
-      <c r="D67" t="s">
-        <v>188</v>
-      </c>
-      <c r="E67" t="s">
-        <v>189</v>
-      </c>
-      <c r="F67" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" t="s">
-        <v>187</v>
-      </c>
-      <c r="D68" t="s">
-        <v>390</v>
-      </c>
-      <c r="E68" t="s">
-        <v>189</v>
-      </c>
-      <c r="F68" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>58</v>
-      </c>
-      <c r="B69" t="s">
-        <v>193</v>
-      </c>
-      <c r="C69" t="s">
-        <v>187</v>
-      </c>
-      <c r="D69" t="s">
-        <v>194</v>
-      </c>
-      <c r="E69" t="s">
-        <v>189</v>
-      </c>
-      <c r="F69" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>58</v>
-      </c>
-      <c r="B70" t="s">
-        <v>333</v>
-      </c>
-      <c r="C70" t="s">
-        <v>314</v>
-      </c>
-      <c r="D70" t="s">
-        <v>334</v>
-      </c>
-      <c r="E70" t="s">
-        <v>189</v>
-      </c>
-      <c r="F70" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>58</v>
-      </c>
-      <c r="B71" t="s">
-        <v>351</v>
-      </c>
-      <c r="C71" t="s">
-        <v>316</v>
-      </c>
-      <c r="D71" t="s">
-        <v>354</v>
-      </c>
-      <c r="E71" t="s">
-        <v>189</v>
-      </c>
-      <c r="F71" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>58</v>
-      </c>
-      <c r="B72" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" t="s">
-        <v>320</v>
-      </c>
-      <c r="D72" t="s">
-        <v>187</v>
-      </c>
-      <c r="E72" t="s">
-        <v>189</v>
-      </c>
-      <c r="F72" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>58</v>
-      </c>
-      <c r="B73" t="s">
-        <v>196</v>
-      </c>
-      <c r="C73" t="s">
-        <v>187</v>
-      </c>
-      <c r="D73" t="s">
-        <v>357</v>
-      </c>
-      <c r="E73" t="s">
-        <v>189</v>
-      </c>
-      <c r="F73" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B74" t="s">
-        <v>186</v>
-      </c>
-      <c r="D74" t="s">
-        <v>188</v>
-      </c>
-      <c r="E74" t="s">
-        <v>189</v>
-      </c>
-      <c r="F74" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" t="s">
-        <v>191</v>
-      </c>
-      <c r="D75" t="s">
-        <v>390</v>
-      </c>
-      <c r="E75" t="s">
-        <v>189</v>
-      </c>
-      <c r="F75" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" t="s">
-        <v>193</v>
-      </c>
-      <c r="D76" t="s">
-        <v>194</v>
-      </c>
-      <c r="E76" t="s">
-        <v>189</v>
-      </c>
-      <c r="F76" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>62</v>
-      </c>
-      <c r="B77" t="s">
-        <v>333</v>
-      </c>
-      <c r="C77" t="s">
-        <v>314</v>
-      </c>
-      <c r="D77">
-        <v>10</v>
-      </c>
-      <c r="E77" t="s">
-        <v>189</v>
-      </c>
-      <c r="F77" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B78" t="s">
-        <v>351</v>
-      </c>
-      <c r="C78" t="s">
-        <v>316</v>
-      </c>
-      <c r="D78" t="s">
-        <v>354</v>
-      </c>
-      <c r="E78" t="s">
-        <v>189</v>
-      </c>
-      <c r="F78" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>62</v>
-      </c>
-      <c r="B79" t="s">
-        <v>196</v>
-      </c>
-      <c r="D79" t="s">
-        <v>357</v>
-      </c>
-      <c r="E79" t="s">
-        <v>189</v>
-      </c>
-      <c r="F79" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>62</v>
-      </c>
-      <c r="B80" t="s">
-        <v>333</v>
-      </c>
-      <c r="C80" t="s">
-        <v>405</v>
-      </c>
-      <c r="D80">
-        <v>10</v>
-      </c>
-      <c r="E80" t="s">
-        <v>189</v>
-      </c>
-      <c r="F80" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>62</v>
-      </c>
-      <c r="B81" t="s">
-        <v>351</v>
-      </c>
-      <c r="C81" t="s">
-        <v>316</v>
-      </c>
-      <c r="D81" t="s">
-        <v>354</v>
-      </c>
-      <c r="E81" t="s">
-        <v>189</v>
-      </c>
-      <c r="F81" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>62</v>
-      </c>
-      <c r="B82" t="s">
-        <v>196</v>
-      </c>
-      <c r="D82" t="s">
-        <v>357</v>
-      </c>
-      <c r="E82" t="s">
-        <v>189</v>
-      </c>
-      <c r="F82" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>62</v>
-      </c>
-      <c r="B83" t="s">
-        <v>333</v>
-      </c>
-      <c r="C83" t="s">
-        <v>405</v>
-      </c>
-      <c r="D83">
-        <v>10</v>
-      </c>
-      <c r="E83" t="s">
-        <v>189</v>
-      </c>
-      <c r="F83" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>62</v>
-      </c>
-      <c r="B84" t="s">
-        <v>351</v>
-      </c>
-      <c r="C84" t="s">
-        <v>316</v>
-      </c>
-      <c r="D84" t="s">
-        <v>354</v>
-      </c>
-      <c r="E84" t="s">
-        <v>189</v>
-      </c>
-      <c r="F84" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>62</v>
-      </c>
-      <c r="B85" t="s">
-        <v>196</v>
-      </c>
-      <c r="D85" t="s">
-        <v>357</v>
-      </c>
-      <c r="E85" t="s">
-        <v>189</v>
-      </c>
-      <c r="F85" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>62</v>
-      </c>
-      <c r="B86" t="s">
-        <v>333</v>
-      </c>
-      <c r="C86" t="s">
-        <v>405</v>
-      </c>
-      <c r="D86">
-        <v>10</v>
-      </c>
-      <c r="E86" t="s">
-        <v>189</v>
-      </c>
-      <c r="F86" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>62</v>
-      </c>
-      <c r="B87" t="s">
-        <v>351</v>
-      </c>
-      <c r="C87" t="s">
-        <v>316</v>
-      </c>
-      <c r="D87" t="s">
-        <v>354</v>
-      </c>
-      <c r="E87" t="s">
-        <v>189</v>
-      </c>
-      <c r="F87" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>62</v>
-      </c>
-      <c r="B88" t="s">
-        <v>196</v>
-      </c>
-      <c r="D88" t="s">
-        <v>357</v>
-      </c>
-      <c r="E88" t="s">
-        <v>189</v>
-      </c>
-      <c r="F88" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>62</v>
-      </c>
-      <c r="B89" t="s">
-        <v>333</v>
-      </c>
-      <c r="C89" t="s">
-        <v>405</v>
-      </c>
-      <c r="D89">
-        <v>10</v>
-      </c>
-      <c r="E89" t="s">
-        <v>189</v>
-      </c>
-      <c r="F89" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>62</v>
-      </c>
-      <c r="B90" t="s">
-        <v>351</v>
-      </c>
-      <c r="C90" t="s">
-        <v>316</v>
-      </c>
-      <c r="D90" t="s">
-        <v>354</v>
-      </c>
-      <c r="E90" t="s">
-        <v>189</v>
-      </c>
-      <c r="F90" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>62</v>
-      </c>
-      <c r="B91" t="s">
-        <v>196</v>
-      </c>
-      <c r="D91" t="s">
-        <v>357</v>
-      </c>
-      <c r="E91" t="s">
-        <v>189</v>
-      </c>
-      <c r="F91" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>62</v>
-      </c>
-      <c r="B92" t="s">
-        <v>333</v>
-      </c>
-      <c r="C92" t="s">
-        <v>405</v>
-      </c>
-      <c r="D92">
-        <v>10</v>
-      </c>
-      <c r="E92" t="s">
-        <v>189</v>
-      </c>
-      <c r="F92" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>62</v>
-      </c>
-      <c r="B93" t="s">
-        <v>351</v>
-      </c>
-      <c r="C93" t="s">
-        <v>316</v>
-      </c>
-      <c r="D93" t="s">
-        <v>354</v>
-      </c>
-      <c r="E93" t="s">
-        <v>189</v>
-      </c>
-      <c r="F93" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>62</v>
-      </c>
-      <c r="B94" t="s">
-        <v>196</v>
-      </c>
-      <c r="D94" t="s">
-        <v>418</v>
-      </c>
-      <c r="E94" t="s">
-        <v>189</v>
-      </c>
-      <c r="F94" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>65</v>
-      </c>
-      <c r="B95" t="s">
-        <v>186</v>
-      </c>
-      <c r="C95" t="s">
-        <v>187</v>
-      </c>
-      <c r="D95" t="s">
-        <v>188</v>
-      </c>
-      <c r="E95" t="s">
-        <v>189</v>
-      </c>
-      <c r="F95" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>65</v>
-      </c>
-      <c r="B96" t="s">
-        <v>191</v>
-      </c>
-      <c r="C96" t="s">
-        <v>187</v>
-      </c>
-      <c r="D96" t="s">
-        <v>390</v>
-      </c>
-      <c r="E96" t="s">
-        <v>189</v>
-      </c>
-      <c r="F96" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>65</v>
-      </c>
-      <c r="B97" t="s">
-        <v>193</v>
-      </c>
-      <c r="C97" t="s">
-        <v>187</v>
-      </c>
-      <c r="D97" t="s">
-        <v>194</v>
-      </c>
-      <c r="E97" t="s">
-        <v>189</v>
-      </c>
-      <c r="F97" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>65</v>
-      </c>
-      <c r="B98" t="s">
-        <v>333</v>
-      </c>
-      <c r="C98" t="s">
-        <v>322</v>
-      </c>
-      <c r="D98" t="s">
-        <v>334</v>
-      </c>
-      <c r="E98" t="s">
-        <v>189</v>
-      </c>
-      <c r="F98" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>65</v>
-      </c>
-      <c r="B99" t="s">
-        <v>333</v>
-      </c>
-      <c r="C99" t="s">
-        <v>324</v>
-      </c>
-      <c r="D99" t="s">
-        <v>334</v>
-      </c>
-      <c r="E99" t="s">
-        <v>189</v>
-      </c>
-      <c r="F99" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>65</v>
-      </c>
-      <c r="B100" t="s">
-        <v>330</v>
-      </c>
-      <c r="C100" t="s">
-        <v>311</v>
-      </c>
-      <c r="D100" t="s">
-        <v>331</v>
-      </c>
-      <c r="E100" t="s">
-        <v>189</v>
-      </c>
-      <c r="F100" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>65</v>
-      </c>
-      <c r="B101" t="s">
-        <v>333</v>
-      </c>
-      <c r="C101" t="s">
-        <v>313</v>
-      </c>
-      <c r="D101" t="s">
-        <v>334</v>
-      </c>
-      <c r="E101" t="s">
-        <v>189</v>
-      </c>
-      <c r="F101" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>65</v>
-      </c>
-      <c r="B102" t="s">
-        <v>196</v>
-      </c>
-      <c r="C102" t="s">
-        <v>187</v>
-      </c>
-      <c r="D102" t="s">
-        <v>336</v>
-      </c>
-      <c r="E102" t="s">
-        <v>189</v>
-      </c>
-      <c r="F102" t="s">
-        <v>200</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" style="34" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" style="34" customWidth="1"/>
     <col min="3" max="3" width="40.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="C1" s="22" t="s">
+    <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="32" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
+        <v>413</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
+        <v>415</v>
+      </c>
+      <c r="B3" s="33"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>345</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="33" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="B7" s="33" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C5" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>301</v>
-      </c>
-      <c r="B6" t="s">
-        <v>309</v>
-      </c>
-      <c r="C6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="33" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="33" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>301</v>
-      </c>
-      <c r="B8" t="s">
-        <v>368</v>
-      </c>
-      <c r="C8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9" t="s">
-        <v>369</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" t="s">
-        <v>380</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B11" t="s">
-        <v>370</v>
-      </c>
-      <c r="C11" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>301</v>
-      </c>
-      <c r="B12" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>301</v>
-      </c>
-      <c r="B13" t="s">
-        <v>376</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>301</v>
-      </c>
-      <c r="B14" t="s">
-        <v>377</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>301</v>
-      </c>
-      <c r="B15" t="s">
-        <v>387</v>
-      </c>
-      <c r="C15" t="s">
-        <v>388</v>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="33" t="s">
+        <v>417</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="33" t="s">
+        <v>418</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B1" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5747,210 +5878,211 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="103.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.77734375" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" customWidth="1"/>
+    <col min="3" max="3" width="95.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="C1" s="22" t="s">
+    <row r="1" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>286</v>
-      </c>
-      <c r="B3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B4" t="s">
-        <v>284</v>
-      </c>
-      <c r="C4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>292</v>
-      </c>
-      <c r="B6" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>296</v>
-      </c>
-      <c r="B8" t="s">
-        <v>284</v>
-      </c>
-      <c r="C8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>298</v>
-      </c>
-      <c r="B9" t="s">
-        <v>284</v>
-      </c>
-      <c r="C9" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>311</v>
-      </c>
-      <c r="B10" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B11" t="s">
-        <v>287</v>
-      </c>
-      <c r="C11" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B12" t="s">
-        <v>287</v>
-      </c>
-      <c r="C12" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>316</v>
-      </c>
-      <c r="B13" t="s">
-        <v>287</v>
-      </c>
-      <c r="C13" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>318</v>
-      </c>
-      <c r="B14" t="s">
-        <v>284</v>
-      </c>
-      <c r="C14" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>320</v>
-      </c>
-      <c r="B15" t="s">
-        <v>287</v>
-      </c>
-      <c r="C15" t="s">
-        <v>321</v>
-      </c>
-    </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>322</v>
-      </c>
-      <c r="B16" t="s">
-        <v>287</v>
-      </c>
-      <c r="C16" t="s">
-        <v>323</v>
+      <c r="A16" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>324</v>
-      </c>
-      <c r="B17" t="s">
-        <v>287</v>
-      </c>
-      <c r="C17" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>405</v>
-      </c>
-      <c r="B18" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" t="s">
-        <v>406</v>
+      <c r="A17" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5976,10 +6108,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="30"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -6008,10 +6140,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="29"/>
+      <c r="B2" s="30"/>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
@@ -6037,11 +6169,11 @@
       <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="30"/>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
@@ -6100,7 +6232,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>16</v>
@@ -6123,7 +6255,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>19</v>
@@ -6146,7 +6278,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>21</v>
@@ -6169,10 +6301,10 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>182</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>183</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>23</v>
@@ -6272,7 +6404,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>17</v>
@@ -6463,7 +6595,7 @@
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>66</v>
@@ -7135,7 +7267,7 @@
       </c>
       <c r="I47" s="18"/>
     </row>
-    <row r="48" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>155</v>
       </c>

--- a/src/test/resources/Login_TC.xlsx
+++ b/src/test/resources/Login_TC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\automation-framework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B2A31B-95CE-4230-BA58-4068D4BD7C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D442CC57-46D6-4E79-918A-C49F8178BF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="3" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="456">
   <si>
     <t>Created Date: 20/05/2025</t>
   </si>
@@ -1231,24 +1231,12 @@
     <t/>
   </si>
   <si>
-    <t>${base.url}</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
     <t>Open Beatchat login page</t>
   </si>
   <si>
-    <t>SSO login</t>
-  </si>
-  <si>
-    <t>${microsoftOtp}</t>
-  </si>
-  <si>
-    <t>Optional Microsoft MFA OTP</t>
-  </si>
-  <si>
     <t>User without security key should see setup suggestion</t>
   </si>
   <si>
@@ -1262,9 +1250,6 @@
   </si>
   <si>
     <t>Skip security key setup if displayed</t>
-  </si>
-  <si>
-    <t>${recipient}</t>
   </si>
   <si>
     <t>Search account and open chat</t>
@@ -1653,292 +1638,412 @@
     <t>Switch to QR login screen</t>
   </si>
   <si>
+    <t>Upload valid QR image</t>
+  </si>
+  <si>
+    <t>Upload invalid QR image</t>
+  </si>
+  <si>
+    <t>QR error should be displayed</t>
+  </si>
+  <si>
+    <t>QR Code  is incorrect, please try again!|QR Code is incorrect|please try again</t>
+  </si>
+  <si>
+    <t>QR error message should be displayed</t>
+  </si>
+  <si>
+    <t>Invalid QR upload attempt 1</t>
+  </si>
+  <si>
+    <t>Invalid QR upload attempt 2</t>
+  </si>
+  <si>
+    <t>Invalid QR upload attempt 3</t>
+  </si>
+  <si>
+    <t>Invalid QR upload attempt 4</t>
+  </si>
+  <si>
+    <t>Invalid QR upload attempt 5</t>
+  </si>
+  <si>
+    <t>Open forgot code flow</t>
+  </si>
+  <si>
+    <t>Cancel/back to PIN screen</t>
+  </si>
+  <si>
+    <t>Enter current passphrase</t>
+  </si>
+  <si>
+    <t>secure.email</t>
+  </si>
+  <si>
+    <t>secure.password</t>
+  </si>
+  <si>
+    <t>secure.passphrase</t>
+  </si>
+  <si>
+    <t>src\test\resources\QR login\Chivq9_UAT_QR.png</t>
+  </si>
+  <si>
+    <t>Fptchat@1234</t>
+  </si>
+  <si>
+    <t>nonSecure.email</t>
+  </si>
+  <si>
+    <t>nonSecure.password</t>
+  </si>
+  <si>
+    <t>fptchat01@fpt.com</t>
+  </si>
+  <si>
+    <t>Devteam@1234562</t>
+  </si>
+  <si>
+    <t>Invalid@1234</t>
+  </si>
+  <si>
+    <t>//button[@type='button' and (.//span[normalize-space()='Gửi' or normalize-space()='Send'] or normalize-space()='Gửi' or normalize-space()='Send')]</t>
+  </si>
+  <si>
+    <t>nonSecure.account</t>
+  </si>
+  <si>
+    <t>fptchat01</t>
+  </si>
+  <si>
+    <t>chivq9</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>You have entered the wrong PIN too many times. Please try again in 60 minutes.</t>
+  </si>
+  <si>
+    <t>After exactly 5 invalid PIN submissions, lock message must be displayed</t>
+  </si>
+  <si>
+    <t>1 attempts remaining|1 attempt remaining</t>
+  </si>
+  <si>
+    <t>After invalid PIN attempt 4</t>
+  </si>
+  <si>
+    <t>2 attempts remaining</t>
+  </si>
+  <si>
+    <t>After invalid PIN attempt 3</t>
+  </si>
+  <si>
+    <t>3 attempts remaining</t>
+  </si>
+  <si>
+    <t>After invalid PIN attempt 2</t>
+  </si>
+  <si>
+    <t>4 attempts remaining</t>
+  </si>
+  <si>
+    <t>After invalid PIN attempt 1</t>
+  </si>
+  <si>
+    <t>Nhập sai mã PIN 5 lần, mỗi lần hiển thị số attempts remaining giảm dần 4 &gt; 3 &gt; 2 &gt; 1, sau lần thứ 5 hiển thị message khóa 60 phút.</t>
+  </si>
+  <si>
+    <t>Verify đúng sequence lỗi nhập sai PIN và message lock sau 5 lần</t>
+  </si>
+  <si>
+    <t>security.qrDeleteButton</t>
+  </si>
+  <si>
+    <t>(//*[local-name()='svg' and @viewBox='0 0 24 24' and .//*[local-name()='path' and contains(@d,'M16 8') and contains(@d,'L16 16')]]/ancestor::*[self::button or @role='button' or contains(@class,'cursor-pointer')][1] | //*[local-name()='svg' and @viewBox='0 0 24 24' and .//*[local-name()='path' and contains(@d,'M16 8') and contains(@d,'L16 16')]])[1]</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 1</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 1</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 2</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 2</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 3</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 3</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 4</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 4</t>
+  </si>
+  <si>
+    <t>QR error should be displayed after attempt 5</t>
+  </si>
+  <si>
+    <t>Delete invalid QR after attempt 5</t>
+  </si>
+  <si>
+    <t>Invalid QR upload attempt 6</t>
+  </si>
+  <si>
+    <t>Bạn đã nhập sai mã PIN quá số lần cho phép. Vui lòng thử lại sau</t>
+  </si>
+  <si>
+    <t>After attempt 6, QR PIN limit message should be displayed</t>
+  </si>
+  <si>
+    <t>Upload QR sai 5 lần: mỗi lần hiển thị lỗi QR và cho phép xóa ảnh để upload lại. Lần upload sai thứ 6 hiển thị message: Bạn đã nhập sai mã PIN quá số lần cho phép. Vui lòng thử lại sau</t>
+  </si>
+  <si>
+    <t>Verify giới hạn upload QR sai: xóa QR giữa các lần upload, lock ở lần thứ 6</t>
+  </si>
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Assertion</t>
+  </si>
+  <si>
+    <t>OPEN_URL</t>
+  </si>
+  <si>
+    <t>VERIFY_TEXT</t>
+  </si>
+  <si>
+    <t>CONTAINS</t>
+  </si>
+  <si>
+    <t>VISIBLE</t>
+  </si>
+  <si>
+    <t>VERIFY_VISIBLE</t>
+  </si>
+  <si>
+    <t>INPUT</t>
+  </si>
+  <si>
+    <t>CLICK_DEEP</t>
+  </si>
+  <si>
+    <t>UPLOAD_FILE</t>
+  </si>
+  <si>
+    <t>KEY</t>
+  </si>
+  <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>base.url</t>
+  </si>
+  <si>
+    <t>https://beatchat.ai/</t>
+  </si>
+  <si>
+    <t>microsoftOtp</t>
+  </si>
+  <si>
+    <t>secure.invalidPassphrase</t>
+  </si>
+  <si>
+    <t>PK-005.recipient</t>
+  </si>
+  <si>
+    <t>PK-005.message</t>
+  </si>
+  <si>
+    <t>OBJECT</t>
+  </si>
+  <si>
+    <t>TYPE</t>
+  </si>
+  <si>
+    <t>Click SSO button</t>
+  </si>
+  <si>
+    <t>SWITCH_TO_NEW_WINDOW</t>
+  </si>
+  <si>
+    <t>Switch to auth window if opened</t>
+  </si>
+  <si>
+    <t>INPUT_IF_VISIBLE</t>
+  </si>
+  <si>
+    <t>microsoft.emailInput</t>
+  </si>
+  <si>
+    <t>Enter SSO email if requested</t>
+  </si>
+  <si>
+    <t>CLICK_IF_VISIBLE</t>
+  </si>
+  <si>
+    <t>microsoft.nextButton</t>
+  </si>
+  <si>
+    <t>Continue after email</t>
+  </si>
+  <si>
+    <t>microsoft.passwordInput</t>
+  </si>
+  <si>
+    <t>Enter SSO password if requested</t>
+  </si>
+  <si>
+    <t>Continue after password</t>
+  </si>
+  <si>
+    <t>microsoft.otpInput</t>
+  </si>
+  <si>
+    <t>Enter Microsoft OTP if provided</t>
+  </si>
+  <si>
+    <t>CLICK_IF_INPUT_PRESENT</t>
+  </si>
+  <si>
+    <t>microsoft.otpSubmitButton</t>
+  </si>
+  <si>
+    <t>Submit OTP only when OTP exists</t>
+  </si>
+  <si>
+    <t>microsoft.staySignedInYesButton</t>
+  </si>
+  <si>
+    <t>Confirm stay signed in when prompted</t>
+  </si>
+  <si>
+    <t>SWITCH_TO_WINDOW_WITH_VISIBLE</t>
+  </si>
+  <si>
+    <t>app.postLoginMarker</t>
+  </si>
+  <si>
+    <t>Return to app after SSO</t>
+  </si>
+  <si>
+    <t>WAIT_VISIBLE</t>
+  </si>
+  <si>
+    <t>app.chatReadyMarker</t>
+  </si>
+  <si>
+    <t>Wait until chat screen is ready</t>
+  </si>
+  <si>
+    <t>INPUT_EDITOR</t>
+  </si>
+  <si>
+    <t>Open account search result</t>
+  </si>
+  <si>
+    <t>Click send message</t>
+  </si>
+  <si>
+    <t>Wait for create group screen</t>
+  </si>
+  <si>
+    <t>app.messageIndicator</t>
+  </si>
+  <si>
+    <t>PIN code is incorrect|Pin code is incorrect|attempts remaining|incorrect|khong dung|khong hop le|Ma bao mat</t>
+  </si>
+  <si>
+    <t>security.qrUploadInput</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>i0116</t>
+  </si>
+  <si>
+    <t>i0118</t>
+  </si>
+  <si>
+    <t>idSIButton9</t>
+  </si>
+  <si>
+    <t>//input[contains(@aria-label,'Code') or contains(@placeholder,'Code') or @id='idTxtBx_SAOTCC_TD' or contains(@name,'otc') or @type='tel']</t>
+  </si>
+  <si>
+    <t>idSubmit_SAOTCC_Continue</t>
+  </si>
+  <si>
+    <t>//*[@id='acceptButton' or @id='idSIButton9' or @value='Yes' or normalize-space(.)='Yes']</t>
+  </si>
+  <si>
+    <t>//*[@id='root']//input | //button[.//span[normalize-space(.)='Bỏ qua'] or normalize-space(.)='Bỏ qua'] | //*[@data-placeholder='Search' or @data-placeholder='Message'] | //button[contains(@class,'send-btn')] | //span[contains(concat(' ',normalize-space(@class),' '),' slider ')]</t>
+  </si>
+  <si>
+    <t>//*[@role='alert' or @role='status' or @role='dialog' or contains(@class,'toast') or contains(@class,'notification') or contains(@class,'message') or contains(@class,'alert') or contains(@class,'tooltip')]</t>
+  </si>
+  <si>
+    <t>//input[@type='file']</t>
+  </si>
+  <si>
+    <t>${base.url}</t>
+  </si>
+  <si>
+    <t>${nonSecure.email}</t>
+  </si>
+  <si>
+    <t>${nonSecure.password}</t>
+  </si>
+  <si>
+    <t>${microsoftOtp}</t>
+  </si>
+  <si>
+    <t>${recipient}</t>
+  </si>
+  <si>
+    <t>${secure.email}</t>
+  </si>
+  <si>
+    <t>${secure.password}</t>
+  </si>
+  <si>
+    <t>${secure.passphrase}</t>
+  </si>
+  <si>
+    <t>${secure.invalidPassphrase}</t>
+  </si>
+  <si>
     <t>${qrValidPath}</t>
   </si>
   <si>
-    <t>Upload valid QR image</t>
-  </si>
-  <si>
     <t>${qrInvalidPath}</t>
   </si>
   <si>
-    <t>Upload invalid QR image</t>
-  </si>
-  <si>
-    <t>QR error should be displayed</t>
-  </si>
-  <si>
-    <t>QR Code  is incorrect, please try again!|QR Code is incorrect|please try again</t>
-  </si>
-  <si>
-    <t>QR error message should be displayed</t>
-  </si>
-  <si>
-    <t>Invalid QR upload attempt 1</t>
-  </si>
-  <si>
-    <t>Invalid QR upload attempt 2</t>
-  </si>
-  <si>
-    <t>Invalid QR upload attempt 3</t>
-  </si>
-  <si>
-    <t>Invalid QR upload attempt 4</t>
-  </si>
-  <si>
-    <t>Invalid QR upload attempt 5</t>
-  </si>
-  <si>
-    <t>Open forgot code flow</t>
-  </si>
-  <si>
-    <t>Cancel/back to PIN screen</t>
-  </si>
-  <si>
-    <t>Enter current passphrase</t>
-  </si>
-  <si>
-    <t>secure.email</t>
-  </si>
-  <si>
-    <t>secure.password</t>
-  </si>
-  <si>
-    <t>secure.passphrase</t>
-  </si>
-  <si>
-    <t>src\test\resources\QR login\Chivq9_UAT_QR.png</t>
-  </si>
-  <si>
-    <t>Fptchat@1234</t>
-  </si>
-  <si>
-    <t>nonSecure.email</t>
-  </si>
-  <si>
-    <t>nonSecure.password</t>
-  </si>
-  <si>
-    <t>fptchat01@fpt.com</t>
-  </si>
-  <si>
-    <t>Devteam@1234562</t>
-  </si>
-  <si>
-    <t>Invalid@1234</t>
-  </si>
-  <si>
-    <t>PIN code is incorrect|Pin code is incorrect|attempts remaining|incorrect|khÃ´ng Ä‘Ãºng|khÃ´ng há»£p lá»‡|MÃ£ báº£o máº­t</t>
-  </si>
-  <si>
-    <t>//button[@type='button' and (.//span[normalize-space()='Gửi' or normalize-space()='Send'] or normalize-space()='Gửi' or normalize-space()='Send')]</t>
-  </si>
-  <si>
-    <t>${nonSecure.email}|${nonSecure.password}</t>
-  </si>
-  <si>
-    <t>nonSecure.account</t>
-  </si>
-  <si>
-    <t>fptchat01</t>
-  </si>
-  <si>
-    <t>chivq9</t>
-  </si>
-  <si>
-    <t>${secure.email}|${secure.password}</t>
-  </si>
-  <si>
-    <t>${secure.passphrase}</t>
-  </si>
-  <si>
-    <t>Ready</t>
-  </si>
-  <si>
-    <t>You have entered the wrong PIN too many times. Please try again in 60 minutes.</t>
-  </si>
-  <si>
-    <t>After exactly 5 invalid PIN submissions, lock message must be displayed</t>
-  </si>
-  <si>
-    <t>1 attempts remaining|1 attempt remaining</t>
-  </si>
-  <si>
-    <t>After invalid PIN attempt 4</t>
-  </si>
-  <si>
-    <t>2 attempts remaining</t>
-  </si>
-  <si>
-    <t>After invalid PIN attempt 3</t>
-  </si>
-  <si>
-    <t>3 attempts remaining</t>
-  </si>
-  <si>
-    <t>After invalid PIN attempt 2</t>
-  </si>
-  <si>
-    <t>4 attempts remaining</t>
-  </si>
-  <si>
-    <t>After invalid PIN attempt 1</t>
-  </si>
-  <si>
-    <t>Nhập sai mã PIN 5 lần, mỗi lần hiển thị số attempts remaining giảm dần 4 &gt; 3 &gt; 2 &gt; 1, sau lần thứ 5 hiển thị message khóa 60 phút.</t>
-  </si>
-  <si>
-    <t>Verify đúng sequence lỗi nhập sai PIN và message lock sau 5 lần</t>
-  </si>
-  <si>
-    <t>security.qrDeleteButton</t>
-  </si>
-  <si>
-    <t>(//*[local-name()='svg' and @viewBox='0 0 24 24' and .//*[local-name()='path' and contains(@d,'M16 8') and contains(@d,'L16 16')]]/ancestor::*[self::button or @role='button' or contains(@class,'cursor-pointer')][1] | //*[local-name()='svg' and @viewBox='0 0 24 24' and .//*[local-name()='path' and contains(@d,'M16 8') and contains(@d,'L16 16')]])[1]</t>
-  </si>
-  <si>
-    <t>QR error should be displayed after attempt 1</t>
-  </si>
-  <si>
-    <t>Delete invalid QR after attempt 1</t>
-  </si>
-  <si>
-    <t>QR error should be displayed after attempt 2</t>
-  </si>
-  <si>
-    <t>Delete invalid QR after attempt 2</t>
-  </si>
-  <si>
-    <t>QR error should be displayed after attempt 3</t>
-  </si>
-  <si>
-    <t>Delete invalid QR after attempt 3</t>
-  </si>
-  <si>
-    <t>QR error should be displayed after attempt 4</t>
-  </si>
-  <si>
-    <t>Delete invalid QR after attempt 4</t>
-  </si>
-  <si>
-    <t>QR error should be displayed after attempt 5</t>
-  </si>
-  <si>
-    <t>Delete invalid QR after attempt 5</t>
-  </si>
-  <si>
-    <t>Invalid QR upload attempt 6</t>
-  </si>
-  <si>
-    <t>Bạn đã nhập sai mã PIN quá số lần cho phép. Vui lòng thử lại sau</t>
-  </si>
-  <si>
-    <t>After attempt 6, QR PIN limit message should be displayed</t>
-  </si>
-  <si>
-    <t>Upload QR sai 5 lần: mỗi lần hiển thị lỗi QR và cho phép xóa ảnh để upload lại. Lần upload sai thứ 6 hiển thị message: Bạn đã nhập sai mã PIN quá số lần cho phép. Vui lòng thử lại sau</t>
-  </si>
-  <si>
-    <t>Verify giới hạn upload QR sai: xóa QR giữa các lần upload, lock ở lần thứ 6</t>
-  </si>
-  <si>
-    <t>TC_ID</t>
-  </si>
-  <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Input</t>
-  </si>
-  <si>
-    <t>Assertion</t>
-  </si>
-  <si>
-    <t>OPEN_URL</t>
-  </si>
-  <si>
-    <t>LOGIN_WITH_MICROSOFT</t>
-  </si>
-  <si>
-    <t>ENTER_MICROSOFT_OTP</t>
-  </si>
-  <si>
-    <t>VERIFY_TEXT</t>
-  </si>
-  <si>
-    <t>CONTAINS</t>
-  </si>
-  <si>
-    <t>SKIP_SECURITY_KEY_SETUP</t>
-  </si>
-  <si>
-    <t>SEARCH_AND_OPEN_ACCOUNT</t>
-  </si>
-  <si>
-    <t>SEND_CHAT_MESSAGE</t>
-  </si>
-  <si>
-    <t>OPEN_CREATE_GROUP_CHAT</t>
-  </si>
-  <si>
-    <t>CLICK_SECURITY_LOCK</t>
-  </si>
-  <si>
-    <t>ASSERT_MESSAGE_VISIBLE</t>
-  </si>
-  <si>
-    <t>VISIBLE</t>
-  </si>
-  <si>
-    <t>VERIFY_VISIBLE</t>
-  </si>
-  <si>
-    <t>INPUT</t>
-  </si>
-  <si>
-    <t>CLICK_DEEP</t>
-  </si>
-  <si>
-    <t>${secure.invalidPassphrase}</t>
-  </si>
-  <si>
-    <t>UPLOAD_FILE</t>
-  </si>
-  <si>
-    <t>KEY</t>
-  </si>
-  <si>
-    <t>VALUE</t>
-  </si>
-  <si>
-    <t>base.url</t>
-  </si>
-  <si>
-    <t>https://beatchat.ai/</t>
-  </si>
-  <si>
-    <t>microsoftOtp</t>
-  </si>
-  <si>
-    <t>secure.invalidPassphrase</t>
-  </si>
-  <si>
-    <t>PK-005.recipient</t>
-  </si>
-  <si>
-    <t>PK-005.message</t>
-  </si>
-  <si>
-    <t>OBJECT</t>
-  </si>
-  <si>
-    <t>TYPE</t>
+    <t>Click Skip security key setup button</t>
+  </si>
+  <si>
+    <t>//*[contains(@class,'create-room') or contains(@class,'send-btn')] | //*[@data-placeholder='Search' or @data-placeholder='Message' or @data-placeholder='Tìm kiếm' or @data-placeholder='Tin nhắn'] | //*[@placeholder='Search' or @placeholder='Message' or @placeholder='Tìm kiếm' or @placeholder='Tin nhắn'] | //*[@aria-label='Search' or @aria-label='Message' or @aria-label='Tìm kiếm' or @aria-label='Tin nhắn']</t>
   </si>
 </sst>
 </file>
@@ -2242,6 +2347,13 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2251,13 +2363,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2589,7 +2694,7 @@
         <v>175</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>183</v>
@@ -2609,10 +2714,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -2629,10 +2734,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -2649,10 +2754,10 @@
         <v>20</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -2669,10 +2774,10 @@
         <v>22</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>182</v>
@@ -2681,7 +2786,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -2689,10 +2794,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -2709,10 +2814,10 @@
         <v>28</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D7" s="25" t="s">
         <v>30</v>
@@ -2721,7 +2826,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="25" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -2729,10 +2834,10 @@
         <v>31</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D8" s="25" t="s">
         <v>33</v>
@@ -2749,13 +2854,13 @@
         <v>35</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -2766,10 +2871,10 @@
         <v>39</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>41</v>
@@ -2786,10 +2891,10 @@
         <v>43</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>45</v>
@@ -2806,10 +2911,10 @@
         <v>46</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>48</v>
@@ -2826,19 +2931,19 @@
         <v>49</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -2846,10 +2951,10 @@
         <v>54</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>56</v>
@@ -2866,10 +2971,10 @@
         <v>58</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>60</v>
@@ -2878,7 +2983,7 @@
         <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="25" customFormat="1" x14ac:dyDescent="0.3">
@@ -2886,19 +2991,19 @@
         <v>62</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -2906,10 +3011,10 @@
         <v>65</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>66</v>
@@ -2926,10 +3031,10 @@
         <v>67</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D18" s="24" t="s">
         <v>70</v>
@@ -2946,10 +3051,10 @@
         <v>71</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C19" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D19" t="s">
         <v>73</v>
@@ -2966,10 +3071,10 @@
         <v>74</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C20" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s">
         <v>76</v>
@@ -2986,10 +3091,10 @@
         <v>77</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C21" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D21" t="s">
         <v>79</v>
@@ -3006,10 +3111,10 @@
         <v>80</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C22" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D22" t="s">
         <v>82</v>
@@ -3026,19 +3131,19 @@
         <v>83</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C23" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D23" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3046,10 +3151,10 @@
         <v>87</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C24" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D24" t="s">
         <v>89</v>
@@ -3058,7 +3163,7 @@
         <v>52</v>
       </c>
       <c r="F24" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3066,10 +3171,10 @@
         <v>91</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C25" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D25" t="s">
         <v>94</v>
@@ -3086,10 +3191,10 @@
         <v>95</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -3106,10 +3211,10 @@
         <v>98</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D27" t="s">
         <v>100</v>
@@ -3126,10 +3231,10 @@
         <v>101</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C28" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D28" t="s">
         <v>104</v>
@@ -3146,10 +3251,10 @@
         <v>105</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C29" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D29" t="s">
         <v>104</v>
@@ -3166,10 +3271,10 @@
         <v>107</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C30" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D30" t="s">
         <v>104</v>
@@ -3186,10 +3291,10 @@
         <v>109</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C31" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D31" t="s">
         <v>112</v>
@@ -3206,10 +3311,10 @@
         <v>113</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C32" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D32" t="s">
         <v>115</v>
@@ -3226,10 +3331,10 @@
         <v>116</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C33" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D33" t="s">
         <v>118</v>
@@ -3238,7 +3343,7 @@
         <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3246,10 +3351,10 @@
         <v>119</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
         <v>121</v>
@@ -3258,7 +3363,7 @@
         <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3266,10 +3371,10 @@
         <v>122</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C35" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D35" t="s">
         <v>125</v>
@@ -3286,10 +3391,10 @@
         <v>126</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C36" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
         <v>128</v>
@@ -3306,10 +3411,10 @@
         <v>129</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C37" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D37" t="s">
         <v>131</v>
@@ -3318,7 +3423,7 @@
         <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3326,10 +3431,10 @@
         <v>132</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D38" t="s">
         <v>135</v>
@@ -3346,10 +3451,10 @@
         <v>136</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C39" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D39" t="s">
         <v>138</v>
@@ -3366,10 +3471,10 @@
         <v>139</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C40" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D40" t="s">
         <v>141</v>
@@ -3386,10 +3491,10 @@
         <v>142</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C41" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D41" t="s">
         <v>145</v>
@@ -3406,10 +3511,10 @@
         <v>146</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C42" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D42" t="s">
         <v>148</v>
@@ -3426,13 +3531,13 @@
         <v>149</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C43" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D43" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -3446,10 +3551,10 @@
         <v>153</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C44" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D44" t="s">
         <v>76</v>
@@ -3466,10 +3571,10 @@
         <v>155</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C45" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D45" t="s">
         <v>157</v>
@@ -3486,10 +3591,10 @@
         <v>158</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C46" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
         <v>161</v>
@@ -3506,10 +3611,10 @@
         <v>162</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C47" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D47" t="s">
         <v>161</v>
@@ -3526,10 +3631,10 @@
         <v>165</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C48" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D48" t="s">
         <v>161</v>
@@ -3546,19 +3651,19 @@
         <v>167</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C49" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D49" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E49" t="s">
         <v>52</v>
       </c>
       <c r="F49" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3566,13 +3671,13 @@
         <v>172</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C50" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D50" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -3590,2145 +3695,4439 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" customWidth="1"/>
-    <col min="5" max="5" width="37.109375" customWidth="1"/>
-    <col min="6" max="6" width="61.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="6.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.77734375" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" customWidth="1"/>
+    <col min="5" max="5" width="24.21875" customWidth="1"/>
+    <col min="6" max="6" width="42.109375" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" customWidth="1"/>
     <col min="8" max="8" width="45.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>382</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="27">
+        <v>1</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="27">
+        <v>2</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" s="27">
+        <v>20</v>
+      </c>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="27">
+        <v>3</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27">
+        <v>8</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="27">
+        <v>4</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="27">
+        <v>5</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E6" s="27">
+        <v>20</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="27">
+        <v>6</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="27">
+        <v>7</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E8" s="27">
+        <v>20</v>
+      </c>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="27">
+        <v>8</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="27">
+        <v>9</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="27">
+        <v>10</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E11" s="27">
+        <v>12</v>
+      </c>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="27">
+        <v>11</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E12" s="27">
+        <v>180</v>
+      </c>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="27">
+        <v>12</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="27">
+        <v>1</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="27">
+        <v>2</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E15" s="27">
+        <v>20</v>
+      </c>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="27">
+        <v>3</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27">
+        <v>8</v>
+      </c>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="27">
+        <v>4</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="27">
+        <v>5</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E18" s="27">
+        <v>20</v>
+      </c>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="27">
+        <v>6</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="27">
+        <v>7</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E20" s="27">
+        <v>20</v>
+      </c>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="27">
+        <v>8</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="27">
+        <v>9</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="27">
+        <v>10</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E23" s="27">
+        <v>12</v>
+      </c>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="27">
+        <v>11</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E24" s="27">
+        <v>180</v>
+      </c>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="27">
+        <v>12</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" s="27">
+        <v>10</v>
+      </c>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="27">
+        <v>13</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="E26" s="27">
+        <v>30</v>
+      </c>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="27">
+        <v>14</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="G27" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H27" s="27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="27">
+        <v>1</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="27">
+        <v>2</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E29" s="27">
+        <v>20</v>
+      </c>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="27">
+        <v>3</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27">
+        <v>8</v>
+      </c>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="27">
+        <v>4</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="27">
+        <v>5</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E32" s="27">
+        <v>20</v>
+      </c>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="27">
+        <v>6</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="27">
+        <v>7</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E34" s="27">
+        <v>20</v>
+      </c>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="27">
+        <v>8</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D35" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E35" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" s="27">
+        <v>9</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D36" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="27">
+        <v>10</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E37" s="27">
+        <v>12</v>
+      </c>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="27">
+        <v>11</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D38" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E38" s="27">
+        <v>180</v>
+      </c>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="27">
+        <v>12</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="E39" s="27">
+        <v>10</v>
+      </c>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="27">
+        <v>13</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="D40" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="E40" s="27">
+        <v>30</v>
+      </c>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="27">
+        <v>14</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="E41" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="27">
+        <v>15</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="E42" s="27">
+        <v>10</v>
+      </c>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="27">
+        <v>16</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="27">
+        <v>17</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="E44" s="27">
+        <v>10</v>
+      </c>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="27">
+        <v>18</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H45" s="27" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" s="27">
+        <v>1</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" s="27">
+        <v>2</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E47" s="27">
+        <v>20</v>
+      </c>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="27">
+        <v>3</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27">
+        <v>8</v>
+      </c>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" s="27">
+        <v>4</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" s="27">
+        <v>5</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E50" s="27">
+        <v>20</v>
+      </c>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" s="27">
+        <v>6</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="27">
+        <v>7</v>
+      </c>
+      <c r="C52" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E52" s="27">
+        <v>20</v>
+      </c>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" s="27">
+        <v>8</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="27">
+        <v>9</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="27">
+        <v>10</v>
+      </c>
+      <c r="C55" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E55" s="27">
+        <v>12</v>
+      </c>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="27">
+        <v>11</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E56" s="27">
+        <v>180</v>
+      </c>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="27">
+        <v>12</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="E57" s="27">
+        <v>10</v>
+      </c>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="27">
+        <v>13</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="E58" s="27">
+        <v>30</v>
+      </c>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="27">
+        <v>14</v>
+      </c>
+      <c r="C59" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D59" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="E59" s="27">
+        <v>12</v>
+      </c>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="27">
+        <v>15</v>
+      </c>
+      <c r="C60" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="D60" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="E60" s="27">
+        <v>12</v>
+      </c>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="27">
+        <v>16</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D61" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="E61" s="27">
+        <v>10</v>
+      </c>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" s="27">
+        <v>17</v>
+      </c>
+      <c r="C62" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D62" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="H62" s="27" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" s="27">
+        <v>1</v>
+      </c>
+      <c r="C63" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" s="27">
+        <v>2</v>
+      </c>
+      <c r="C64" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D64" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E64" s="27">
+        <v>20</v>
+      </c>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" s="27">
+        <v>3</v>
+      </c>
+      <c r="C65" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27">
+        <v>8</v>
+      </c>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="27">
+        <v>4</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="27">
+        <v>5</v>
+      </c>
+      <c r="C67" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D67" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E67" s="27">
+        <v>20</v>
+      </c>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="27">
+        <v>6</v>
+      </c>
+      <c r="C68" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D68" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E68" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" s="27">
+        <v>7</v>
+      </c>
+      <c r="C69" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E69" s="27">
+        <v>20</v>
+      </c>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="27">
+        <v>8</v>
+      </c>
+      <c r="C70" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D70" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E70" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="27">
+        <v>9</v>
+      </c>
+      <c r="C71" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D71" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E71" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="27">
+        <v>10</v>
+      </c>
+      <c r="C72" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D72" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E72" s="27">
+        <v>12</v>
+      </c>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A73" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" s="27">
+        <v>11</v>
+      </c>
+      <c r="C73" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E73" s="27">
+        <v>180</v>
+      </c>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="H73" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B74" s="27">
+        <v>12</v>
+      </c>
+      <c r="C74" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E74" s="27"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="H74" s="27" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A75" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" s="27">
+        <v>13</v>
+      </c>
+      <c r="C75" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="G75" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H75" s="27" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B76" s="27">
+        <v>1</v>
+      </c>
+      <c r="C76" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F76" s="27"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B77" s="27">
+        <v>2</v>
+      </c>
+      <c r="C77" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D77" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E77" s="27">
+        <v>20</v>
+      </c>
+      <c r="F77" s="27"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" s="27">
+        <v>3</v>
+      </c>
+      <c r="C78" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27">
+        <v>8</v>
+      </c>
+      <c r="F78" s="27"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" s="27">
+        <v>4</v>
+      </c>
+      <c r="C79" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D79" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E79" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" s="27">
+        <v>5</v>
+      </c>
+      <c r="C80" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D80" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E80" s="27">
+        <v>20</v>
+      </c>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B81" s="27">
+        <v>6</v>
+      </c>
+      <c r="C81" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D81" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B82" s="27">
+        <v>7</v>
+      </c>
+      <c r="C82" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D82" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E82" s="27">
+        <v>20</v>
+      </c>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B83" s="27">
+        <v>8</v>
+      </c>
+      <c r="C83" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D83" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E83" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" s="27">
+        <v>9</v>
+      </c>
+      <c r="C84" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D84" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E84" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B85" s="27">
+        <v>10</v>
+      </c>
+      <c r="C85" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D85" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E85" s="27">
+        <v>12</v>
+      </c>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B86" s="27">
+        <v>11</v>
+      </c>
+      <c r="C86" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D86" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E86" s="27">
+        <v>180</v>
+      </c>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B87" s="27">
+        <v>12</v>
+      </c>
+      <c r="C87" s="27" t="s">
         <v>388</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="D87" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E87" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="27" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B88" s="27">
+        <v>13</v>
+      </c>
+      <c r="C88" s="27" t="s">
         <v>389</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="D88" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E88" s="27">
+        <v>10</v>
+      </c>
+      <c r="F88" s="27"/>
+      <c r="G88" s="27"/>
+      <c r="H88" s="27" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B89" s="27">
+        <v>14</v>
+      </c>
+      <c r="C89" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="G89" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H89" s="27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B90" s="27">
+        <v>1</v>
+      </c>
+      <c r="C90" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F90" s="27"/>
+      <c r="G90" s="27"/>
+      <c r="H90" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B91" s="27">
+        <v>2</v>
+      </c>
+      <c r="C91" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D91" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E91" s="27">
+        <v>20</v>
+      </c>
+      <c r="F91" s="27"/>
+      <c r="G91" s="27"/>
+      <c r="H91" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B92" s="27">
+        <v>3</v>
+      </c>
+      <c r="C92" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27">
+        <v>8</v>
+      </c>
+      <c r="F92" s="27"/>
+      <c r="G92" s="27"/>
+      <c r="H92" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B93" s="27">
+        <v>4</v>
+      </c>
+      <c r="C93" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D93" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E93" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="F93" s="27"/>
+      <c r="G93" s="27"/>
+      <c r="H93" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B94" s="27">
+        <v>5</v>
+      </c>
+      <c r="C94" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D94" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E94" s="27">
+        <v>20</v>
+      </c>
+      <c r="F94" s="27"/>
+      <c r="G94" s="27"/>
+      <c r="H94" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B95" s="27">
+        <v>6</v>
+      </c>
+      <c r="C95" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D95" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E95" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+      <c r="H95" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B96" s="27">
+        <v>7</v>
+      </c>
+      <c r="C96" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D96" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E96" s="27">
+        <v>20</v>
+      </c>
+      <c r="F96" s="27"/>
+      <c r="G96" s="27"/>
+      <c r="H96" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B97" s="27">
+        <v>8</v>
+      </c>
+      <c r="C97" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D97" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F97" s="27"/>
+      <c r="G97" s="27"/>
+      <c r="H97" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B98" s="27">
+        <v>9</v>
+      </c>
+      <c r="C98" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D98" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E98" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F98" s="27"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B99" s="27">
+        <v>10</v>
+      </c>
+      <c r="C99" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D99" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E99" s="27">
+        <v>12</v>
+      </c>
+      <c r="F99" s="27"/>
+      <c r="G99" s="27"/>
+      <c r="H99" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A100" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B100" s="27">
+        <v>11</v>
+      </c>
+      <c r="C100" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D100" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E100" s="27">
+        <v>180</v>
+      </c>
+      <c r="F100" s="27"/>
+      <c r="G100" s="27"/>
+      <c r="H100" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A101" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B101" s="27">
+        <v>12</v>
+      </c>
+      <c r="C101" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="D101" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="F101" s="27"/>
+      <c r="G101" s="27"/>
+      <c r="H101" s="27" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B102" s="27">
+        <v>13</v>
+      </c>
+      <c r="C102" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D102" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E102" s="27">
+        <v>10</v>
+      </c>
+      <c r="F102" s="27"/>
+      <c r="G102" s="27"/>
+      <c r="H102" s="27" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B103" s="27">
+        <v>14</v>
+      </c>
+      <c r="C103" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27" t="s">
+        <v>431</v>
+      </c>
+      <c r="G103" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H103" s="27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B104" s="27">
+        <v>1</v>
+      </c>
+      <c r="C104" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D104" s="27"/>
+      <c r="E104" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F104" s="27"/>
+      <c r="G104" s="27"/>
+      <c r="H104" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B105" s="27">
+        <v>2</v>
+      </c>
+      <c r="C105" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D105" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E105" s="27">
+        <v>20</v>
+      </c>
+      <c r="F105" s="27"/>
+      <c r="G105" s="27"/>
+      <c r="H105" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B106" s="27">
+        <v>3</v>
+      </c>
+      <c r="C106" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D106" s="27"/>
+      <c r="E106" s="27">
+        <v>8</v>
+      </c>
+      <c r="F106" s="27"/>
+      <c r="G106" s="27"/>
+      <c r="H106" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B107" s="27">
+        <v>4</v>
+      </c>
+      <c r="C107" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D107" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="F107" s="27"/>
+      <c r="G107" s="27"/>
+      <c r="H107" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B108" s="27">
+        <v>5</v>
+      </c>
+      <c r="C108" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D108" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E108" s="27">
+        <v>20</v>
+      </c>
+      <c r="F108" s="27"/>
+      <c r="G108" s="27"/>
+      <c r="H108" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B109" s="27">
+        <v>6</v>
+      </c>
+      <c r="C109" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D109" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E109" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F109" s="27"/>
+      <c r="G109" s="27"/>
+      <c r="H109" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B110" s="27">
+        <v>7</v>
+      </c>
+      <c r="C110" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D110" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E110" s="27">
+        <v>20</v>
+      </c>
+      <c r="F110" s="27"/>
+      <c r="G110" s="27"/>
+      <c r="H110" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B111" s="27">
+        <v>8</v>
+      </c>
+      <c r="C111" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D111" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E111" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F111" s="27"/>
+      <c r="G111" s="27"/>
+      <c r="H111" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B112" s="27">
+        <v>9</v>
+      </c>
+      <c r="C112" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D112" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E112" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F112" s="27"/>
+      <c r="G112" s="27"/>
+      <c r="H112" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B113" s="27">
+        <v>10</v>
+      </c>
+      <c r="C113" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D113" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E113" s="27">
+        <v>12</v>
+      </c>
+      <c r="F113" s="27"/>
+      <c r="G113" s="27"/>
+      <c r="H113" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A114" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B114" s="27">
+        <v>11</v>
+      </c>
+      <c r="C114" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D114" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E114" s="27">
+        <v>180</v>
+      </c>
+      <c r="F114" s="27"/>
+      <c r="G114" s="27"/>
+      <c r="H114" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A115" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B115" s="27">
+        <v>12</v>
+      </c>
+      <c r="C115" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="D115" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="F115" s="27"/>
+      <c r="G115" s="27"/>
+      <c r="H115" s="27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B116" s="27">
+        <v>13</v>
+      </c>
+      <c r="C116" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D116" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E116" s="27">
+        <v>10</v>
+      </c>
+      <c r="F116" s="27"/>
+      <c r="G116" s="27"/>
+      <c r="H116" s="27" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A117" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B117" s="27">
+        <v>14</v>
+      </c>
+      <c r="C117" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D117" s="27"/>
+      <c r="E117" s="27"/>
+      <c r="F117" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="G117" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H117" s="27" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A118" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B118" s="27">
+        <v>15</v>
+      </c>
+      <c r="C118" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="D118" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="F118" s="27"/>
+      <c r="G118" s="27"/>
+      <c r="H118" s="27" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B119" s="27">
+        <v>16</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D119" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E119" s="27">
+        <v>10</v>
+      </c>
+      <c r="F119" s="27"/>
+      <c r="G119" s="27"/>
+      <c r="H119" s="27" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A120" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B120" s="27">
+        <v>17</v>
+      </c>
+      <c r="C120" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D120" s="27"/>
+      <c r="E120" s="27"/>
+      <c r="F120" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="G120" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H120" s="27" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A121" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B121" s="27">
+        <v>18</v>
+      </c>
+      <c r="C121" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="D121" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="F121" s="27"/>
+      <c r="G121" s="27"/>
+      <c r="H121" s="27" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B122" s="27">
+        <v>19</v>
+      </c>
+      <c r="C122" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D122" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E122" s="27">
+        <v>10</v>
+      </c>
+      <c r="F122" s="27"/>
+      <c r="G122" s="27"/>
+      <c r="H122" s="27" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A123" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B123" s="27">
+        <v>20</v>
+      </c>
+      <c r="C123" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D123" s="27"/>
+      <c r="E123" s="27"/>
+      <c r="F123" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="G123" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H123" s="27" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A124" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B124" s="27">
+        <v>21</v>
+      </c>
+      <c r="C124" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="D124" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="F124" s="27"/>
+      <c r="G124" s="27"/>
+      <c r="H124" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B125" s="27">
+        <v>22</v>
+      </c>
+      <c r="C125" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D125" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E125" s="27">
+        <v>10</v>
+      </c>
+      <c r="F125" s="27"/>
+      <c r="G125" s="27"/>
+      <c r="H125" s="27" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A126" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B126" s="27">
+        <v>23</v>
+      </c>
+      <c r="C126" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="27"/>
+      <c r="F126" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="G126" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H126" s="27" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A127" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B127" s="27">
+        <v>24</v>
+      </c>
+      <c r="C127" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="D127" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E127" s="27" t="s">
+        <v>451</v>
+      </c>
+      <c r="F127" s="27"/>
+      <c r="G127" s="27"/>
+      <c r="H127" s="27" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B128" s="27">
+        <v>25</v>
+      </c>
+      <c r="C128" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D128" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E128" s="27">
+        <v>10</v>
+      </c>
+      <c r="F128" s="27"/>
+      <c r="G128" s="27"/>
+      <c r="H128" s="27" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A129" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B129" s="27">
+        <v>26</v>
+      </c>
+      <c r="C129" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D129" s="27"/>
+      <c r="E129" s="27"/>
+      <c r="F129" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="G129" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H129" s="27" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B130" s="27">
+        <v>1</v>
+      </c>
+      <c r="C130" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D130" s="27"/>
+      <c r="E130" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F130" s="27"/>
+      <c r="G130" s="27"/>
+      <c r="H130" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B131" s="27">
+        <v>2</v>
+      </c>
+      <c r="C131" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D131" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E131" s="27">
+        <v>20</v>
+      </c>
+      <c r="F131" s="27"/>
+      <c r="G131" s="27"/>
+      <c r="H131" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B132" s="27">
+        <v>3</v>
+      </c>
+      <c r="C132" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D132" s="27"/>
+      <c r="E132" s="27">
+        <v>8</v>
+      </c>
+      <c r="F132" s="27"/>
+      <c r="G132" s="27"/>
+      <c r="H132" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B133" s="27">
+        <v>4</v>
+      </c>
+      <c r="C133" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D133" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E133" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="F133" s="27"/>
+      <c r="G133" s="27"/>
+      <c r="H133" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B134" s="27">
+        <v>5</v>
+      </c>
+      <c r="C134" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D134" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E134" s="27">
+        <v>20</v>
+      </c>
+      <c r="F134" s="27"/>
+      <c r="G134" s="27"/>
+      <c r="H134" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B135" s="27">
+        <v>6</v>
+      </c>
+      <c r="C135" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D135" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E135" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
+      <c r="H135" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B136" s="27">
+        <v>7</v>
+      </c>
+      <c r="C136" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D136" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E136" s="27">
+        <v>20</v>
+      </c>
+      <c r="F136" s="27"/>
+      <c r="G136" s="27"/>
+      <c r="H136" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B137" s="27">
+        <v>8</v>
+      </c>
+      <c r="C137" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D137" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E137" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F137" s="27"/>
+      <c r="G137" s="27"/>
+      <c r="H137" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B138" s="27">
+        <v>9</v>
+      </c>
+      <c r="C138" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D138" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E138" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F138" s="27"/>
+      <c r="G138" s="27"/>
+      <c r="H138" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B139" s="27">
+        <v>10</v>
+      </c>
+      <c r="C139" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D139" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E139" s="27">
+        <v>12</v>
+      </c>
+      <c r="F139" s="27"/>
+      <c r="G139" s="27"/>
+      <c r="H139" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A140" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B140" s="27">
+        <v>11</v>
+      </c>
+      <c r="C140" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D140" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E140" s="27">
+        <v>180</v>
+      </c>
+      <c r="F140" s="27"/>
+      <c r="G140" s="27"/>
+      <c r="H140" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B141" s="27">
+        <v>12</v>
+      </c>
+      <c r="C141" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D141" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="E141" s="27">
+        <v>10</v>
+      </c>
+      <c r="F141" s="27"/>
+      <c r="G141" s="27"/>
+      <c r="H141" s="27" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B142" s="27">
+        <v>13</v>
+      </c>
+      <c r="C142" s="27" t="s">
         <v>390</v>
       </c>
-      <c r="D1" s="32" t="s">
-        <v>391</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>392</v>
-      </c>
-      <c r="F1" s="32" t="s">
+      <c r="D142" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E142" s="27" t="s">
+        <v>452</v>
+      </c>
+      <c r="F142" s="27"/>
+      <c r="G142" s="27"/>
+      <c r="H142" s="27" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A143" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B143" s="27">
+        <v>14</v>
+      </c>
+      <c r="C143" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D143" s="27"/>
+      <c r="E143" s="27"/>
+      <c r="F143" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="G143" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H143" s="27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B144" s="27">
+        <v>1</v>
+      </c>
+      <c r="C144" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D144" s="27"/>
+      <c r="E144" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F144" s="27"/>
+      <c r="G144" s="27"/>
+      <c r="H144" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B145" s="27">
+        <v>2</v>
+      </c>
+      <c r="C145" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D145" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E145" s="27">
+        <v>20</v>
+      </c>
+      <c r="F145" s="27"/>
+      <c r="G145" s="27"/>
+      <c r="H145" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B146" s="27">
+        <v>3</v>
+      </c>
+      <c r="C146" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D146" s="27"/>
+      <c r="E146" s="27">
+        <v>8</v>
+      </c>
+      <c r="F146" s="27"/>
+      <c r="G146" s="27"/>
+      <c r="H146" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B147" s="27">
+        <v>4</v>
+      </c>
+      <c r="C147" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D147" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E147" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="F147" s="27"/>
+      <c r="G147" s="27"/>
+      <c r="H147" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B148" s="27">
+        <v>5</v>
+      </c>
+      <c r="C148" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D148" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E148" s="27">
+        <v>20</v>
+      </c>
+      <c r="F148" s="27"/>
+      <c r="G148" s="27"/>
+      <c r="H148" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B149" s="27">
+        <v>6</v>
+      </c>
+      <c r="C149" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D149" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E149" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B150" s="27">
+        <v>7</v>
+      </c>
+      <c r="C150" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D150" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E150" s="27">
+        <v>20</v>
+      </c>
+      <c r="F150" s="27"/>
+      <c r="G150" s="27"/>
+      <c r="H150" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B151" s="27">
+        <v>8</v>
+      </c>
+      <c r="C151" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D151" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E151" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F151" s="27"/>
+      <c r="G151" s="27"/>
+      <c r="H151" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B152" s="27">
+        <v>9</v>
+      </c>
+      <c r="C152" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D152" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E152" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F152" s="27"/>
+      <c r="G152" s="27"/>
+      <c r="H152" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B153" s="27">
+        <v>10</v>
+      </c>
+      <c r="C153" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D153" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E153" s="27">
+        <v>12</v>
+      </c>
+      <c r="F153" s="27"/>
+      <c r="G153" s="27"/>
+      <c r="H153" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A154" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B154" s="27">
         <v>11</v>
       </c>
-      <c r="G1" s="32" t="s">
-        <v>393</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="C154" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D154" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E154" s="27">
+        <v>180</v>
+      </c>
+      <c r="F154" s="27"/>
+      <c r="G154" s="27"/>
+      <c r="H154" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B155" s="27">
+        <v>12</v>
+      </c>
+      <c r="C155" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D155" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="E155" s="27">
+        <v>10</v>
+      </c>
+      <c r="F155" s="27"/>
+      <c r="G155" s="27"/>
+      <c r="H155" s="27" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B156" s="27">
+        <v>13</v>
+      </c>
+      <c r="C156" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="D156" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E156" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="F156" s="27"/>
+      <c r="G156" s="27"/>
+      <c r="H156" s="27" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B157" s="27">
         <v>14</v>
       </c>
-      <c r="B2" s="33">
+      <c r="C157" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D157" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="E157" s="27"/>
+      <c r="F157" s="27"/>
+      <c r="G157" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="H157" s="27" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A158" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B158" s="27">
+        <v>15</v>
+      </c>
+      <c r="C158" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D158" s="27"/>
+      <c r="E158" s="27"/>
+      <c r="F158" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="G158" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H158" s="27" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B159" s="27">
         <v>1</v>
       </c>
-      <c r="C2" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="C159" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D159" s="27"/>
+      <c r="E159" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F159" s="27"/>
+      <c r="G159" s="27"/>
+      <c r="H159" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B160" s="27">
+        <v>2</v>
+      </c>
+      <c r="C160" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D160" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E160" s="27">
+        <v>20</v>
+      </c>
+      <c r="F160" s="27"/>
+      <c r="G160" s="27"/>
+      <c r="H160" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B161" s="27">
+        <v>3</v>
+      </c>
+      <c r="C161" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D161" s="27"/>
+      <c r="E161" s="27">
+        <v>8</v>
+      </c>
+      <c r="F161" s="27"/>
+      <c r="G161" s="27"/>
+      <c r="H161" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B162" s="27">
+        <v>4</v>
+      </c>
+      <c r="C162" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D162" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E162" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="F162" s="27"/>
+      <c r="G162" s="27"/>
+      <c r="H162" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B163" s="27">
+        <v>5</v>
+      </c>
+      <c r="C163" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D163" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E163" s="27">
+        <v>20</v>
+      </c>
+      <c r="F163" s="27"/>
+      <c r="G163" s="27"/>
+      <c r="H163" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B164" s="27">
+        <v>6</v>
+      </c>
+      <c r="C164" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D164" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E164" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F164" s="27"/>
+      <c r="G164" s="27"/>
+      <c r="H164" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B165" s="27">
+        <v>7</v>
+      </c>
+      <c r="C165" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D165" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E165" s="27">
+        <v>20</v>
+      </c>
+      <c r="F165" s="27"/>
+      <c r="G165" s="27"/>
+      <c r="H165" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B166" s="27">
+        <v>8</v>
+      </c>
+      <c r="C166" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D166" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E166" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F166" s="27"/>
+      <c r="G166" s="27"/>
+      <c r="H166" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B167" s="27">
+        <v>9</v>
+      </c>
+      <c r="C167" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D167" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E167" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F167" s="27"/>
+      <c r="G167" s="27"/>
+      <c r="H167" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B168" s="27">
+        <v>10</v>
+      </c>
+      <c r="C168" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D168" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E168" s="27">
+        <v>12</v>
+      </c>
+      <c r="F168" s="27"/>
+      <c r="G168" s="27"/>
+      <c r="H168" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A169" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B169" s="27">
+        <v>11</v>
+      </c>
+      <c r="C169" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D169" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E169" s="27">
+        <v>180</v>
+      </c>
+      <c r="F169" s="27"/>
+      <c r="G169" s="27"/>
+      <c r="H169" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B170" s="27">
+        <v>12</v>
+      </c>
+      <c r="C170" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D170" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="E170" s="27">
+        <v>10</v>
+      </c>
+      <c r="F170" s="27"/>
+      <c r="G170" s="27"/>
+      <c r="H170" s="27" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B171" s="27">
+        <v>13</v>
+      </c>
+      <c r="C171" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="D171" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E171" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="F171" s="27"/>
+      <c r="G171" s="27"/>
+      <c r="H171" s="27" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A172" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B172" s="27">
         <v>14</v>
       </c>
-      <c r="B3" s="33">
+      <c r="C172" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D172" s="27"/>
+      <c r="E172" s="27"/>
+      <c r="F172" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="G172" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H172" s="27" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B173" s="27">
+        <v>15</v>
+      </c>
+      <c r="C173" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D173" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E173" s="27">
+        <v>10</v>
+      </c>
+      <c r="F173" s="27"/>
+      <c r="G173" s="27"/>
+      <c r="H173" s="27" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B174" s="27">
+        <v>16</v>
+      </c>
+      <c r="C174" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="D174" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E174" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="F174" s="27"/>
+      <c r="G174" s="27"/>
+      <c r="H174" s="27" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A175" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B175" s="27">
+        <v>17</v>
+      </c>
+      <c r="C175" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D175" s="27"/>
+      <c r="E175" s="27"/>
+      <c r="F175" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="G175" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H175" s="27" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B176" s="27">
+        <v>18</v>
+      </c>
+      <c r="C176" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D176" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E176" s="27">
+        <v>10</v>
+      </c>
+      <c r="F176" s="27"/>
+      <c r="G176" s="27"/>
+      <c r="H176" s="27" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B177" s="27">
+        <v>19</v>
+      </c>
+      <c r="C177" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="D177" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E177" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="F177" s="27"/>
+      <c r="G177" s="27"/>
+      <c r="H177" s="27" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A178" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B178" s="27">
+        <v>20</v>
+      </c>
+      <c r="C178" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D178" s="27"/>
+      <c r="E178" s="27"/>
+      <c r="F178" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="G178" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H178" s="27" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B179" s="27">
+        <v>21</v>
+      </c>
+      <c r="C179" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D179" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E179" s="27">
+        <v>10</v>
+      </c>
+      <c r="F179" s="27"/>
+      <c r="G179" s="27"/>
+      <c r="H179" s="27" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B180" s="27">
+        <v>22</v>
+      </c>
+      <c r="C180" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="D180" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E180" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="F180" s="27"/>
+      <c r="G180" s="27"/>
+      <c r="H180" s="27" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A181" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B181" s="27">
+        <v>23</v>
+      </c>
+      <c r="C181" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D181" s="27"/>
+      <c r="E181" s="27"/>
+      <c r="F181" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="G181" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H181" s="27" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B182" s="27">
+        <v>24</v>
+      </c>
+      <c r="C182" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D182" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E182" s="27">
+        <v>10</v>
+      </c>
+      <c r="F182" s="27"/>
+      <c r="G182" s="27"/>
+      <c r="H182" s="27" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B183" s="27">
+        <v>25</v>
+      </c>
+      <c r="C183" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="D183" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E183" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="F183" s="27"/>
+      <c r="G183" s="27"/>
+      <c r="H183" s="27" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A184" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B184" s="27">
+        <v>26</v>
+      </c>
+      <c r="C184" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D184" s="27"/>
+      <c r="E184" s="27"/>
+      <c r="F184" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="G184" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H184" s="27" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B185" s="27">
+        <v>27</v>
+      </c>
+      <c r="C185" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D185" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E185" s="27">
+        <v>10</v>
+      </c>
+      <c r="F185" s="27"/>
+      <c r="G185" s="27"/>
+      <c r="H185" s="27" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B186" s="27">
+        <v>28</v>
+      </c>
+      <c r="C186" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="D186" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="E186" s="27" t="s">
+        <v>453</v>
+      </c>
+      <c r="F186" s="27"/>
+      <c r="G186" s="27"/>
+      <c r="H186" s="27" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A187" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B187" s="27">
+        <v>29</v>
+      </c>
+      <c r="C187" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D187" s="27"/>
+      <c r="E187" s="27"/>
+      <c r="F187" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="G187" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H187" s="27" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B188" s="27">
+        <v>1</v>
+      </c>
+      <c r="C188" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="D188" s="27"/>
+      <c r="E188" s="27" t="s">
+        <v>443</v>
+      </c>
+      <c r="F188" s="27"/>
+      <c r="G188" s="27"/>
+      <c r="H188" s="27" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B189" s="27">
         <v>2</v>
       </c>
-      <c r="C3" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33" t="s">
-        <v>352</v>
-      </c>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="C189" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D189" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="E189" s="27">
+        <v>20</v>
+      </c>
+      <c r="F189" s="27"/>
+      <c r="G189" s="27"/>
+      <c r="H189" s="27" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B190" s="27">
+        <v>3</v>
+      </c>
+      <c r="C190" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="D190" s="27"/>
+      <c r="E190" s="27">
+        <v>8</v>
+      </c>
+      <c r="F190" s="27"/>
+      <c r="G190" s="27"/>
+      <c r="H190" s="27" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B191" s="27">
+        <v>4</v>
+      </c>
+      <c r="C191" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D191" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="E191" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="F191" s="27"/>
+      <c r="G191" s="27"/>
+      <c r="H191" s="27" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B192" s="27">
+        <v>5</v>
+      </c>
+      <c r="C192" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D192" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E192" s="27">
+        <v>20</v>
+      </c>
+      <c r="F192" s="27"/>
+      <c r="G192" s="27"/>
+      <c r="H192" s="27" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B193" s="27">
+        <v>6</v>
+      </c>
+      <c r="C193" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D193" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="E193" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F193" s="27"/>
+      <c r="G193" s="27"/>
+      <c r="H193" s="27" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B194" s="27">
+        <v>7</v>
+      </c>
+      <c r="C194" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D194" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="E194" s="27">
+        <v>20</v>
+      </c>
+      <c r="F194" s="27"/>
+      <c r="G194" s="27"/>
+      <c r="H194" s="27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B195" s="27">
+        <v>8</v>
+      </c>
+      <c r="C195" s="27" t="s">
+        <v>404</v>
+      </c>
+      <c r="D195" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="E195" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F195" s="27"/>
+      <c r="G195" s="27"/>
+      <c r="H195" s="27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B196" s="27">
+        <v>9</v>
+      </c>
+      <c r="C196" s="27" t="s">
+        <v>415</v>
+      </c>
+      <c r="D196" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="E196" s="27" t="s">
+        <v>446</v>
+      </c>
+      <c r="F196" s="27"/>
+      <c r="G196" s="27"/>
+      <c r="H196" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B197" s="27">
+        <v>10</v>
+      </c>
+      <c r="C197" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="D197" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="E197" s="27">
+        <v>12</v>
+      </c>
+      <c r="F197" s="27"/>
+      <c r="G197" s="27"/>
+      <c r="H197" s="27" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A198" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B198" s="27">
+        <v>11</v>
+      </c>
+      <c r="C198" s="27" t="s">
+        <v>420</v>
+      </c>
+      <c r="D198" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="E198" s="27">
+        <v>180</v>
+      </c>
+      <c r="F198" s="27"/>
+      <c r="G198" s="27"/>
+      <c r="H198" s="27" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B199" s="27">
+        <v>12</v>
+      </c>
+      <c r="C199" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D199" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="E199" s="27">
+        <v>10</v>
+      </c>
+      <c r="F199" s="27"/>
+      <c r="G199" s="27"/>
+      <c r="H199" s="27" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B200" s="27">
+        <v>13</v>
+      </c>
+      <c r="C200" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D200" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="E200" s="27">
+        <v>10</v>
+      </c>
+      <c r="F200" s="27"/>
+      <c r="G200" s="27"/>
+      <c r="H200" s="27" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B201" s="27">
         <v>14</v>
       </c>
-      <c r="B4" s="33">
-        <v>3</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33" t="s">
+      <c r="C201" s="27" t="s">
+        <v>388</v>
+      </c>
+      <c r="D201" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="E201" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="F201" s="27"/>
+      <c r="G201" s="27"/>
+      <c r="H201" s="27" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B202" s="27">
+        <v>15</v>
+      </c>
+      <c r="C202" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="D202" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="E202" s="27">
+        <v>10</v>
+      </c>
+      <c r="F202" s="27"/>
+      <c r="G202" s="27"/>
+      <c r="H202" s="27" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A203" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B203" s="27">
+        <v>16</v>
+      </c>
+      <c r="C203" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="D203" s="27"/>
+      <c r="E203" s="27"/>
+      <c r="F203" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="G203" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="H203" s="27" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="33">
-        <v>4</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="33">
-        <v>1</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="33">
-        <v>2</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33" t="s">
-        <v>352</v>
-      </c>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="33">
-        <v>3</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="33">
-        <v>4</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>399</v>
-      </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="33">
-        <v>5</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="33">
-        <v>1</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="33">
-        <v>2</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33" t="s">
-        <v>352</v>
-      </c>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="33">
-        <v>3</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="33">
-        <v>4</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>399</v>
-      </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="33">
-        <v>5</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>400</v>
-      </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="33">
-        <v>6</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>401</v>
-      </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="33">
-        <v>7</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="G17" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H17" s="33" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="33">
-        <v>1</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="33">
-        <v>2</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33" t="s">
-        <v>352</v>
-      </c>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="33">
-        <v>3</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="33">
-        <v>4</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>399</v>
-      </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="33">
-        <v>5</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>402</v>
-      </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="33">
-        <v>6</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>403</v>
-      </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="33">
-        <v>7</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>404</v>
-      </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33" t="s">
-        <v>405</v>
-      </c>
-      <c r="H24" s="33" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="33">
-        <v>1</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="33">
-        <v>2</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="33">
-        <v>3</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="33">
-        <v>4</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>406</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33" t="s">
-        <v>405</v>
-      </c>
-      <c r="H28" s="33" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="33">
-        <v>5</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="G29" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H29" s="33" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="33">
-        <v>1</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="33">
-        <v>2</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="33">
-        <v>3</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="33">
-        <v>4</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="33">
-        <v>5</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D34" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="E34" s="33">
-        <v>10</v>
-      </c>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="33">
-        <v>6</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="G35" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H35" s="33" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="33">
-        <v>1</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="33">
-        <v>2</v>
-      </c>
-      <c r="C37" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="33">
-        <v>3</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="33">
-        <v>4</v>
-      </c>
-      <c r="C39" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E39" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="33">
-        <v>5</v>
-      </c>
-      <c r="C40" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="E40" s="33">
-        <v>10</v>
-      </c>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="33">
-        <v>6</v>
-      </c>
-      <c r="C41" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33" t="s">
-        <v>350</v>
-      </c>
-      <c r="G41" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H41" s="33" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="33">
-        <v>1</v>
-      </c>
-      <c r="C42" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="33">
-        <v>2</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="33">
-        <v>3</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" s="33">
-        <v>4</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D45" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E45" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="33">
-        <v>5</v>
-      </c>
-      <c r="C46" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D46" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="E46" s="33">
-        <v>10</v>
-      </c>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="33">
-        <v>6</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="G47" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H47" s="33" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="33">
-        <v>7</v>
-      </c>
-      <c r="C48" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D48" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E48" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="33">
-        <v>8</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="E49" s="33">
-        <v>10</v>
-      </c>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="33" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="33">
-        <v>9</v>
-      </c>
-      <c r="C50" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33" t="s">
-        <v>365</v>
-      </c>
-      <c r="G50" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H50" s="33" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="33">
-        <v>10</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E51" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="33">
-        <v>11</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D52" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="E52" s="33">
-        <v>10</v>
-      </c>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
-      <c r="H52" s="33" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" s="33">
-        <v>12</v>
-      </c>
-      <c r="C53" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="G53" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H53" s="33" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="33">
-        <v>13</v>
-      </c>
-      <c r="C54" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D54" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E54" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" s="33">
-        <v>14</v>
-      </c>
-      <c r="C55" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D55" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="E55" s="33">
-        <v>10</v>
-      </c>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" s="33">
-        <v>15</v>
-      </c>
-      <c r="C56" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="33" t="s">
-        <v>361</v>
-      </c>
-      <c r="G56" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H56" s="33" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57" s="33">
-        <v>16</v>
-      </c>
-      <c r="C57" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D57" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E57" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="33" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="33">
-        <v>17</v>
-      </c>
-      <c r="C58" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D58" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="E58" s="33">
-        <v>10</v>
-      </c>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B59" s="33">
-        <v>18</v>
-      </c>
-      <c r="C59" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33" t="s">
-        <v>359</v>
-      </c>
-      <c r="G59" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H59" s="33" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="33">
-        <v>1</v>
-      </c>
-      <c r="C60" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B61" s="33">
-        <v>2</v>
-      </c>
-      <c r="C61" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="F61" s="33"/>
-      <c r="G61" s="33"/>
-      <c r="H61" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62" s="33">
-        <v>3</v>
-      </c>
-      <c r="C62" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D62" s="33"/>
-      <c r="E62" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F62" s="33"/>
-      <c r="G62" s="33"/>
-      <c r="H62" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" s="33">
-        <v>4</v>
-      </c>
-      <c r="C63" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D63" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="E63" s="33">
-        <v>10</v>
-      </c>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="33">
-        <v>5</v>
-      </c>
-      <c r="C64" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="D64" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E64" s="33" t="s">
-        <v>325</v>
-      </c>
-      <c r="F64" s="33"/>
-      <c r="G64" s="33"/>
-      <c r="H64" s="33" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B65" s="33">
-        <v>6</v>
-      </c>
-      <c r="C65" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D65" s="33"/>
-      <c r="E65" s="33"/>
-      <c r="F65" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="G65" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H65" s="33" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="33">
-        <v>1</v>
-      </c>
-      <c r="C66" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D66" s="33"/>
-      <c r="E66" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F66" s="33"/>
-      <c r="G66" s="33"/>
-      <c r="H66" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" s="33">
-        <v>2</v>
-      </c>
-      <c r="C67" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="33">
-        <v>3</v>
-      </c>
-      <c r="C68" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D68" s="33"/>
-      <c r="E68" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F68" s="33"/>
-      <c r="G68" s="33"/>
-      <c r="H68" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B69" s="33">
-        <v>4</v>
-      </c>
-      <c r="C69" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D69" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="E69" s="33">
-        <v>10</v>
-      </c>
-      <c r="F69" s="33"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B70" s="33">
-        <v>5</v>
-      </c>
-      <c r="C70" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="D70" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E70" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="F70" s="33"/>
-      <c r="G70" s="33"/>
-      <c r="H70" s="33" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B71" s="33">
-        <v>6</v>
-      </c>
-      <c r="C71" s="33" t="s">
-        <v>406</v>
-      </c>
-      <c r="D71" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="E71" s="33"/>
-      <c r="F71" s="33"/>
-      <c r="G71" s="33" t="s">
-        <v>405</v>
-      </c>
-      <c r="H71" s="33" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="B72" s="33">
-        <v>7</v>
-      </c>
-      <c r="C72" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="G72" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H72" s="33" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B73" s="33">
-        <v>1</v>
-      </c>
-      <c r="C73" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D73" s="33"/>
-      <c r="E73" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F73" s="33"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B74" s="33">
-        <v>2</v>
-      </c>
-      <c r="C74" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D74" s="33"/>
-      <c r="E74" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="F74" s="33"/>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" s="33">
-        <v>3</v>
-      </c>
-      <c r="C75" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D75" s="33"/>
-      <c r="E75" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F75" s="33"/>
-      <c r="G75" s="33"/>
-      <c r="H75" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="33">
-        <v>4</v>
-      </c>
-      <c r="C76" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D76" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="E76" s="33">
-        <v>10</v>
-      </c>
-      <c r="F76" s="33"/>
-      <c r="G76" s="33"/>
-      <c r="H76" s="33" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B77" s="33">
-        <v>5</v>
-      </c>
-      <c r="C77" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="D77" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E77" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="F77" s="33"/>
-      <c r="G77" s="33"/>
-      <c r="H77" s="33" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B78" s="33">
-        <v>6</v>
-      </c>
-      <c r="C78" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="G78" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H78" s="33" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B79" s="33">
-        <v>7</v>
-      </c>
-      <c r="C79" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D79" s="33" t="s">
-        <v>371</v>
-      </c>
-      <c r="E79" s="33">
-        <v>10</v>
-      </c>
-      <c r="F79" s="33"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="33" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B80" s="33">
-        <v>8</v>
-      </c>
-      <c r="C80" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E80" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="F80" s="33"/>
-      <c r="G80" s="33"/>
-      <c r="H80" s="33" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B81" s="33">
-        <v>9</v>
-      </c>
-      <c r="C81" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D81" s="33"/>
-      <c r="E81" s="33"/>
-      <c r="F81" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="G81" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H81" s="33" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B82" s="33">
-        <v>10</v>
-      </c>
-      <c r="C82" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D82" s="33" t="s">
-        <v>371</v>
-      </c>
-      <c r="E82" s="33">
-        <v>10</v>
-      </c>
-      <c r="F82" s="33"/>
-      <c r="G82" s="33"/>
-      <c r="H82" s="33" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B83" s="33">
-        <v>11</v>
-      </c>
-      <c r="C83" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="D83" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E83" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="F83" s="33"/>
-      <c r="G83" s="33"/>
-      <c r="H83" s="33" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B84" s="33">
-        <v>12</v>
-      </c>
-      <c r="C84" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D84" s="33"/>
-      <c r="E84" s="33"/>
-      <c r="F84" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="G84" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H84" s="33" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B85" s="33">
-        <v>13</v>
-      </c>
-      <c r="C85" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D85" s="33" t="s">
-        <v>371</v>
-      </c>
-      <c r="E85" s="33">
-        <v>10</v>
-      </c>
-      <c r="F85" s="33"/>
-      <c r="G85" s="33"/>
-      <c r="H85" s="33" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B86" s="33">
-        <v>14</v>
-      </c>
-      <c r="C86" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E86" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="F86" s="33"/>
-      <c r="G86" s="33"/>
-      <c r="H86" s="33" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B87" s="33">
-        <v>15</v>
-      </c>
-      <c r="C87" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D87" s="33"/>
-      <c r="E87" s="33"/>
-      <c r="F87" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="G87" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H87" s="33" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B88" s="33">
-        <v>16</v>
-      </c>
-      <c r="C88" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D88" s="33" t="s">
-        <v>371</v>
-      </c>
-      <c r="E88" s="33">
-        <v>10</v>
-      </c>
-      <c r="F88" s="33"/>
-      <c r="G88" s="33"/>
-      <c r="H88" s="33" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B89" s="33">
-        <v>17</v>
-      </c>
-      <c r="C89" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="D89" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E89" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="F89" s="33"/>
-      <c r="G89" s="33"/>
-      <c r="H89" s="33" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B90" s="33">
-        <v>18</v>
-      </c>
-      <c r="C90" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D90" s="33"/>
-      <c r="E90" s="33"/>
-      <c r="F90" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="G90" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H90" s="33" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B91" s="33">
-        <v>19</v>
-      </c>
-      <c r="C91" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D91" s="33" t="s">
-        <v>371</v>
-      </c>
-      <c r="E91" s="33">
-        <v>10</v>
-      </c>
-      <c r="F91" s="33"/>
-      <c r="G91" s="33"/>
-      <c r="H91" s="33" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B92" s="33">
-        <v>20</v>
-      </c>
-      <c r="C92" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="D92" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E92" s="33" t="s">
-        <v>327</v>
-      </c>
-      <c r="F92" s="33"/>
-      <c r="G92" s="33"/>
-      <c r="H92" s="33" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="B93" s="33">
-        <v>21</v>
-      </c>
-      <c r="C93" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="33" t="s">
-        <v>384</v>
-      </c>
-      <c r="G93" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H93" s="33" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B94" s="33">
-        <v>1</v>
-      </c>
-      <c r="C94" s="33" t="s">
-        <v>394</v>
-      </c>
-      <c r="D94" s="33"/>
-      <c r="E94" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="F94" s="33"/>
-      <c r="G94" s="33"/>
-      <c r="H94" s="33" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B95" s="33">
-        <v>2</v>
-      </c>
-      <c r="C95" s="33" t="s">
-        <v>395</v>
-      </c>
-      <c r="D95" s="33"/>
-      <c r="E95" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="F95" s="33"/>
-      <c r="G95" s="33"/>
-      <c r="H95" s="33" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B96" s="33">
-        <v>3</v>
-      </c>
-      <c r="C96" s="33" t="s">
-        <v>396</v>
-      </c>
-      <c r="D96" s="33"/>
-      <c r="E96" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="F96" s="33"/>
-      <c r="G96" s="33"/>
-      <c r="H96" s="33" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B97" s="33">
-        <v>4</v>
-      </c>
-      <c r="C97" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D97" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="E97" s="33">
-        <v>10</v>
-      </c>
-      <c r="F97" s="33"/>
-      <c r="G97" s="33"/>
-      <c r="H97" s="33" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B98" s="33">
-        <v>5</v>
-      </c>
-      <c r="C98" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D98" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="E98" s="33">
-        <v>10</v>
-      </c>
-      <c r="F98" s="33"/>
-      <c r="G98" s="33"/>
-      <c r="H98" s="33" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B99" s="33">
-        <v>6</v>
-      </c>
-      <c r="C99" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="D99" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E99" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="F99" s="33"/>
-      <c r="G99" s="33"/>
-      <c r="H99" s="33" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B100" s="33">
-        <v>7</v>
-      </c>
-      <c r="C100" s="33" t="s">
-        <v>408</v>
-      </c>
-      <c r="D100" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="E100" s="33">
-        <v>10</v>
-      </c>
-      <c r="F100" s="33"/>
-      <c r="G100" s="33"/>
-      <c r="H100" s="33" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B101" s="33">
-        <v>8</v>
-      </c>
-      <c r="C101" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="D101" s="33"/>
-      <c r="E101" s="33"/>
-      <c r="F101" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="G101" s="33" t="s">
-        <v>398</v>
-      </c>
-      <c r="H101" s="33" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -5743,127 +8142,127 @@
   <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" style="34" customWidth="1"/>
-    <col min="2" max="2" width="70.77734375" style="34" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" style="31" customWidth="1"/>
+    <col min="2" max="2" width="70.77734375" style="31" customWidth="1"/>
     <col min="3" max="3" width="40.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>412</v>
+      <c r="A1" s="29" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>413</v>
-      </c>
-      <c r="B2" s="33" t="s">
-        <v>414</v>
+      <c r="A2" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
-        <v>415</v>
-      </c>
-      <c r="B3" s="33"/>
+      <c r="A3" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="B3" s="30"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B6" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="B4" s="33" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="30" t="s">
+        <v>396</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="B14" s="30" t="s">
         <v>346</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="33" t="s">
-        <v>353</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
-        <v>340</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
-        <v>416</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="33" t="s">
-        <v>417</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>355</v>
-      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="33" t="s">
-        <v>418</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>281</v>
+      <c r="A15" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -5875,210 +8274,320 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.77734375" customWidth="1"/>
+    <col min="1" max="1" width="36.77734375" customWidth="1"/>
     <col min="2" max="2" width="14.77734375" customWidth="1"/>
-    <col min="3" max="3" width="95.77734375" customWidth="1"/>
+    <col min="3" max="3" width="120.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B4" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>264</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="27" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="27" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>372</v>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>433</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>433</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>433</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="27" t="s">
+        <v>416</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>433</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="27" t="s">
+        <v>418</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="27" t="s">
+        <v>424</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="27" t="s">
+        <v>430</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="27" t="s">
+        <v>432</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -6108,10 +8617,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -6140,10 +8649,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
@@ -6169,11 +8678,11 @@
       <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="30"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="33"/>
       <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
@@ -6404,7 +8913,7 @@
         <v>37</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>17</v>
@@ -6595,7 +9104,7 @@
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>66</v>
@@ -7267,7 +9776,7 @@
       </c>
       <c r="I47" s="18"/>
     </row>
-    <row r="48" spans="1:9" ht="69.599999999999994" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>155</v>
       </c>

--- a/src/test/resources/Login_TC.xlsx
+++ b/src/test/resources/Login_TC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\automation-framework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D442CC57-46D6-4E79-918A-C49F8178BF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3F4CDE-8361-4BAF-82AD-F62F409E5C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
   </bookViews>
@@ -1995,9 +1995,6 @@
     <t>idSubmit_SAOTCC_Continue</t>
   </si>
   <si>
-    <t>//*[@id='acceptButton' or @id='idSIButton9' or @value='Yes' or normalize-space(.)='Yes']</t>
-  </si>
-  <si>
     <t>//*[@id='root']//input | //button[.//span[normalize-space(.)='Bỏ qua'] or normalize-space(.)='Bỏ qua'] | //*[@data-placeholder='Search' or @data-placeholder='Message'] | //button[contains(@class,'send-btn')] | //span[contains(concat(' ',normalize-space(@class),' '),' slider ')]</t>
   </si>
   <si>
@@ -2044,6 +2041,9 @@
   </si>
   <si>
     <t>//*[contains(@class,'create-room') or contains(@class,'send-btn')] | //*[@data-placeholder='Search' or @data-placeholder='Message' or @data-placeholder='Tìm kiếm' or @data-placeholder='Tin nhắn'] | //*[@placeholder='Search' or @placeholder='Message' or @placeholder='Tìm kiếm' or @placeholder='Tin nhắn'] | //*[@aria-label='Search' or @aria-label='Message' or @aria-label='Tìm kiếm' or @aria-label='Tin nhắn']</t>
+  </si>
+  <si>
+    <t>//*[@id='acceptButton' or @id='idSIButton9' or @value='Yes' or @aria-label='Yes' or @title='Yes' or normalize-space(.)='Yes']</t>
   </si>
 </sst>
 </file>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F2" s="27"/>
       <c r="G2" s="27"/>
@@ -3810,7 +3810,7 @@
         <v>405</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="27"/>
@@ -3854,7 +3854,7 @@
         <v>410</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F7" s="27"/>
       <c r="G7" s="27"/>
@@ -3898,7 +3898,7 @@
         <v>413</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F9" s="27"/>
       <c r="G9" s="27"/>
@@ -3920,7 +3920,7 @@
         <v>416</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
@@ -3942,7 +3942,7 @@
         <v>418</v>
       </c>
       <c r="E11" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F14" s="27"/>
       <c r="G14" s="27"/>
@@ -4070,7 +4070,7 @@
         <v>405</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F17" s="27"/>
       <c r="G17" s="27"/>
@@ -4114,7 +4114,7 @@
         <v>410</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F19" s="27"/>
       <c r="G19" s="27"/>
@@ -4158,7 +4158,7 @@
         <v>413</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F21" s="27"/>
       <c r="G21" s="27"/>
@@ -4180,7 +4180,7 @@
         <v>416</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F22" s="27"/>
       <c r="G22" s="27"/>
@@ -4202,7 +4202,7 @@
         <v>418</v>
       </c>
       <c r="E23" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F23" s="27"/>
       <c r="G23" s="27"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="D28" s="27"/>
       <c r="E28" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
@@ -4374,7 +4374,7 @@
         <v>405</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
@@ -4418,7 +4418,7 @@
         <v>410</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F33" s="27"/>
       <c r="G33" s="27"/>
@@ -4462,7 +4462,7 @@
         <v>413</v>
       </c>
       <c r="E35" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F35" s="27"/>
       <c r="G35" s="27"/>
@@ -4484,7 +4484,7 @@
         <v>416</v>
       </c>
       <c r="E36" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F36" s="27"/>
       <c r="G36" s="27"/>
@@ -4506,7 +4506,7 @@
         <v>418</v>
       </c>
       <c r="E37" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F37" s="27"/>
       <c r="G37" s="27"/>
@@ -4594,7 +4594,7 @@
         <v>263</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F41" s="27"/>
       <c r="G41" s="27"/>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D46" s="27"/>
       <c r="E46" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F46" s="27"/>
       <c r="G46" s="27"/>
@@ -4766,7 +4766,7 @@
         <v>405</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F49" s="27"/>
       <c r="G49" s="27"/>
@@ -4810,7 +4810,7 @@
         <v>410</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F51" s="27"/>
       <c r="G51" s="27"/>
@@ -4854,7 +4854,7 @@
         <v>413</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F53" s="27"/>
       <c r="G53" s="27"/>
@@ -4876,7 +4876,7 @@
         <v>416</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F54" s="27"/>
       <c r="G54" s="27"/>
@@ -4898,7 +4898,7 @@
         <v>418</v>
       </c>
       <c r="E55" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F55" s="27"/>
       <c r="G55" s="27"/>
@@ -4947,7 +4947,7 @@
       <c r="F57" s="27"/>
       <c r="G57" s="27"/>
       <c r="H57" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="D63" s="27"/>
       <c r="E63" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F63" s="27"/>
       <c r="G63" s="27"/>
@@ -5136,7 +5136,7 @@
         <v>405</v>
       </c>
       <c r="E66" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F66" s="27"/>
       <c r="G66" s="27"/>
@@ -5180,7 +5180,7 @@
         <v>410</v>
       </c>
       <c r="E68" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F68" s="27"/>
       <c r="G68" s="27"/>
@@ -5224,7 +5224,7 @@
         <v>413</v>
       </c>
       <c r="E70" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F70" s="27"/>
       <c r="G70" s="27"/>
@@ -5246,7 +5246,7 @@
         <v>416</v>
       </c>
       <c r="E71" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F71" s="27"/>
       <c r="G71" s="27"/>
@@ -5268,7 +5268,7 @@
         <v>418</v>
       </c>
       <c r="E72" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F72" s="27"/>
       <c r="G72" s="27"/>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F76" s="27"/>
       <c r="G76" s="27"/>
@@ -5418,7 +5418,7 @@
         <v>405</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F79" s="27"/>
       <c r="G79" s="27"/>
@@ -5462,7 +5462,7 @@
         <v>410</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F81" s="27"/>
       <c r="G81" s="27"/>
@@ -5506,7 +5506,7 @@
         <v>413</v>
       </c>
       <c r="E83" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F83" s="27"/>
       <c r="G83" s="27"/>
@@ -5528,7 +5528,7 @@
         <v>416</v>
       </c>
       <c r="E84" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F84" s="27"/>
       <c r="G84" s="27"/>
@@ -5550,7 +5550,7 @@
         <v>418</v>
       </c>
       <c r="E85" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F85" s="27"/>
       <c r="G85" s="27"/>
@@ -5594,7 +5594,7 @@
         <v>285</v>
       </c>
       <c r="E87" s="27" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F87" s="27"/>
       <c r="G87" s="27"/>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F90" s="27"/>
       <c r="G90" s="27"/>
@@ -5722,7 +5722,7 @@
         <v>405</v>
       </c>
       <c r="E93" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F93" s="27"/>
       <c r="G93" s="27"/>
@@ -5766,7 +5766,7 @@
         <v>410</v>
       </c>
       <c r="E95" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F95" s="27"/>
       <c r="G95" s="27"/>
@@ -5810,7 +5810,7 @@
         <v>413</v>
       </c>
       <c r="E97" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F97" s="27"/>
       <c r="G97" s="27"/>
@@ -5832,7 +5832,7 @@
         <v>416</v>
       </c>
       <c r="E98" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F98" s="27"/>
       <c r="G98" s="27"/>
@@ -5854,7 +5854,7 @@
         <v>418</v>
       </c>
       <c r="E99" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F99" s="27"/>
       <c r="G99" s="27"/>
@@ -5898,7 +5898,7 @@
         <v>285</v>
       </c>
       <c r="E101" s="27" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F101" s="27"/>
       <c r="G101" s="27"/>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D104" s="27"/>
       <c r="E104" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F104" s="27"/>
       <c r="G104" s="27"/>
@@ -6026,7 +6026,7 @@
         <v>405</v>
       </c>
       <c r="E107" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F107" s="27"/>
       <c r="G107" s="27"/>
@@ -6070,7 +6070,7 @@
         <v>410</v>
       </c>
       <c r="E109" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F109" s="27"/>
       <c r="G109" s="27"/>
@@ -6114,7 +6114,7 @@
         <v>413</v>
       </c>
       <c r="E111" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F111" s="27"/>
       <c r="G111" s="27"/>
@@ -6136,7 +6136,7 @@
         <v>416</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F112" s="27"/>
       <c r="G112" s="27"/>
@@ -6158,7 +6158,7 @@
         <v>418</v>
       </c>
       <c r="E113" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F113" s="27"/>
       <c r="G113" s="27"/>
@@ -6202,7 +6202,7 @@
         <v>285</v>
       </c>
       <c r="E115" s="27" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F115" s="27"/>
       <c r="G115" s="27"/>
@@ -6268,7 +6268,7 @@
         <v>285</v>
       </c>
       <c r="E118" s="27" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F118" s="27"/>
       <c r="G118" s="27"/>
@@ -6334,7 +6334,7 @@
         <v>285</v>
       </c>
       <c r="E121" s="27" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F121" s="27"/>
       <c r="G121" s="27"/>
@@ -6400,7 +6400,7 @@
         <v>285</v>
       </c>
       <c r="E124" s="27" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F124" s="27"/>
       <c r="G124" s="27"/>
@@ -6466,7 +6466,7 @@
         <v>285</v>
       </c>
       <c r="E127" s="27" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F127" s="27"/>
       <c r="G127" s="27"/>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D130" s="27"/>
       <c r="E130" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F130" s="27"/>
       <c r="G130" s="27"/>
@@ -6594,7 +6594,7 @@
         <v>405</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F133" s="27"/>
       <c r="G133" s="27"/>
@@ -6638,7 +6638,7 @@
         <v>410</v>
       </c>
       <c r="E135" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F135" s="27"/>
       <c r="G135" s="27"/>
@@ -6682,7 +6682,7 @@
         <v>413</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F137" s="27"/>
       <c r="G137" s="27"/>
@@ -6704,7 +6704,7 @@
         <v>416</v>
       </c>
       <c r="E138" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F138" s="27"/>
       <c r="G138" s="27"/>
@@ -6726,7 +6726,7 @@
         <v>418</v>
       </c>
       <c r="E139" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F139" s="27"/>
       <c r="G139" s="27"/>
@@ -6792,7 +6792,7 @@
         <v>432</v>
       </c>
       <c r="E142" s="27" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F142" s="27"/>
       <c r="G142" s="27"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D144" s="27"/>
       <c r="E144" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F144" s="27"/>
       <c r="G144" s="27"/>
@@ -6898,7 +6898,7 @@
         <v>405</v>
       </c>
       <c r="E147" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F147" s="27"/>
       <c r="G147" s="27"/>
@@ -6942,7 +6942,7 @@
         <v>410</v>
       </c>
       <c r="E149" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F149" s="27"/>
       <c r="G149" s="27"/>
@@ -6986,7 +6986,7 @@
         <v>413</v>
       </c>
       <c r="E151" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F151" s="27"/>
       <c r="G151" s="27"/>
@@ -7008,7 +7008,7 @@
         <v>416</v>
       </c>
       <c r="E152" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F152" s="27"/>
       <c r="G152" s="27"/>
@@ -7030,7 +7030,7 @@
         <v>418</v>
       </c>
       <c r="E153" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F153" s="27"/>
       <c r="G153" s="27"/>
@@ -7096,7 +7096,7 @@
         <v>432</v>
       </c>
       <c r="E156" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F156" s="27"/>
       <c r="G156" s="27"/>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="D159" s="27"/>
       <c r="E159" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F159" s="27"/>
       <c r="G159" s="27"/>
@@ -7224,7 +7224,7 @@
         <v>405</v>
       </c>
       <c r="E162" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F162" s="27"/>
       <c r="G162" s="27"/>
@@ -7268,7 +7268,7 @@
         <v>410</v>
       </c>
       <c r="E164" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F164" s="27"/>
       <c r="G164" s="27"/>
@@ -7312,7 +7312,7 @@
         <v>413</v>
       </c>
       <c r="E166" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F166" s="27"/>
       <c r="G166" s="27"/>
@@ -7334,7 +7334,7 @@
         <v>416</v>
       </c>
       <c r="E167" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F167" s="27"/>
       <c r="G167" s="27"/>
@@ -7356,7 +7356,7 @@
         <v>418</v>
       </c>
       <c r="E168" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F168" s="27"/>
       <c r="G168" s="27"/>
@@ -7422,7 +7422,7 @@
         <v>432</v>
       </c>
       <c r="E171" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F171" s="27"/>
       <c r="G171" s="27"/>
@@ -7488,7 +7488,7 @@
         <v>432</v>
       </c>
       <c r="E174" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F174" s="27"/>
       <c r="G174" s="27"/>
@@ -7554,7 +7554,7 @@
         <v>432</v>
       </c>
       <c r="E177" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F177" s="27"/>
       <c r="G177" s="27"/>
@@ -7620,7 +7620,7 @@
         <v>432</v>
       </c>
       <c r="E180" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F180" s="27"/>
       <c r="G180" s="27"/>
@@ -7686,7 +7686,7 @@
         <v>432</v>
       </c>
       <c r="E183" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F183" s="27"/>
       <c r="G183" s="27"/>
@@ -7752,7 +7752,7 @@
         <v>432</v>
       </c>
       <c r="E186" s="27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F186" s="27"/>
       <c r="G186" s="27"/>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D188" s="27"/>
       <c r="E188" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F188" s="27"/>
       <c r="G188" s="27"/>
@@ -7858,7 +7858,7 @@
         <v>405</v>
       </c>
       <c r="E191" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F191" s="27"/>
       <c r="G191" s="27"/>
@@ -7902,7 +7902,7 @@
         <v>410</v>
       </c>
       <c r="E193" s="27" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F193" s="27"/>
       <c r="G193" s="27"/>
@@ -7946,7 +7946,7 @@
         <v>413</v>
       </c>
       <c r="E195" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F195" s="27"/>
       <c r="G195" s="27"/>
@@ -7968,7 +7968,7 @@
         <v>416</v>
       </c>
       <c r="E196" s="27" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F196" s="27"/>
       <c r="G196" s="27"/>
@@ -7990,7 +7990,7 @@
         <v>418</v>
       </c>
       <c r="E197" s="27">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F197" s="27"/>
       <c r="G197" s="27"/>
@@ -8078,7 +8078,7 @@
         <v>285</v>
       </c>
       <c r="E201" s="27" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F201" s="27"/>
       <c r="G201" s="27"/>
@@ -8543,7 +8543,7 @@
         <v>262</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
@@ -8554,7 +8554,7 @@
         <v>262</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
@@ -8565,7 +8565,7 @@
         <v>262</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
@@ -8576,7 +8576,7 @@
         <v>262</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -8587,7 +8587,7 @@
         <v>262</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/Login_TC.xlsx
+++ b/src/test/resources/Login_TC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\automation-framework\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3F4CDE-8361-4BAF-82AD-F62F409E5C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDE1930-1326-46A8-95BB-D14CEC8E608F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{014559CE-770C-44B1-B217-FE0B04801BDC}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="3" r:id="rId1"/>
